--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fragment_material" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_fragment" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -625,11 +625,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1042,159 +1043,328 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13.0769230769231" customWidth="1" style="1" min="1" max="1"/>
-    <col width="20.3846153846154" customWidth="1" style="1" min="2" max="2"/>
-    <col width="13.4615384615385" customWidth="1" style="1" min="3" max="3"/>
-    <col width="12.0769230769231" customWidth="1" style="1" min="4" max="4"/>
-    <col width="11.8461538461538" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.0769230769231" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
+    <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="13.4615384615385" customWidth="1" min="2" max="2"/>
+    <col width="17.6153846153846" customWidth="1" min="3" max="3"/>
+    <col width="15.1538461538462" customWidth="1" min="5" max="5"/>
+    <col width="10.3076923076923" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>fragmentId</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>materialId</t>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>baseWeight</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>hiddenRange</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>*shapeRows</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>*materialIds</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>##comment</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>碎片格标签记录ID</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>胃碎片ID</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>格子X坐标</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>格子Y坐标</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>挂载标签ID</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>餐桌碎片ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>随机基础权重</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>商店价格</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>出现隐藏分区间(单元格: min,max)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>碎片形状行列表</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>该碎片形状可随机分布的材质ID列表（运行时按占格稳定随机落位）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>HiddenRange</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>list,string</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>fct_gold2x2_0_0</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>gut_4x4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>XXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>XXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>XXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>XXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>frag_1x2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>frag_2x1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>frag_L</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10,25</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>m_cherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>.X</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>frag_gold2x2</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25,45</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>m_gold</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>fct_L_1_1</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>frag_L</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>m_cherry</t>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>XX</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15200" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -263,7 +263,8 @@
     <t>翡翠</t>
   </si>
   <si>
-    <t>每占 1 格翡翠，倍率+0.3</t>
+    <t>每占 1 格翡翠
+倍率+0.3</t>
   </si>
   <si>
     <t>AddMultFlatPerCell</t>
@@ -275,7 +276,8 @@
     <t>金</t>
   </si>
   <si>
-    <t>占据 2 格金餐桌时，获得 10 金币。</t>
+    <t>占据 2 格金餐桌时
++ 10 金币</t>
   </si>
   <si>
     <t>GrantGoldIfCellCount</t>
@@ -290,7 +292,8 @@
     <t>银</t>
   </si>
   <si>
-    <t>占据 2 格银餐桌时，1/3 概率获得主动道具。</t>
+    <t>占据 2 格银餐桌时
+1/3 概率获得主动道具</t>
   </si>
   <si>
     <t>GrantItemRollIfCellCount</t>
@@ -910,10 +913,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1807,14 +1813,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1824,14 +1830,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>86</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1844,14 +1850,14 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
         <v>89</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E10" s="1" t="s">

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="213">
   <si>
     <t>##var</t>
   </si>
@@ -26,9 +26,6 @@
     <t>baseWeight</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>hiddenRange</t>
   </si>
   <si>
@@ -47,10 +44,7 @@
     <t>随机基础权重</t>
   </si>
   <si>
-    <t>商店价格</t>
-  </si>
-  <si>
-    <t>出现隐藏分区间(单元格: min,max)</t>
+    <t>出现隐藏分区间</t>
   </si>
   <si>
     <t>碎片形状行列表</t>
@@ -68,9 +62,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>HiddenRange</t>
   </si>
   <si>
@@ -86,73 +77,454 @@
     <t>XXXX</t>
   </si>
   <si>
+    <t>0周</t>
+  </si>
+  <si>
     <t>frag_1x1</t>
   </si>
   <si>
-    <t>1,10</t>
+    <t>10,100</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
+    <t>1周</t>
+  </si>
+  <si>
     <t>frag_1x2</t>
   </si>
   <si>
     <t>XX</t>
   </si>
   <si>
+    <t>2周</t>
+  </si>
+  <si>
     <t>frag_2x1</t>
   </si>
   <si>
+    <t>3周</t>
+  </si>
+  <si>
+    <t>4周</t>
+  </si>
+  <si>
+    <t>frag_L1</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
+    <t>.X</t>
+  </si>
+  <si>
+    <t>frag_L2</t>
+  </si>
+  <si>
+    <t>frag_L3</t>
+  </si>
+  <si>
+    <t>X.</t>
+  </si>
+  <si>
+    <t>frag_L4</t>
+  </si>
+  <si>
+    <t>frag_2x2</t>
+  </si>
+  <si>
+    <t>40,100</t>
+  </si>
+  <si>
+    <t>frag_L5</t>
+  </si>
+  <si>
+    <t>frag_L6</t>
+  </si>
+  <si>
+    <t>frag_L7</t>
+  </si>
+  <si>
+    <t>frag_L8</t>
+  </si>
+  <si>
+    <t>frag_S1</t>
+  </si>
+  <si>
+    <t>frag_S2</t>
+  </si>
+  <si>
+    <t>frag_S3</t>
+  </si>
+  <si>
+    <t>.XX</t>
+  </si>
+  <si>
+    <t>XX.</t>
+  </si>
+  <si>
+    <t>frag_S4</t>
+  </si>
+  <si>
+    <t>frag_1x1_cherry</t>
+  </si>
+  <si>
     <t>m_cherry</t>
   </si>
   <si>
-    <t>frag_L1</t>
-  </si>
-  <si>
-    <t>10,25</t>
-  </si>
-  <si>
-    <t>.X</t>
+    <t>frag_1x2_cherry</t>
+  </si>
+  <si>
+    <t>frag_2x1_cherry</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>frag_L1_cherry</t>
+  </si>
+  <si>
+    <t>frag_L2_cherry</t>
+  </si>
+  <si>
+    <t>frag_L3_cherry</t>
+  </si>
+  <si>
+    <t>frag_L4_cherry</t>
+  </si>
+  <si>
+    <t>frag_2x2_cherry</t>
+  </si>
+  <si>
+    <t>frag_L5_cherry</t>
+  </si>
+  <si>
+    <t>frag_L6_cherry</t>
+  </si>
+  <si>
+    <t>frag_L7_cherry</t>
+  </si>
+  <si>
+    <t>frag_L8_cherry</t>
+  </si>
+  <si>
+    <t>frag_S1_cherry</t>
+  </si>
+  <si>
+    <t>frag_S2_cherry</t>
+  </si>
+  <si>
+    <t>frag_S3_cherry</t>
+  </si>
+  <si>
+    <t>frag_S4_cherry</t>
+  </si>
+  <si>
+    <t>frag_1x1_walnut</t>
+  </si>
+  <si>
+    <t>m_walnut</t>
+  </si>
+  <si>
+    <t>frag_1x2_walnut</t>
+  </si>
+  <si>
+    <t>frag_2x1_walnut</t>
+  </si>
+  <si>
+    <t>frag_L1_walnut</t>
+  </si>
+  <si>
+    <t>frag_L2_walnut</t>
+  </si>
+  <si>
+    <t>frag_L3_walnut</t>
+  </si>
+  <si>
+    <t>frag_L4_walnut</t>
+  </si>
+  <si>
+    <t>frag_2x2_walnut</t>
+  </si>
+  <si>
+    <t>frag_L5_walnut</t>
+  </si>
+  <si>
+    <t>frag_L6_walnut</t>
+  </si>
+  <si>
+    <t>frag_L7_walnut</t>
+  </si>
+  <si>
+    <t>frag_L8_walnut</t>
+  </si>
+  <si>
+    <t>frag_S1_walnut</t>
+  </si>
+  <si>
+    <t>frag_S2_walnut</t>
+  </si>
+  <si>
+    <t>frag_S3_walnut</t>
+  </si>
+  <si>
+    <t>frag_S4_walnut</t>
+  </si>
+  <si>
+    <t>frag_1x1_marble</t>
+  </si>
+  <si>
+    <t>m_marble</t>
+  </si>
+  <si>
+    <t>frag_1x2_marble</t>
+  </si>
+  <si>
+    <t>frag_2x1_marble</t>
+  </si>
+  <si>
+    <t>frag_L1_marble</t>
+  </si>
+  <si>
+    <t>frag_L2_marble</t>
+  </si>
+  <si>
+    <t>frag_L3_marble</t>
+  </si>
+  <si>
+    <t>frag_L4_marble</t>
+  </si>
+  <si>
+    <t>frag_2x2_marble</t>
+  </si>
+  <si>
+    <t>frag_L5_marble</t>
+  </si>
+  <si>
+    <t>frag_L6_marble</t>
+  </si>
+  <si>
+    <t>frag_L7_marble</t>
+  </si>
+  <si>
+    <t>frag_L8_marble</t>
+  </si>
+  <si>
+    <t>frag_S1_marble</t>
+  </si>
+  <si>
+    <t>frag_S2_marble</t>
+  </si>
+  <si>
+    <t>frag_S3_marble</t>
+  </si>
+  <si>
+    <t>frag_S4_marble</t>
+  </si>
+  <si>
+    <t>frag_1x1_obsidian</t>
+  </si>
+  <si>
+    <t>m_obsidian</t>
+  </si>
+  <si>
+    <t>frag_1x2_obsidian</t>
+  </si>
+  <si>
+    <t>frag_2x1_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L1_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L2_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L3_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L4_obsidian</t>
+  </si>
+  <si>
+    <t>frag_2x2_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L5_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L6_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L7_obsidian</t>
+  </si>
+  <si>
+    <t>frag_L8_obsidian</t>
+  </si>
+  <si>
+    <t>frag_S1_obsidian</t>
+  </si>
+  <si>
+    <t>frag_S2_obsidian</t>
+  </si>
+  <si>
+    <t>frag_S3_obsidian</t>
+  </si>
+  <si>
+    <t>frag_S4_obsidian</t>
+  </si>
+  <si>
+    <t>frag_1x1_emerald</t>
+  </si>
+  <si>
+    <t>m_emerald</t>
+  </si>
+  <si>
+    <t>frag_1x2_emerald</t>
+  </si>
+  <si>
+    <t>frag_2x1_emerald</t>
+  </si>
+  <si>
+    <t>frag_L1_emerald</t>
+  </si>
+  <si>
+    <t>frag_L2_emerald</t>
+  </si>
+  <si>
+    <t>frag_L3_emerald</t>
+  </si>
+  <si>
+    <t>frag_L4_emerald</t>
+  </si>
+  <si>
+    <t>frag_2x2_emerald</t>
+  </si>
+  <si>
+    <t>frag_L5_emerald</t>
+  </si>
+  <si>
+    <t>frag_L6_emerald</t>
+  </si>
+  <si>
+    <t>frag_L7_emerald</t>
+  </si>
+  <si>
+    <t>frag_L8_emerald</t>
+  </si>
+  <si>
+    <t>frag_S1_emerald</t>
+  </si>
+  <si>
+    <t>frag_S2_emerald</t>
+  </si>
+  <si>
+    <t>frag_S3_emerald</t>
+  </si>
+  <si>
+    <t>frag_S4_emerald</t>
+  </si>
+  <si>
+    <t>frag_1x1_gold</t>
   </si>
   <si>
     <t>m_gold</t>
   </si>
   <si>
-    <t>frag_L2</t>
-  </si>
-  <si>
-    <t>frag_L3</t>
-  </si>
-  <si>
-    <t>X.</t>
-  </si>
-  <si>
-    <t>frag_L4</t>
-  </si>
-  <si>
-    <t>frag_gold2x2</t>
-  </si>
-  <si>
-    <t>25,45</t>
-  </si>
-  <si>
-    <t>frag_L5</t>
-  </si>
-  <si>
-    <t>frag_L6</t>
-  </si>
-  <si>
-    <t>frag_L7</t>
-  </si>
-  <si>
-    <t>25,46</t>
-  </si>
-  <si>
-    <t>frag_L8</t>
-  </si>
-  <si>
-    <t>25,47</t>
+    <t>frag_1x2_gold</t>
+  </si>
+  <si>
+    <t>frag_2x1_gold</t>
+  </si>
+  <si>
+    <t>frag_L1_gold</t>
+  </si>
+  <si>
+    <t>frag_L2_gold</t>
+  </si>
+  <si>
+    <t>frag_L3_gold</t>
+  </si>
+  <si>
+    <t>frag_L4_gold</t>
+  </si>
+  <si>
+    <t>frag_2x2_gold</t>
+  </si>
+  <si>
+    <t>frag_L5_gold</t>
+  </si>
+  <si>
+    <t>frag_L6_gold</t>
+  </si>
+  <si>
+    <t>frag_L7_gold</t>
+  </si>
+  <si>
+    <t>frag_L8_gold</t>
+  </si>
+  <si>
+    <t>frag_S1_gold</t>
+  </si>
+  <si>
+    <t>frag_S2_gold</t>
+  </si>
+  <si>
+    <t>frag_S3_gold</t>
+  </si>
+  <si>
+    <t>frag_S4_gold</t>
+  </si>
+  <si>
+    <t>frag_1x1_silver</t>
+  </si>
+  <si>
+    <t>m_silver</t>
+  </si>
+  <si>
+    <t>frag_1x2_silver</t>
+  </si>
+  <si>
+    <t>frag_2x1_silver</t>
+  </si>
+  <si>
+    <t>frag_L1_silver</t>
+  </si>
+  <si>
+    <t>frag_L2_silver</t>
+  </si>
+  <si>
+    <t>frag_L3_silver</t>
+  </si>
+  <si>
+    <t>frag_L4_silver</t>
+  </si>
+  <si>
+    <t>frag_2x2_silver</t>
+  </si>
+  <si>
+    <t>frag_L5_silver</t>
+  </si>
+  <si>
+    <t>frag_L6_silver</t>
+  </si>
+  <si>
+    <t>frag_L7_silver</t>
+  </si>
+  <si>
+    <t>frag_L8_silver</t>
+  </si>
+  <si>
+    <t>frag_S1_silver</t>
+  </si>
+  <si>
+    <t>frag_S2_silver</t>
+  </si>
+  <si>
+    <t>frag_S3_silver</t>
+  </si>
+  <si>
+    <t>frag_S4_silver</t>
   </si>
   <si>
     <t>name</t>
@@ -212,9 +584,6 @@
     <t>30</t>
   </si>
   <si>
-    <t>m_walnut</t>
-  </si>
-  <si>
     <t>胡桃木</t>
   </si>
   <si>
@@ -227,9 +596,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>m_marble</t>
-  </si>
-  <si>
     <t>大理石</t>
   </si>
   <si>
@@ -242,9 +608,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>m_obsidian</t>
-  </si>
-  <si>
     <t>黑曜石</t>
   </si>
   <si>
@@ -255,9 +618,6 @@
   </si>
   <si>
     <t>1.5</t>
-  </si>
-  <si>
-    <t>m_emerald</t>
   </si>
   <si>
     <t>翡翠</t>
@@ -284,9 +644,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>m_silver</t>
   </si>
   <si>
     <t>银</t>
@@ -913,13 +1270,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1267,381 +1633,4216 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:S312"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="13.4615384615385" customWidth="1"/>
-    <col min="3" max="3" width="17.6153846153846" customWidth="1"/>
-    <col min="5" max="5" width="15.1538461538462" customWidth="1"/>
-    <col min="6" max="6" width="17.6153846153846" customWidth="1"/>
-    <col min="7" max="7" width="27.6153846153846" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="3" customWidth="1"/>
+    <col min="2" max="2" width="16.5384615384615" style="3" customWidth="1"/>
+    <col min="3" max="3" width="17.6153846153846" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.6153846153846" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.6153846153846" style="3" customWidth="1"/>
+    <col min="6" max="6" width="27.6153846153846" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3" customWidth="1"/>
+    <col min="8" max="12" width="9" style="3"/>
+    <col min="13" max="13" width="12.9230769230769" style="3"/>
+    <col min="14" max="20" width="9" style="3"/>
+    <col min="21" max="21" width="12.2307692307692" style="3" customWidth="1"/>
+    <col min="22" max="22" width="9" style="3"/>
+    <col min="23" max="23" width="43.3846153846154" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+    </row>
+    <row r="5" spans="5:5">
+      <c r="E5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
-      <c r="B4" t="s">
+    <row r="6" spans="5:19">
+      <c r="E6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="L6" s="3">
+        <v>10</v>
+      </c>
+      <c r="M6" s="3">
+        <v>11</v>
+      </c>
+      <c r="N6" s="3">
+        <v>12</v>
+      </c>
+      <c r="O6" s="3">
+        <v>13</v>
+      </c>
+      <c r="P6" s="3">
+        <v>14</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>15</v>
+      </c>
+      <c r="R6" s="3">
+        <v>16</v>
+      </c>
+      <c r="S6" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C7" s="3">
+        <v>7</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="6:6">
-      <c r="F5" t="s">
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3">
+        <v>20</v>
+      </c>
+      <c r="M7" s="3">
+        <v>21</v>
+      </c>
+      <c r="N7" s="3">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="6:6">
-      <c r="F6" t="s">
+      <c r="O7" s="3">
+        <v>23</v>
+      </c>
+      <c r="P7" s="3">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>25</v>
+      </c>
+      <c r="R7" s="3">
+        <v>26</v>
+      </c>
+      <c r="S7" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3">
+        <v>700</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" t="s">
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="3">
+        <v>30</v>
+      </c>
+      <c r="M8" s="3">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3">
+        <v>32</v>
+      </c>
+      <c r="O8" s="3">
+        <v>33</v>
+      </c>
+      <c r="P8" s="3">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>35</v>
+      </c>
+      <c r="R8" s="3">
+        <v>36</v>
+      </c>
+      <c r="S8" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3">
+        <v>700</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="6:12">
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" t="s">
+      <c r="K9" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" t="s">
+      <c r="L9" s="3">
+        <v>40</v>
+      </c>
+      <c r="M9" s="3">
+        <v>41</v>
+      </c>
+      <c r="N9" s="3">
+        <v>42</v>
+      </c>
+      <c r="O9" s="3">
+        <v>43</v>
+      </c>
+      <c r="P9" s="3">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>45</v>
+      </c>
+      <c r="R9" s="3">
+        <v>46</v>
+      </c>
+      <c r="S9" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="5:19">
+      <c r="E10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11">
+      <c r="L10" s="3">
+        <v>50</v>
+      </c>
+      <c r="M10" s="3">
+        <v>51</v>
+      </c>
+      <c r="N10" s="3">
+        <v>52</v>
+      </c>
+      <c r="O10" s="3">
+        <v>53</v>
+      </c>
+      <c r="P10" s="3">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>55</v>
+      </c>
+      <c r="R10" s="3">
+        <v>56</v>
+      </c>
+      <c r="S10" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3">
+        <v>700</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="5:5">
+      <c r="E12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3">
+        <v>700</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="3">
+        <v>700</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="5:5">
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3">
+        <v>700</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="3">
+        <v>700</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5">
+      <c r="D20" s="5"/>
+      <c r="E20" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3">
+        <v>700</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5">
+      <c r="D22" s="5"/>
+      <c r="E22" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5">
+      <c r="D23" s="5"/>
+      <c r="E23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="3">
+        <v>700</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5">
+      <c r="D25" s="5"/>
+      <c r="E25" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5">
+      <c r="D26" s="5"/>
+      <c r="E26" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="3">
+        <v>700</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5">
+      <c r="D28" s="5"/>
+      <c r="E28" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
+      <c r="D29" s="5"/>
+      <c r="E29" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="3">
+        <v>700</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5">
+      <c r="D31" s="5"/>
+      <c r="E31" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5">
+      <c r="D32" s="5"/>
+      <c r="E32" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="3">
+        <v>700</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="4:5">
+      <c r="D34" s="5"/>
+      <c r="E34" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="4:5">
+      <c r="D35" s="5"/>
+      <c r="E35" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="3">
+        <v>700</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="4:5">
+      <c r="D37" s="5"/>
+      <c r="E37" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="4:5">
+      <c r="D38" s="5"/>
+      <c r="E38" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="3">
+        <v>700</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="4:5">
+      <c r="D40" s="5"/>
+      <c r="E40" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="3">
+        <v>700</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="4:5">
+      <c r="D42" s="5"/>
+      <c r="E42" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="3">
+        <v>100</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F44" s="3" t="str">
+        <f>IF(B44="","",$F$43)</f>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="3">
+        <v>100</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="3" t="str">
+        <f t="shared" ref="F45:F77" si="0">IF(B45="","",$F$43)</f>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C47" s="3">
+        <v>100</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F47" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="3">
+        <v>100</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F50" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="3">
+        <v>100</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C53" s="3">
+        <v>100</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C55" s="3">
+        <v>100</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F56" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="3">
+        <v>100</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60" s="3">
+        <v>100</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="5"/>
+      <c r="E62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="3">
+        <v>100</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="E64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="B65" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D65" s="5"/>
+      <c r="E65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="B66" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" s="3">
+        <v>100</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F66" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="B67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D67" s="5"/>
+      <c r="E67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="B68" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" s="5"/>
+      <c r="E68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F68" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" s="3">
+        <v>100</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D70" s="5"/>
+      <c r="E70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D71" s="5"/>
+      <c r="E71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C72" s="3">
+        <v>100</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F72" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="B73" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" s="5"/>
+      <c r="E73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="B74" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D74" s="5"/>
+      <c r="E74" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="B75" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="3">
+        <v>100</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F75" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
+      <c r="B76" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D76" s="5"/>
+      <c r="E76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
+      <c r="B77" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C77" s="3">
+        <v>100</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="78" spans="4:7">
+      <c r="D78" s="5"/>
+      <c r="E78" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G78" s="3" t="str">
+        <f>IF(B78="","",B78&amp;"_cherry")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
+      <c r="B79" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="3">
+        <v>1</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
+      <c r="B80" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="6:12">
-      <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13">
-        <v>70</v>
-      </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="6:6">
-      <c r="F14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15">
-        <v>70</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17">
-        <v>70</v>
-      </c>
-      <c r="D17">
-        <v>4</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="6:6">
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19">
-        <v>70</v>
-      </c>
-      <c r="D19">
-        <v>6</v>
-      </c>
-      <c r="E19" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="6:6">
-      <c r="F20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21">
-        <v>70</v>
-      </c>
-      <c r="E21" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="6:6">
-      <c r="F22" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="6:6">
-      <c r="F23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24">
-        <v>70</v>
-      </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="25" spans="6:6">
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="6:6">
-      <c r="F26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27">
-        <v>70</v>
-      </c>
-      <c r="E27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="6:6">
-      <c r="F28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="6:6">
-      <c r="F29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30">
-        <v>70</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="6:6">
-      <c r="F31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="6:6">
-      <c r="F32" t="s">
-        <v>36</v>
-      </c>
+      <c r="C80" s="3">
+        <v>100</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6">
+      <c r="B81" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="3">
+        <v>100</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
+      <c r="B82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="5"/>
+      <c r="E82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="2:6">
+      <c r="B83" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="3">
+        <v>100</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
+      <c r="B84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D84" s="5"/>
+      <c r="E84" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
+      <c r="B85" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="3">
+        <v>100</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6">
+      <c r="B86" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" s="5"/>
+      <c r="E86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6">
+      <c r="B87" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="3">
+        <v>100</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6">
+      <c r="B88" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" s="5"/>
+      <c r="E88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6">
+      <c r="B89" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89" s="3">
+        <v>100</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
+      <c r="B90" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="E90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="91" spans="2:6">
+      <c r="B91" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C91" s="3">
+        <v>100</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6">
+      <c r="B92" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" s="5"/>
+      <c r="E92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
+      <c r="B93" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" s="3">
+        <v>100</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="2:6">
+      <c r="B94" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D94" s="5"/>
+      <c r="E94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
+      <c r="B95" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D95" s="5"/>
+      <c r="E95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
+      <c r="B96" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C96" s="3">
+        <v>100</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="5"/>
+      <c r="E97" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D98" s="5"/>
+      <c r="E98" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
+      <c r="B99" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C99" s="3">
+        <v>100</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D100" s="5"/>
+      <c r="E100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D101" s="5"/>
+      <c r="E101" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C102" s="3">
+        <v>100</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D103" s="5"/>
+      <c r="E103" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D104" s="5"/>
+      <c r="E104" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C105" s="3">
+        <v>100</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6">
+      <c r="B106" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D106" s="5"/>
+      <c r="E106" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D107" s="5"/>
+      <c r="E107" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C108" s="3">
+        <v>100</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D109" s="5"/>
+      <c r="E109" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D110" s="5"/>
+      <c r="E110" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6">
+      <c r="B111" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C111" s="3">
+        <v>100</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D112" s="5"/>
+      <c r="E112" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
+      <c r="B113" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C113" s="3">
+        <v>100</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="114" spans="4:5">
+      <c r="D114" s="5"/>
+      <c r="E114" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6">
+      <c r="B115" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="116" spans="2:6">
+      <c r="B116" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C116" s="3">
+        <v>100</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="2:6">
+      <c r="B117" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C117" s="3">
+        <v>100</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
+      <c r="B118" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D118" s="5"/>
+      <c r="E118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
+      <c r="B119" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C119" s="3">
+        <v>100</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
+      <c r="B120" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D120" s="5"/>
+      <c r="E120" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
+      <c r="B121" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C121" s="3">
+        <v>100</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
+      <c r="B122" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D122" s="5"/>
+      <c r="E122" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
+      <c r="B123" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C123" s="3">
+        <v>100</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D124" s="5"/>
+      <c r="E124" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="125" spans="2:6">
+      <c r="B125" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C125" s="3">
+        <v>100</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="126" spans="2:6">
+      <c r="B126" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D126" s="5"/>
+      <c r="E126" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6">
+      <c r="B127" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C127" s="3">
+        <v>100</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="2:6">
+      <c r="B128" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D128" s="5"/>
+      <c r="E128" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="129" spans="2:6">
+      <c r="B129" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C129" s="3">
+        <v>100</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D130" s="5"/>
+      <c r="E130" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6">
+      <c r="B131" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D131" s="5"/>
+      <c r="E131" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6">
+      <c r="B132" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C132" s="3">
+        <v>100</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="133" spans="2:6">
+      <c r="B133" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D133" s="5"/>
+      <c r="E133" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="134" spans="2:6">
+      <c r="B134" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D134" s="5"/>
+      <c r="E134" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6">
+      <c r="B135" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C135" s="3">
+        <v>100</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D136" s="5"/>
+      <c r="E136" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D137" s="5"/>
+      <c r="E137" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6">
+      <c r="B138" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C138" s="3">
+        <v>100</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="139" spans="2:6">
+      <c r="B139" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D139" s="5"/>
+      <c r="E139" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D140" s="5"/>
+      <c r="E140" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C141" s="3">
+        <v>100</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="142" spans="2:6">
+      <c r="B142" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D142" s="5"/>
+      <c r="E142" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="143" spans="2:6">
+      <c r="B143" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D143" s="5"/>
+      <c r="E143" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C144" s="3">
+        <v>100</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6">
+      <c r="B145" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D145" s="5"/>
+      <c r="E145" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6">
+      <c r="B146" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D146" s="5"/>
+      <c r="E146" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
+      <c r="B147" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C147" s="3">
+        <v>100</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6">
+      <c r="B148" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D148" s="5"/>
+      <c r="E148" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C149" s="3">
+        <v>100</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="150" spans="4:5">
+      <c r="D150" s="5"/>
+      <c r="E150" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6">
+      <c r="B151" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C151" s="3">
+        <v>1</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C152" s="3">
+        <v>100</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6">
+      <c r="B153" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="3">
+        <v>100</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6">
+      <c r="B154" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D154" s="5"/>
+      <c r="E154" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C155" s="3">
+        <v>100</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6">
+      <c r="B156" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D156" s="5"/>
+      <c r="E156" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6">
+      <c r="B157" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C157" s="3">
+        <v>100</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" spans="2:6">
+      <c r="B158" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D158" s="5"/>
+      <c r="E158" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C159" s="3">
+        <v>100</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D160" s="5"/>
+      <c r="E160" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C161" s="3">
+        <v>100</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D162" s="5"/>
+      <c r="E162" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C163" s="3">
+        <v>100</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D164" s="5"/>
+      <c r="E164" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C165" s="3">
+        <v>100</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6">
+      <c r="B166" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D166" s="5"/>
+      <c r="E166" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6">
+      <c r="B167" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D167" s="5"/>
+      <c r="E167" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6">
+      <c r="B168" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C168" s="3">
+        <v>100</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D169" s="5"/>
+      <c r="E169" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6">
+      <c r="B170" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D170" s="5"/>
+      <c r="E170" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="171" spans="2:6">
+      <c r="B171" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C171" s="3">
+        <v>100</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D172" s="5"/>
+      <c r="E172" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6">
+      <c r="B173" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D173" s="5"/>
+      <c r="E173" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="174" spans="2:6">
+      <c r="B174" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C174" s="3">
+        <v>100</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="175" spans="2:6">
+      <c r="B175" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D176" s="5"/>
+      <c r="E176" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C177" s="3">
+        <v>100</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D178" s="5"/>
+      <c r="E178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D179" s="5"/>
+      <c r="E179" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C180" s="3">
+        <v>100</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="181" spans="2:6">
+      <c r="B181" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D181" s="5"/>
+      <c r="E181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D182" s="5"/>
+      <c r="E182" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6">
+      <c r="B183" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C183" s="3">
+        <v>100</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D184" s="5"/>
+      <c r="E184" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C185" s="3">
+        <v>100</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="186" spans="4:5">
+      <c r="D186" s="5"/>
+      <c r="E186" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="187" spans="2:6">
+      <c r="B187" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C187" s="3">
+        <v>1</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="188" spans="2:6">
+      <c r="B188" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C188" s="3">
+        <v>100</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C189" s="3">
+        <v>100</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6">
+      <c r="B190" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D190" s="5"/>
+      <c r="E190" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C191" s="3">
+        <v>100</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D192" s="5"/>
+      <c r="E192" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="193" spans="2:6">
+      <c r="B193" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C193" s="3">
+        <v>100</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="194" spans="2:6">
+      <c r="B194" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D194" s="5"/>
+      <c r="E194" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6">
+      <c r="B195" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C195" s="3">
+        <v>100</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6">
+      <c r="B196" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D196" s="5"/>
+      <c r="E196" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6">
+      <c r="B197" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C197" s="3">
+        <v>100</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="198" spans="2:6">
+      <c r="B198" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D198" s="5"/>
+      <c r="E198" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6">
+      <c r="B199" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C199" s="3">
+        <v>100</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6">
+      <c r="B200" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D200" s="5"/>
+      <c r="E200" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6">
+      <c r="B201" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C201" s="3">
+        <v>100</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6">
+      <c r="B202" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D202" s="5"/>
+      <c r="E202" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6">
+      <c r="B203" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D203" s="5"/>
+      <c r="E203" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="204" spans="2:6">
+      <c r="B204" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C204" s="3">
+        <v>100</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6">
+      <c r="B205" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D205" s="5"/>
+      <c r="E205" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="206" spans="2:6">
+      <c r="B206" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D206" s="5"/>
+      <c r="E206" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="207" spans="2:6">
+      <c r="B207" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C207" s="3">
+        <v>100</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="208" spans="2:6">
+      <c r="B208" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D208" s="5"/>
+      <c r="E208" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="209" spans="2:6">
+      <c r="B209" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D209" s="5"/>
+      <c r="E209" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="210" spans="2:6">
+      <c r="B210" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C210" s="3">
+        <v>100</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="211" spans="2:6">
+      <c r="B211" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D211" s="5"/>
+      <c r="E211" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6">
+      <c r="B212" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D212" s="5"/>
+      <c r="E212" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6">
+      <c r="B213" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C213" s="3">
+        <v>100</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="214" spans="2:6">
+      <c r="B214" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D214" s="5"/>
+      <c r="E214" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6">
+      <c r="B215" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D215" s="5"/>
+      <c r="E215" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="216" spans="2:6">
+      <c r="B216" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C216" s="3">
+        <v>100</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="217" spans="2:6">
+      <c r="B217" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D217" s="5"/>
+      <c r="E217" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6">
+      <c r="B218" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D218" s="5"/>
+      <c r="E218" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6">
+      <c r="B219" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C219" s="3">
+        <v>100</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E219" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6">
+      <c r="B220" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D220" s="5"/>
+      <c r="E220" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="221" spans="2:6">
+      <c r="B221" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C221" s="3">
+        <v>100</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E221" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="222" spans="4:5">
+      <c r="D222" s="5"/>
+      <c r="E222" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="223" spans="2:6">
+      <c r="B223" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C223" s="3">
+        <v>1</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E223" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6">
+      <c r="B224" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C224" s="3">
+        <v>100</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="225" spans="2:6">
+      <c r="B225" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C225" s="3">
+        <v>100</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6">
+      <c r="B226" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D226" s="5"/>
+      <c r="E226" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6">
+      <c r="B227" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C227" s="3">
+        <v>100</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="228" spans="2:6">
+      <c r="B228" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D228" s="5"/>
+      <c r="E228" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="229" spans="2:6">
+      <c r="B229" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C229" s="3">
+        <v>100</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="230" spans="2:6">
+      <c r="B230" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D230" s="5"/>
+      <c r="E230" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="231" spans="2:6">
+      <c r="B231" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C231" s="3">
+        <v>100</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E231" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="232" spans="2:6">
+      <c r="B232" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D232" s="5"/>
+      <c r="E232" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="233" spans="2:6">
+      <c r="B233" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C233" s="3">
+        <v>100</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="234" spans="2:6">
+      <c r="B234" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D234" s="5"/>
+      <c r="E234" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="235" spans="2:6">
+      <c r="B235" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C235" s="3">
+        <v>100</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="236" spans="2:6">
+      <c r="B236" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D236" s="5"/>
+      <c r="E236" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="237" spans="2:6">
+      <c r="B237" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C237" s="3">
+        <v>100</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="238" spans="2:6">
+      <c r="B238" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D238" s="5"/>
+      <c r="E238" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="239" spans="2:6">
+      <c r="B239" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D239" s="5"/>
+      <c r="E239" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="240" spans="2:6">
+      <c r="B240" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C240" s="3">
+        <v>100</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="241" spans="2:6">
+      <c r="B241" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D241" s="5"/>
+      <c r="E241" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="242" spans="2:6">
+      <c r="B242" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D242" s="5"/>
+      <c r="E242" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="243" spans="2:6">
+      <c r="B243" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C243" s="3">
+        <v>100</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="244" spans="2:6">
+      <c r="B244" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D244" s="5"/>
+      <c r="E244" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6">
+      <c r="B245" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D245" s="5"/>
+      <c r="E245" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6">
+      <c r="B246" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C246" s="3">
+        <v>100</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6">
+      <c r="B247" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D247" s="5"/>
+      <c r="E247" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6">
+      <c r="B248" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D248" s="5"/>
+      <c r="E248" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6">
+      <c r="B249" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C249" s="3">
+        <v>100</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6">
+      <c r="B250" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D250" s="5"/>
+      <c r="E250" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6">
+      <c r="B251" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D251" s="5"/>
+      <c r="E251" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6">
+      <c r="B252" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C252" s="3">
+        <v>100</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="253" spans="2:6">
+      <c r="B253" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D253" s="5"/>
+      <c r="E253" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="254" spans="2:6">
+      <c r="B254" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D254" s="5"/>
+      <c r="E254" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="255" spans="2:6">
+      <c r="B255" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C255" s="3">
+        <v>100</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="256" spans="2:6">
+      <c r="B256" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D256" s="5"/>
+      <c r="E256" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="257" spans="2:6">
+      <c r="B257" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C257" s="3">
+        <v>100</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E257" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="258" spans="4:5">
+      <c r="D258" s="5"/>
+      <c r="E258" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6">
+      <c r="B259" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C259" s="3">
+        <v>1</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E259" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="260" spans="2:6">
+      <c r="B260" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C260" s="3">
+        <v>100</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="261" spans="2:6">
+      <c r="B261" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C261" s="3">
+        <v>100</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E261" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6">
+      <c r="B262" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D262" s="5"/>
+      <c r="E262" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6">
+      <c r="B263" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C263" s="3">
+        <v>100</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="264" spans="2:6">
+      <c r="B264" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D264" s="5"/>
+      <c r="E264" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6">
+      <c r="B265" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C265" s="3">
+        <v>100</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E265" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="266" spans="2:6">
+      <c r="B266" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D266" s="5"/>
+      <c r="E266" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="267" spans="2:6">
+      <c r="B267" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C267" s="3">
+        <v>100</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E267" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="268" spans="2:6">
+      <c r="B268" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D268" s="5"/>
+      <c r="E268" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="269" spans="2:6">
+      <c r="B269" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C269" s="3">
+        <v>100</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E269" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="270" spans="2:6">
+      <c r="B270" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D270" s="5"/>
+      <c r="E270" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="271" spans="2:6">
+      <c r="B271" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C271" s="3">
+        <v>100</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E271" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="272" spans="2:6">
+      <c r="B272" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D272" s="5"/>
+      <c r="E272" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="273" spans="2:6">
+      <c r="B273" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C273" s="3">
+        <v>100</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E273" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="274" spans="2:6">
+      <c r="B274" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D274" s="5"/>
+      <c r="E274" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="275" spans="2:6">
+      <c r="B275" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D275" s="5"/>
+      <c r="E275" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="276" spans="2:6">
+      <c r="B276" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C276" s="3">
+        <v>100</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E276" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="277" spans="2:6">
+      <c r="B277" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D277" s="5"/>
+      <c r="E277" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="278" spans="2:6">
+      <c r="B278" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D278" s="5"/>
+      <c r="E278" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="279" spans="2:6">
+      <c r="B279" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C279" s="3">
+        <v>100</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E279" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="280" spans="2:6">
+      <c r="B280" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D280" s="5"/>
+      <c r="E280" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="281" spans="2:6">
+      <c r="B281" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D281" s="5"/>
+      <c r="E281" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="282" spans="2:6">
+      <c r="B282" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C282" s="3">
+        <v>100</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E282" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="283" spans="2:6">
+      <c r="B283" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D283" s="5"/>
+      <c r="E283" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="284" spans="2:6">
+      <c r="B284" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D284" s="5"/>
+      <c r="E284" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="285" spans="2:6">
+      <c r="B285" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C285" s="3">
+        <v>100</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E285" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="286" spans="2:6">
+      <c r="B286" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D286" s="5"/>
+      <c r="E286" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="287" spans="2:6">
+      <c r="B287" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D287" s="5"/>
+      <c r="E287" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="288" spans="2:6">
+      <c r="B288" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C288" s="3">
+        <v>100</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E288" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="289" spans="2:6">
+      <c r="B289" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D289" s="5"/>
+      <c r="E289" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="290" spans="2:6">
+      <c r="B290" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D290" s="5"/>
+      <c r="E290" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="291" spans="2:6">
+      <c r="B291" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C291" s="3">
+        <v>100</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E291" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="292" spans="2:6">
+      <c r="B292" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D292" s="5"/>
+      <c r="E292" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="293" spans="2:6">
+      <c r="B293" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C293" s="3">
+        <v>100</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E293" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="294" spans="4:5">
+      <c r="D294" s="5"/>
+      <c r="E294" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="295" spans="4:4">
+      <c r="D295" s="5"/>
+    </row>
+    <row r="296" spans="4:4">
+      <c r="D296" s="5"/>
+    </row>
+    <row r="297" spans="4:4">
+      <c r="D297" s="5"/>
+    </row>
+    <row r="298" spans="4:4">
+      <c r="D298" s="5"/>
+    </row>
+    <row r="299" spans="4:4">
+      <c r="D299" s="5"/>
+    </row>
+    <row r="300" spans="4:4">
+      <c r="D300" s="5"/>
+    </row>
+    <row r="301" spans="4:4">
+      <c r="D301" s="5"/>
+    </row>
+    <row r="302" spans="4:4">
+      <c r="D302" s="5"/>
+    </row>
+    <row r="303" spans="4:4">
+      <c r="D303" s="5"/>
+    </row>
+    <row r="304" spans="4:4">
+      <c r="D304" s="5"/>
+    </row>
+    <row r="305" spans="4:4">
+      <c r="D305" s="5"/>
+    </row>
+    <row r="306" spans="4:4">
+      <c r="D306" s="5"/>
+    </row>
+    <row r="307" spans="4:4">
+      <c r="D307" s="5"/>
+    </row>
+    <row r="308" spans="4:4">
+      <c r="D308" s="5"/>
+    </row>
+    <row r="309" spans="4:4">
+      <c r="D309" s="5"/>
+    </row>
+    <row r="310" spans="4:4">
+      <c r="D310" s="5"/>
+    </row>
+    <row r="311" spans="4:4">
+      <c r="D311" s="5"/>
+    </row>
+    <row r="312" spans="4:4">
+      <c r="D312" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1675,199 +5876,199 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>54</v>
+        <v>178</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>58</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>187</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>74</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>81</v>
+        <v>201</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>206</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>90</v>
+        <v>209</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>92</v>
+        <v>211</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>88</v>
+        <v>208</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>93</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="214">
   <si>
     <t>##var</t>
   </si>
@@ -134,40 +134,43 @@
     <t>frag_2x2</t>
   </si>
   <si>
+    <t>30,100</t>
+  </si>
+  <si>
+    <t>frag_L5</t>
+  </si>
+  <si>
+    <t>frag_L6</t>
+  </si>
+  <si>
+    <t>frag_L7</t>
+  </si>
+  <si>
+    <t>frag_L8</t>
+  </si>
+  <si>
+    <t>frag_S1</t>
+  </si>
+  <si>
+    <t>frag_S2</t>
+  </si>
+  <si>
+    <t>frag_S3</t>
+  </si>
+  <si>
+    <t>.XX</t>
+  </si>
+  <si>
+    <t>XX.</t>
+  </si>
+  <si>
+    <t>frag_S4</t>
+  </si>
+  <si>
+    <t>frag_1x1_cherry</t>
+  </si>
+  <si>
     <t>40,100</t>
-  </si>
-  <si>
-    <t>frag_L5</t>
-  </si>
-  <si>
-    <t>frag_L6</t>
-  </si>
-  <si>
-    <t>frag_L7</t>
-  </si>
-  <si>
-    <t>frag_L8</t>
-  </si>
-  <si>
-    <t>frag_S1</t>
-  </si>
-  <si>
-    <t>frag_S2</t>
-  </si>
-  <si>
-    <t>frag_S3</t>
-  </si>
-  <si>
-    <t>.XX</t>
-  </si>
-  <si>
-    <t>XX.</t>
-  </si>
-  <si>
-    <t>frag_S4</t>
-  </si>
-  <si>
-    <t>frag_1x1_cherry</t>
   </si>
   <si>
     <t>m_cherry</t>
@@ -2218,24 +2221,24 @@
         <v>1</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C44" s="3">
         <v>100</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>26</v>
@@ -2247,13 +2250,13 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C45" s="3">
         <v>100</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>23</v>
@@ -2265,7 +2268,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="3" t="s">
@@ -2278,13 +2281,13 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C47" s="3">
         <v>100</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>26</v>
@@ -2296,7 +2299,7 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="3" t="s">
@@ -2309,13 +2312,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C49" s="3">
         <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>33</v>
@@ -2327,7 +2330,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="3" t="s">
@@ -2340,13 +2343,13 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C51" s="3">
         <v>100</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>36</v>
@@ -2358,7 +2361,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
@@ -2371,13 +2374,13 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C53" s="3">
         <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>26</v>
@@ -2389,7 +2392,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
@@ -2402,13 +2405,13 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C55" s="3">
         <v>100</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>26</v>
@@ -2420,7 +2423,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="3" t="s">
@@ -2433,13 +2436,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3">
         <v>100</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>26</v>
@@ -2451,7 +2454,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
@@ -2464,7 +2467,7 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D59" s="5"/>
       <c r="E59" s="3" t="s">
@@ -2477,13 +2480,13 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C60" s="3">
         <v>100</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>33</v>
@@ -2495,7 +2498,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="3" t="s">
@@ -2508,7 +2511,7 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="3" t="s">
@@ -2521,13 +2524,13 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C63" s="3">
         <v>100</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>36</v>
@@ -2539,7 +2542,7 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="3" t="s">
@@ -2552,7 +2555,7 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
@@ -2565,13 +2568,13 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C66" s="3">
         <v>100</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>26</v>
@@ -2583,7 +2586,7 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D67" s="5"/>
       <c r="E67" s="3" t="s">
@@ -2596,7 +2599,7 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="3" t="s">
@@ -2609,13 +2612,13 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C69" s="3">
         <v>100</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>36</v>
@@ -2627,7 +2630,7 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="3" t="s">
@@ -2640,7 +2643,7 @@
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
@@ -2653,13 +2656,13 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C72" s="3">
         <v>100</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>33</v>
@@ -2671,7 +2674,7 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D73" s="5"/>
       <c r="E73" s="3" t="s">
@@ -2684,7 +2687,7 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="3" t="s">
@@ -2697,13 +2700,13 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C75" s="3">
         <v>100</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>47</v>
@@ -2715,7 +2718,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="3" t="s">
@@ -2728,13 +2731,13 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C77" s="3">
         <v>100</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>48</v>
@@ -2756,502 +2759,502 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C79" s="3">
         <v>1</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="3">
+        <v>100</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F80" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="C80" s="3">
-        <v>100</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="3">
         <v>100</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C83" s="3">
         <v>100</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C87" s="3">
         <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C89" s="3">
         <v>100</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C91" s="3">
         <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C93" s="3">
         <v>100</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D95" s="5"/>
       <c r="E95" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C96" s="3">
         <v>100</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D97" s="5"/>
       <c r="E97" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C99" s="3">
         <v>100</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D100" s="5"/>
       <c r="E100" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C102" s="3">
         <v>100</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D103" s="5"/>
       <c r="E103" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C105" s="3">
         <v>100</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D106" s="5"/>
       <c r="E106" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C108" s="3">
         <v>100</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E108" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D109" s="5"/>
       <c r="E109" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C111" s="3">
         <v>100</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D112" s="5"/>
       <c r="E112" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C113" s="3">
         <v>100</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="4:5">
@@ -3262,502 +3265,502 @@
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C115" s="3">
         <v>1</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C116" s="3">
+        <v>100</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="C116" s="3">
-        <v>100</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C117" s="3">
         <v>100</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="2:6">
       <c r="B118" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D118" s="5"/>
       <c r="E118" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C119" s="3">
         <v>100</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D120" s="5"/>
       <c r="E120" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C123" s="3">
         <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C125" s="3">
         <v>100</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C127" s="3">
         <v>100</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C129" s="3">
         <v>100</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D131" s="5"/>
       <c r="E131" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C132" s="3">
         <v>100</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D133" s="5"/>
       <c r="E133" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="135" spans="2:6">
       <c r="B135" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C135" s="3">
         <v>100</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D136" s="5"/>
       <c r="E136" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="2:6">
       <c r="B138" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C138" s="3">
         <v>100</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D139" s="5"/>
       <c r="E139" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" spans="2:6">
       <c r="B141" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C141" s="3">
         <v>100</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D142" s="5"/>
       <c r="E142" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="144" spans="2:6">
       <c r="B144" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C144" s="3">
         <v>100</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D145" s="5"/>
       <c r="E145" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C147" s="3">
         <v>100</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D148" s="5"/>
       <c r="E148" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C149" s="3">
         <v>100</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="4:5">
@@ -3768,502 +3771,502 @@
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C151" s="3">
         <v>1</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C152" s="3">
+        <v>100</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F152" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="C152" s="3">
-        <v>100</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E152" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C153" s="3">
         <v>100</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="154" spans="2:6">
       <c r="B154" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D154" s="5"/>
       <c r="E154" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C155" s="3">
         <v>100</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D156" s="5"/>
       <c r="E156" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C159" s="3">
         <v>100</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C161" s="3">
         <v>100</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C163" s="3">
         <v>100</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C165" s="3">
         <v>100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D167" s="5"/>
       <c r="E167" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C168" s="3">
         <v>100</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D169" s="5"/>
       <c r="E169" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="171" spans="2:6">
       <c r="B171" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C171" s="3">
         <v>100</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D172" s="5"/>
       <c r="E172" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="2:6">
       <c r="B174" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C174" s="3">
         <v>100</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D175" s="5"/>
       <c r="E175" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="177" spans="2:6">
       <c r="B177" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C177" s="3">
         <v>100</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D178" s="5"/>
       <c r="E178" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C180" s="3">
         <v>100</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D181" s="5"/>
       <c r="E181" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="183" spans="2:6">
       <c r="B183" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C183" s="3">
         <v>100</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D184" s="5"/>
       <c r="E184" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C185" s="3">
         <v>100</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="186" spans="4:5">
@@ -4274,502 +4277,502 @@
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C187" s="3">
         <v>1</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C188" s="3">
+        <v>100</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C188" s="3">
-        <v>100</v>
-      </c>
-      <c r="D188" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C189" s="3">
         <v>100</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D190" s="5"/>
       <c r="E190" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C191" s="3">
         <v>100</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D192" s="5"/>
       <c r="E192" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C195" s="3">
         <v>100</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C197" s="3">
         <v>100</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C199" s="3">
         <v>100</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C201" s="3">
         <v>100</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D203" s="5"/>
       <c r="E203" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C204" s="3">
         <v>100</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D205" s="5"/>
       <c r="E205" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="B207" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C207" s="3">
         <v>100</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D208" s="5"/>
       <c r="E208" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C210" s="3">
         <v>100</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D211" s="5"/>
       <c r="E211" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D212" s="5"/>
       <c r="E212" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C213" s="3">
         <v>100</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D214" s="5"/>
       <c r="E214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C216" s="3">
         <v>100</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D217" s="5"/>
       <c r="E217" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C219" s="3">
         <v>100</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D220" s="5"/>
       <c r="E220" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C221" s="3">
         <v>100</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="222" spans="4:5">
@@ -4780,502 +4783,502 @@
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C223" s="3">
         <v>1</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C224" s="3">
+        <v>100</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F224" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C224" s="3">
-        <v>100</v>
-      </c>
-      <c r="D224" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E224" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C225" s="3">
         <v>100</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="226" spans="2:6">
       <c r="B226" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D226" s="5"/>
       <c r="E226" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="227" spans="2:6">
       <c r="B227" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C227" s="3">
         <v>100</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D228" s="5"/>
       <c r="E228" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C231" s="3">
         <v>100</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C233" s="3">
         <v>100</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D234" s="5"/>
       <c r="E234" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C235" s="3">
         <v>100</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D236" s="5"/>
       <c r="E236" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C237" s="3">
         <v>100</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D238" s="5"/>
       <c r="E238" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D239" s="5"/>
       <c r="E239" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C240" s="3">
         <v>100</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D241" s="5"/>
       <c r="E241" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D242" s="5"/>
       <c r="E242" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C243" s="3">
         <v>100</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D244" s="5"/>
       <c r="E244" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C246" s="3">
         <v>100</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D247" s="5"/>
       <c r="E247" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D248" s="5"/>
       <c r="E248" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C249" s="3">
         <v>100</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D250" s="5"/>
       <c r="E250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C252" s="3">
         <v>100</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D253" s="5"/>
       <c r="E253" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D254" s="5"/>
       <c r="E254" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C255" s="3">
         <v>100</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D256" s="5"/>
       <c r="E256" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C257" s="3">
         <v>100</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="258" spans="4:5">
@@ -5286,502 +5289,502 @@
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C259" s="3">
         <v>1</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C260" s="3">
+        <v>100</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E260" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F260" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="C260" s="3">
-        <v>100</v>
-      </c>
-      <c r="D260" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E260" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C261" s="3">
         <v>100</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="262" spans="2:6">
       <c r="B262" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C263" s="3">
         <v>100</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D264" s="5"/>
       <c r="E264" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C267" s="3">
         <v>100</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C269" s="3">
         <v>100</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C271" s="3">
         <v>100</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C273" s="3">
         <v>100</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D275" s="5"/>
       <c r="E275" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C276" s="3">
         <v>100</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D277" s="5"/>
       <c r="E277" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D278" s="5"/>
       <c r="E278" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="279" spans="2:6">
       <c r="B279" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C279" s="3">
         <v>100</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D280" s="5"/>
       <c r="E280" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="282" spans="2:6">
       <c r="B282" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C282" s="3">
         <v>100</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D283" s="5"/>
       <c r="E283" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="285" spans="2:6">
       <c r="B285" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C285" s="3">
         <v>100</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D286" s="5"/>
       <c r="E286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="288" spans="2:6">
       <c r="B288" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C288" s="3">
         <v>100</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E288" s="3" t="s">
         <v>33</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D289" s="5"/>
       <c r="E289" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D290" s="5"/>
       <c r="E290" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C291" s="3">
         <v>100</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D292" s="5"/>
       <c r="E292" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C293" s="3">
         <v>100</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>48</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="294" spans="4:5">
@@ -5876,22 +5879,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5899,25 +5902,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5934,13 +5937,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5948,127 +5951,127 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="217">
   <si>
     <t>##var</t>
   </si>
@@ -110,10 +110,19 @@
     <t>4周</t>
   </si>
   <si>
+    <t>frag_3x1</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>frag_1x3</t>
+  </si>
+  <si>
     <t>frag_L1</t>
-  </si>
-  <si>
-    <t>10,60</t>
   </si>
   <si>
     <t>.X</t>
@@ -1636,7 +1645,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S312"/>
+  <dimension ref="A1:S316"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="3" customWidth="1"/>
@@ -1932,31 +1941,31 @@
         <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="5:5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3">
+        <v>700</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="E12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
-      <c r="B13" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="3">
-        <v>700</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>32</v>
-      </c>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="5:5">
       <c r="E13" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="5:5">
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="2:5">
@@ -1970,12 +1979,12 @@
         <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="5:5">
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:5">
@@ -1989,12 +1998,12 @@
         <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="5:5">
       <c r="E18" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:5">
@@ -2004,15 +2013,14 @@
       <c r="C19" s="3">
         <v>700</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>39</v>
+      <c r="D19" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5">
-      <c r="D20" s="5"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5">
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
@@ -2024,67 +2032,74 @@
       <c r="C21" s="3">
         <v>700</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>39</v>
+      <c r="D21" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="4:5">
-      <c r="D22" s="5"/>
+    <row r="22" spans="5:5">
       <c r="E22" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5">
-      <c r="D23" s="5"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3">
+        <v>700</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E23" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5">
-      <c r="B24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5">
+      <c r="D24" s="5"/>
+      <c r="E24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="3">
         <v>700</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5">
-      <c r="D25" s="5"/>
+      <c r="D25" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E25" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="4:5">
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5">
-      <c r="B27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5">
+      <c r="D27" s="5"/>
+      <c r="E27" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="3">
+        <v>700</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="3">
-        <v>700</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" spans="4:5">
-      <c r="D28" s="5"/>
       <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
@@ -2092,51 +2107,51 @@
     <row r="29" spans="4:5">
       <c r="D29" s="5"/>
       <c r="E29" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5">
-      <c r="B30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5">
+      <c r="D30" s="5"/>
+      <c r="E30" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="3">
         <v>700</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="4:5">
-      <c r="D31" s="5"/>
+      <c r="D31" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E31" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="4:5">
       <c r="D32" s="5"/>
       <c r="E32" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="4:5">
+      <c r="D33" s="5"/>
+      <c r="E33" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="3">
         <v>700</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="4:5">
-      <c r="D34" s="5"/>
+      <c r="D34" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E34" s="3" t="s">
         <v>26</v>
       </c>
@@ -2144,170 +2159,140 @@
     <row r="35" spans="4:5">
       <c r="D35" s="5"/>
       <c r="E35" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5">
-      <c r="B36" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C36" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="4:5">
+      <c r="D36" s="5"/>
+      <c r="E36" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="3">
         <v>700</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="4:5">
-      <c r="D37" s="5"/>
+      <c r="D37" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E37" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="4:5">
       <c r="D38" s="5"/>
       <c r="E38" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="4:5">
+      <c r="D39" s="5"/>
+      <c r="E39" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="3">
         <v>700</v>
       </c>
-      <c r="D39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="40" spans="4:5">
-      <c r="D40" s="5"/>
+      <c r="D40" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="E40" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="3">
-        <v>700</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>39</v>
-      </c>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="4:5">
+      <c r="D41" s="5"/>
       <c r="E41" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="4:5">
       <c r="D42" s="5"/>
       <c r="E42" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
       <c r="B43" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="3">
+        <v>700</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C43" s="3">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="s">
+    </row>
+    <row r="44" spans="4:5">
+      <c r="D44" s="5"/>
+      <c r="E44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="3" t="s">
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="3">
-        <v>100</v>
-      </c>
-      <c r="D44" s="5" t="s">
+      <c r="C45" s="3">
+        <v>700</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F44" s="3" t="str">
-        <f>IF(B44="","",$F$43)</f>
-        <v>m_cherry</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="3">
-        <v>100</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F45" s="3" t="str">
-        <f t="shared" ref="F45:F77" si="0">IF(B45="","",$F$43)</f>
-        <v>m_cherry</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="3" t="s">
-        <v>55</v>
-      </c>
+    </row>
+    <row r="46" spans="4:5">
       <c r="D46" s="5"/>
       <c r="E46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C47" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F47" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v>23</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="5"/>
+        <v>56</v>
+      </c>
+      <c r="C48" s="3">
+        <v>100</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E48" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F48" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f>IF(B48="","",$F$47)</f>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="49" spans="2:6">
@@ -2318,23 +2303,23 @@
         <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F49:F81" si="0">IF(B49="","",$F$47)</f>
         <v>m_cherry</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2343,16 +2328,16 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="3">
         <v>100</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2361,11 +2346,11 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2374,16 +2359,16 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C53" s="3">
         <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2392,11 +2377,11 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2405,16 +2390,16 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C55" s="3">
         <v>100</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2423,7 +2408,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="3" t="s">
@@ -2436,13 +2421,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C57" s="3">
         <v>100</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>26</v>
@@ -2454,11 +2439,11 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F58" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2467,55 +2452,60 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D59" s="5"/>
+        <v>63</v>
+      </c>
+      <c r="C59" s="3">
+        <v>100</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E59" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F59" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" s="3">
-        <v>100</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D60" s="5"/>
       <c r="E60" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F60" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D61" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="C61" s="3">
+        <v>100</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E61" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F61" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F62" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2524,42 +2514,42 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="3">
-        <v>100</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F63" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" s="5"/>
+        <v>65</v>
+      </c>
+      <c r="C64" s="3">
+        <v>100</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E64" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F64" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F65" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2568,42 +2558,42 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="3">
-        <v>100</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D66" s="5"/>
       <c r="E66" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F66" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D67" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="C67" s="3">
+        <v>100</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E67" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F67" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F68" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2612,42 +2602,42 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" s="3">
-        <v>100</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D69" s="5"/>
       <c r="E69" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F69" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D70" s="5"/>
+        <v>67</v>
+      </c>
+      <c r="C70" s="3">
+        <v>100</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F70" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F71" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2656,42 +2646,42 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C72" s="3">
-        <v>100</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D72" s="5"/>
       <c r="E72" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F72" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D73" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="C73" s="3">
+        <v>100</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E73" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F73" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F74" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2700,3110 +2690,3155 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C75" s="3">
-        <v>100</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D75" s="5"/>
       <c r="E75" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F75" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D76" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="C76" s="3">
+        <v>100</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E76" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F76" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C77" s="3">
-        <v>100</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D77" s="5"/>
       <c r="E77" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F77" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
-      </c>
-    </row>
-    <row r="78" spans="4:7">
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
+      <c r="B78" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D78" s="5"/>
       <c r="E78" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G78" s="3" t="str">
-        <f>IF(B78="","",B78&amp;"_cherry")</f>
+        <v>39</v>
+      </c>
+      <c r="F78" s="3" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C79" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+      <c r="F79" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C80" s="3">
-        <v>100</v>
-      </c>
-      <c r="D80" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D80" s="5"/>
+      <c r="E80" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>70</v>
+      <c r="F80" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" s="3">
         <v>100</v>
       </c>
       <c r="D81" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="F81" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="82" spans="4:7">
       <c r="D82" s="5"/>
       <c r="E82" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="G82" s="3" t="str">
+        <f>IF(B82="","",B82&amp;"_cherry")</f>
+        <v/>
       </c>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C83" s="3">
-        <v>100</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D84" s="5"/>
+        <v>74</v>
+      </c>
+      <c r="C84" s="3">
+        <v>100</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E84" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C87" s="3">
         <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C89" s="3">
         <v>100</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C91" s="3">
         <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C93" s="3">
         <v>100</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D95" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="C95" s="3">
+        <v>100</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E95" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C96" s="3">
-        <v>100</v>
-      </c>
-      <c r="D96" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D96" s="5"/>
       <c r="E96" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D97" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="C97" s="3">
+        <v>100</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E97" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C99" s="3">
-        <v>100</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D100" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="C100" s="3">
+        <v>100</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E100" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C102" s="3">
-        <v>100</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D103" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="C103" s="3">
+        <v>100</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E103" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C105" s="3">
-        <v>100</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D105" s="5"/>
       <c r="E105" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D106" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="C106" s="3">
+        <v>100</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E106" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C108" s="3">
-        <v>100</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D108" s="5"/>
       <c r="E108" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D109" s="5"/>
+        <v>85</v>
+      </c>
+      <c r="C109" s="3">
+        <v>100</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E109" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C111" s="3">
-        <v>100</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D111" s="5"/>
       <c r="E111" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D112" s="5"/>
+        <v>86</v>
+      </c>
+      <c r="C112" s="3">
+        <v>100</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E112" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C113" s="3">
-        <v>100</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D113" s="5"/>
       <c r="E113" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="114" spans="2:6">
+      <c r="B114" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C115" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C116" s="3">
-        <v>100</v>
-      </c>
-      <c r="D116" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D116" s="5"/>
+      <c r="E116" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="F116" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C117" s="3">
         <v>100</v>
       </c>
       <c r="D117" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E117" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F117" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="118" spans="2:6">
-      <c r="B118" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="118" spans="4:5">
       <c r="D118" s="5"/>
       <c r="E118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C119" s="3">
+        <v>1</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="C119" s="3">
-        <v>100</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D120" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="C120" s="3">
+        <v>100</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E120" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C123" s="3">
         <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C125" s="3">
         <v>100</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C127" s="3">
         <v>100</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C129" s="3">
         <v>100</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D131" s="5"/>
+        <v>97</v>
+      </c>
+      <c r="C131" s="3">
+        <v>100</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E131" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C132" s="3">
-        <v>100</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D132" s="5"/>
       <c r="E132" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D133" s="5"/>
+        <v>98</v>
+      </c>
+      <c r="C133" s="3">
+        <v>100</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E133" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="135" spans="2:6">
       <c r="B135" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C135" s="3">
-        <v>100</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D136" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="C136" s="3">
+        <v>100</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E136" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="138" spans="2:6">
       <c r="B138" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C138" s="3">
-        <v>100</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D139" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="C139" s="3">
+        <v>100</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E139" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="141" spans="2:6">
       <c r="B141" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C141" s="3">
-        <v>100</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D142" s="5"/>
+        <v>101</v>
+      </c>
+      <c r="C142" s="3">
+        <v>100</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E142" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144" spans="2:6">
       <c r="B144" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C144" s="3">
-        <v>100</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D144" s="5"/>
       <c r="E144" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D145" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="C145" s="3">
+        <v>100</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E145" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C147" s="3">
-        <v>100</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D147" s="5"/>
       <c r="E147" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D148" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="C148" s="3">
+        <v>100</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E148" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C149" s="3">
-        <v>100</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D149" s="5"/>
       <c r="E149" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="150" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C151" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C152" s="3">
-        <v>100</v>
-      </c>
-      <c r="D152" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D152" s="5"/>
+      <c r="E152" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E152" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="F152" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C153" s="3">
         <v>100</v>
       </c>
       <c r="D153" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E153" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E153" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F153" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="154" spans="2:6">
-      <c r="B154" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="154" spans="4:5">
       <c r="D154" s="5"/>
       <c r="E154" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F154" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C155" s="3">
+        <v>1</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F155" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="C155" s="3">
-        <v>100</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D156" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="C156" s="3">
+        <v>100</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E156" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C159" s="3">
         <v>100</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C161" s="3">
         <v>100</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C163" s="3">
         <v>100</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C165" s="3">
         <v>100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D167" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="C167" s="3">
+        <v>100</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E167" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C168" s="3">
-        <v>100</v>
-      </c>
-      <c r="D168" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D168" s="5"/>
       <c r="E168" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D169" s="5"/>
+        <v>115</v>
+      </c>
+      <c r="C169" s="3">
+        <v>100</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E169" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="171" spans="2:6">
       <c r="B171" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C171" s="3">
-        <v>100</v>
-      </c>
-      <c r="D171" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D172" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="C172" s="3">
+        <v>100</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E172" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="174" spans="2:6">
       <c r="B174" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C174" s="3">
-        <v>100</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D175" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="C175" s="3">
+        <v>100</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E175" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="177" spans="2:6">
       <c r="B177" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C177" s="3">
-        <v>100</v>
-      </c>
-      <c r="D177" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D178" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="C178" s="3">
+        <v>100</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E178" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C180" s="3">
-        <v>100</v>
-      </c>
-      <c r="D180" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D180" s="5"/>
       <c r="E180" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D181" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="C181" s="3">
+        <v>100</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E181" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="183" spans="2:6">
       <c r="B183" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C183" s="3">
-        <v>100</v>
-      </c>
-      <c r="D183" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D184" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="C184" s="3">
+        <v>100</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E184" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C185" s="3">
-        <v>100</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D185" s="5"/>
       <c r="E185" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="186" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="186" spans="2:6">
+      <c r="B186" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C187" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C188" s="3">
-        <v>100</v>
-      </c>
-      <c r="D188" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D188" s="5"/>
+      <c r="E188" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E188" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="F188" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C189" s="3">
         <v>100</v>
       </c>
       <c r="D189" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E189" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E189" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F189" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="190" spans="2:6">
-      <c r="B190" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="190" spans="4:5">
       <c r="D190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C191" s="3">
+        <v>1</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F191" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="C191" s="3">
-        <v>100</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D192" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="C192" s="3">
+        <v>100</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E192" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C195" s="3">
         <v>100</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C197" s="3">
         <v>100</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C199" s="3">
         <v>100</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C201" s="3">
         <v>100</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D203" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="C203" s="3">
+        <v>100</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E203" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C204" s="3">
-        <v>100</v>
-      </c>
-      <c r="D204" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D204" s="5"/>
       <c r="E204" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D205" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="C205" s="3">
+        <v>100</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E205" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="B207" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C207" s="3">
-        <v>100</v>
-      </c>
-      <c r="D207" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D208" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="C208" s="3">
+        <v>100</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E208" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C210" s="3">
-        <v>100</v>
-      </c>
-      <c r="D210" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D211" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="C211" s="3">
+        <v>100</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E211" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D212" s="5"/>
       <c r="E212" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C213" s="3">
-        <v>100</v>
-      </c>
-      <c r="D213" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D214" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="C214" s="3">
+        <v>100</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C216" s="3">
-        <v>100</v>
-      </c>
-      <c r="D216" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D216" s="5"/>
       <c r="E216" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D217" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="C217" s="3">
+        <v>100</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E217" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C219" s="3">
-        <v>100</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D220" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="C220" s="3">
+        <v>100</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E220" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>55</v>
+        <v>124</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C221" s="3">
-        <v>100</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D221" s="5"/>
       <c r="E221" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="222" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="222" spans="2:6">
+      <c r="B222" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D222" s="5"/>
       <c r="E222" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C223" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C224" s="3">
-        <v>100</v>
-      </c>
-      <c r="D224" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D224" s="5"/>
+      <c r="E224" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E224" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="F224" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C225" s="3">
         <v>100</v>
       </c>
       <c r="D225" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E225" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E225" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F225" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="226" spans="2:6">
-      <c r="B226" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="226" spans="4:5">
       <c r="D226" s="5"/>
       <c r="E226" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="227" spans="2:6">
       <c r="B227" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C227" s="3">
+        <v>1</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F227" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="C227" s="3">
-        <v>100</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D228" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="C228" s="3">
+        <v>100</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E228" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C231" s="3">
         <v>100</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C233" s="3">
         <v>100</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D234" s="5"/>
       <c r="E234" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C235" s="3">
         <v>100</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D236" s="5"/>
       <c r="E236" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C237" s="3">
         <v>100</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D238" s="5"/>
       <c r="E238" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D239" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="C239" s="3">
+        <v>100</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E239" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C240" s="3">
-        <v>100</v>
-      </c>
-      <c r="D240" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D240" s="5"/>
       <c r="E240" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D241" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="C241" s="3">
+        <v>100</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E241" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D242" s="5"/>
       <c r="E242" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C243" s="3">
-        <v>100</v>
-      </c>
-      <c r="D243" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D243" s="5"/>
       <c r="E243" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D244" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="C244" s="3">
+        <v>100</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E244" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C246" s="3">
-        <v>100</v>
-      </c>
-      <c r="D246" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D247" s="5"/>
+        <v>151</v>
+      </c>
+      <c r="C247" s="3">
+        <v>100</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E247" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D248" s="5"/>
       <c r="E248" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C249" s="3">
-        <v>100</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D250" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="C250" s="3">
+        <v>100</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C252" s="3">
-        <v>100</v>
-      </c>
-      <c r="D252" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D252" s="5"/>
       <c r="E252" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D253" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="C253" s="3">
+        <v>100</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E253" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D254" s="5"/>
       <c r="E254" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C255" s="3">
-        <v>100</v>
-      </c>
-      <c r="D255" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D256" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="C256" s="3">
+        <v>100</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E256" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C257" s="3">
-        <v>100</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D257" s="5"/>
       <c r="E257" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="258" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="258" spans="2:6">
+      <c r="B258" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C259" s="3">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C260" s="3">
-        <v>100</v>
-      </c>
-      <c r="D260" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D260" s="5"/>
+      <c r="E260" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E260" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="F260" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C261" s="3">
         <v>100</v>
       </c>
       <c r="D261" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E261" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="F261" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="262" spans="2:6">
-      <c r="B262" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="262" spans="4:5">
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C263" s="3">
+        <v>1</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E263" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F263" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C263" s="3">
-        <v>100</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E263" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F263" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D264" s="5"/>
+        <v>159</v>
+      </c>
+      <c r="C264" s="3">
+        <v>100</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E264" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C267" s="3">
         <v>100</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C269" s="3">
         <v>100</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C271" s="3">
         <v>100</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C273" s="3">
         <v>100</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D275" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="C275" s="3">
+        <v>100</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E275" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C276" s="3">
-        <v>100</v>
-      </c>
-      <c r="D276" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D276" s="5"/>
       <c r="E276" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D277" s="5"/>
+        <v>166</v>
+      </c>
+      <c r="C277" s="3">
+        <v>100</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E277" s="3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D278" s="5"/>
       <c r="E278" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="279" spans="2:6">
       <c r="B279" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C279" s="3">
-        <v>100</v>
-      </c>
-      <c r="D279" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D279" s="5"/>
       <c r="E279" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D280" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="C280" s="3">
+        <v>100</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E280" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="282" spans="2:6">
       <c r="B282" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C282" s="3">
-        <v>100</v>
-      </c>
-      <c r="D282" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D282" s="5"/>
       <c r="E282" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D283" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="C283" s="3">
+        <v>100</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E283" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285" spans="2:6">
       <c r="B285" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C285" s="3">
-        <v>100</v>
-      </c>
-      <c r="D285" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D286" s="5"/>
+        <v>169</v>
+      </c>
+      <c r="C286" s="3">
+        <v>100</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="288" spans="2:6">
       <c r="B288" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C288" s="3">
-        <v>100</v>
-      </c>
-      <c r="D288" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D288" s="5"/>
       <c r="E288" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D289" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="C289" s="3">
+        <v>100</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E289" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D290" s="5"/>
       <c r="E290" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C291" s="3">
-        <v>100</v>
-      </c>
-      <c r="D291" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D292" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="C292" s="3">
+        <v>100</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="E292" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C293" s="3">
-        <v>100</v>
-      </c>
-      <c r="D293" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D293" s="5"/>
       <c r="E293" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="294" spans="4:5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="294" spans="2:6">
+      <c r="B294" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="295" spans="4:4">
-      <c r="D295" s="5"/>
-    </row>
-    <row r="296" spans="4:4">
+        <v>39</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="295" spans="2:6">
+      <c r="B295" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C295" s="3">
+        <v>100</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E295" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="296" spans="2:6">
+      <c r="B296" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="D296" s="5"/>
-    </row>
-    <row r="297" spans="4:4">
-      <c r="D297" s="5"/>
-    </row>
-    <row r="298" spans="4:4">
+      <c r="E296" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="297" spans="2:6">
+      <c r="B297" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C297" s="3">
+        <v>100</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E297" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="298" spans="4:5">
       <c r="D298" s="5"/>
+      <c r="E298" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="299" spans="4:4">
       <c r="D299" s="5"/>
@@ -5846,6 +5881,18 @@
     </row>
     <row r="312" spans="4:4">
       <c r="D312" s="5"/>
+    </row>
+    <row r="313" spans="4:4">
+      <c r="D313" s="5"/>
+    </row>
+    <row r="314" spans="4:4">
+      <c r="D314" s="5"/>
+    </row>
+    <row r="315" spans="4:4">
+      <c r="D315" s="5"/>
+    </row>
+    <row r="316" spans="4:4">
+      <c r="D316" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5879,22 +5926,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5902,25 +5949,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5937,13 +5984,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5951,127 +5998,127 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15440"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="216">
   <si>
     <t>##var</t>
   </si>
@@ -68,13 +68,13 @@
     <t>list,string</t>
   </si>
   <si>
-    <t>gut_3x4</t>
+    <t>gut_3x3</t>
   </si>
   <si>
     <t>0,0</t>
   </si>
   <si>
-    <t>XXXX</t>
+    <t>XXX</t>
   </si>
   <si>
     <t>0周</t>
@@ -114,9 +114,6 @@
   </si>
   <si>
     <t>10,60</t>
-  </si>
-  <si>
-    <t>XXX</t>
   </si>
   <si>
     <t>frag_1x3</t>
@@ -1941,12 +1938,12 @@
         <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="3">
         <v>700</v>
@@ -1970,7 +1967,7 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3">
         <v>700</v>
@@ -1984,12 +1981,12 @@
     </row>
     <row r="16" spans="5:5">
       <c r="E16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3">
         <v>700</v>
@@ -1998,7 +1995,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="5:5">
@@ -2008,7 +2005,7 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3">
         <v>700</v>
@@ -2017,7 +2014,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="5:5">
@@ -2027,7 +2024,7 @@
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3">
         <v>700</v>
@@ -2041,18 +2038,18 @@
     </row>
     <row r="22" spans="5:5">
       <c r="E22" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3">
         <v>700</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
@@ -2066,13 +2063,13 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3">
         <v>700</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
@@ -2081,33 +2078,33 @@
     <row r="26" spans="4:5">
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="4:5">
       <c r="D27" s="5"/>
       <c r="E27" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3">
         <v>700</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="4:5">
       <c r="D29" s="5"/>
       <c r="E29" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="4:5">
@@ -2118,22 +2115,22 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3">
         <v>700</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="4:5">
       <c r="D32" s="5"/>
       <c r="E32" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="4:5">
@@ -2144,13 +2141,13 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="3">
         <v>700</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>26</v>
@@ -2159,27 +2156,27 @@
     <row r="35" spans="4:5">
       <c r="D35" s="5"/>
       <c r="E35" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="4:5">
       <c r="D36" s="5"/>
       <c r="E36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3">
         <v>700</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="4:5">
@@ -2191,21 +2188,21 @@
     <row r="39" spans="4:5">
       <c r="D39" s="5"/>
       <c r="E39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="3">
         <v>700</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="4:5">
@@ -2217,75 +2214,75 @@
     <row r="42" spans="4:5">
       <c r="D42" s="5"/>
       <c r="E42" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="3">
         <v>700</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="4:5">
       <c r="D44" s="5"/>
       <c r="E44" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="3">
         <v>700</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="4:5">
       <c r="D46" s="5"/>
       <c r="E46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C48" s="3">
         <v>100</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>26</v>
@@ -2297,13 +2294,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C49" s="3">
         <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>23</v>
@@ -2315,7 +2312,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="3" t="s">
@@ -2328,13 +2325,13 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51" s="3">
         <v>100</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>26</v>
@@ -2346,11 +2343,11 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2359,16 +2356,16 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="3">
         <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2377,7 +2374,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
@@ -2390,16 +2387,16 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C55" s="3">
         <v>100</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2408,7 +2405,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="3" t="s">
@@ -2421,13 +2418,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3">
         <v>100</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>26</v>
@@ -2439,11 +2436,11 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2452,13 +2449,13 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="3">
         <v>100</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>26</v>
@@ -2470,7 +2467,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="3" t="s">
@@ -2483,13 +2480,13 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" s="3">
         <v>100</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>26</v>
@@ -2501,11 +2498,11 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2514,11 +2511,11 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F63" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2527,16 +2524,16 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C64" s="3">
         <v>100</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F64" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2545,11 +2542,11 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2558,7 +2555,7 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="3" t="s">
@@ -2571,16 +2568,16 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C67" s="3">
         <v>100</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F67" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2589,11 +2586,11 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F68" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2602,7 +2599,7 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="3" t="s">
@@ -2615,13 +2612,13 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C70" s="3">
         <v>100</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>26</v>
@@ -2633,11 +2630,11 @@
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F71" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2646,11 +2643,11 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F72" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2659,16 +2656,16 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" s="3">
         <v>100</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F73" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2677,7 +2674,7 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="3" t="s">
@@ -2690,11 +2687,11 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F75" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2703,16 +2700,16 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C76" s="3">
         <v>100</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F76" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2721,7 +2718,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="3" t="s">
@@ -2734,11 +2731,11 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F78" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2747,16 +2744,16 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C79" s="3">
         <v>100</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F79" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2765,11 +2762,11 @@
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F80" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2778,16 +2775,16 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C81" s="3">
         <v>100</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F81" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2797,7 +2794,7 @@
     <row r="82" spans="4:7">
       <c r="D82" s="5"/>
       <c r="E82" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G82" s="3" t="str">
         <f>IF(B82="","",B82&amp;"_cherry")</f>
@@ -2806,3038 +2803,3038 @@
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C84" s="3">
         <v>100</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C87" s="3">
         <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C89" s="3">
         <v>100</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C91" s="3">
         <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C93" s="3">
         <v>100</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C95" s="3">
         <v>100</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C97" s="3">
         <v>100</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C100" s="3">
         <v>100</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C103" s="3">
         <v>100</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C106" s="3">
         <v>100</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C109" s="3">
         <v>100</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C112" s="3">
         <v>100</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C115" s="3">
         <v>100</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C117" s="3">
         <v>100</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="118" spans="4:5">
       <c r="D118" s="5"/>
       <c r="E118" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C119" s="3">
         <v>1</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C120" s="3">
         <v>100</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C123" s="3">
         <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C125" s="3">
         <v>100</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C127" s="3">
         <v>100</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C129" s="3">
         <v>100</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C131" s="3">
         <v>100</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D132" s="5"/>
       <c r="E132" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C133" s="3">
         <v>100</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="135" spans="2:6">
       <c r="B135" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C136" s="3">
         <v>100</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="138" spans="2:6">
       <c r="B138" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C139" s="3">
         <v>100</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="141" spans="2:6">
       <c r="B141" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C142" s="3">
         <v>100</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144" spans="2:6">
       <c r="B144" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C145" s="3">
         <v>100</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C148" s="3">
         <v>100</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150" spans="2:6">
       <c r="B150" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C151" s="3">
         <v>100</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D152" s="5"/>
       <c r="E152" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C153" s="3">
         <v>100</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="154" spans="4:5">
       <c r="D154" s="5"/>
       <c r="E154" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C156" s="3">
         <v>100</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C159" s="3">
         <v>100</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C161" s="3">
         <v>100</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C163" s="3">
         <v>100</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C165" s="3">
         <v>100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C167" s="3">
         <v>100</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D168" s="5"/>
       <c r="E168" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C169" s="3">
         <v>100</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171" spans="2:6">
       <c r="B171" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C172" s="3">
         <v>100</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="174" spans="2:6">
       <c r="B174" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C175" s="3">
         <v>100</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="177" spans="2:6">
       <c r="B177" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C178" s="3">
         <v>100</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D180" s="5"/>
       <c r="E180" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C181" s="3">
         <v>100</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="183" spans="2:6">
       <c r="B183" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C184" s="3">
         <v>100</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D185" s="5"/>
       <c r="E185" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="186" spans="2:6">
       <c r="B186" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C187" s="3">
         <v>100</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D188" s="5"/>
       <c r="E188" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C189" s="3">
         <v>100</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="190" spans="4:5">
       <c r="D190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C191" s="3">
         <v>1</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C192" s="3">
         <v>100</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C195" s="3">
         <v>100</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C197" s="3">
         <v>100</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C199" s="3">
         <v>100</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C201" s="3">
         <v>100</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C203" s="3">
         <v>100</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D204" s="5"/>
       <c r="E204" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C205" s="3">
         <v>100</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="B207" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C208" s="3">
         <v>100</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C211" s="3">
         <v>100</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D212" s="5"/>
       <c r="E212" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C214" s="3">
         <v>100</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D216" s="5"/>
       <c r="E216" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C217" s="3">
         <v>100</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C220" s="3">
         <v>100</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D221" s="5"/>
       <c r="E221" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="222" spans="2:6">
       <c r="B222" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D222" s="5"/>
       <c r="E222" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C223" s="3">
         <v>100</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D224" s="5"/>
       <c r="E224" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C225" s="3">
         <v>100</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="226" spans="4:5">
       <c r="D226" s="5"/>
       <c r="E226" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="227" spans="2:6">
       <c r="B227" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C227" s="3">
         <v>1</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C228" s="3">
         <v>100</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C231" s="3">
         <v>100</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C233" s="3">
         <v>100</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D234" s="5"/>
       <c r="E234" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C235" s="3">
         <v>100</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D236" s="5"/>
       <c r="E236" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C237" s="3">
         <v>100</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D238" s="5"/>
       <c r="E238" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C239" s="3">
         <v>100</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D240" s="5"/>
       <c r="E240" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C241" s="3">
         <v>100</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D242" s="5"/>
       <c r="E242" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D243" s="5"/>
       <c r="E243" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C244" s="3">
         <v>100</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C247" s="3">
         <v>100</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D248" s="5"/>
       <c r="E248" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C250" s="3">
         <v>100</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D252" s="5"/>
       <c r="E252" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C253" s="3">
         <v>100</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D254" s="5"/>
       <c r="E254" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C256" s="3">
         <v>100</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D257" s="5"/>
       <c r="E257" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="258" spans="2:6">
       <c r="B258" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C259" s="3">
         <v>100</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D260" s="5"/>
       <c r="E260" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C261" s="3">
         <v>100</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="262" spans="4:5">
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C263" s="3">
         <v>1</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C264" s="3">
         <v>100</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C267" s="3">
         <v>100</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C269" s="3">
         <v>100</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C271" s="3">
         <v>100</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C273" s="3">
         <v>100</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C275" s="3">
         <v>100</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D276" s="5"/>
       <c r="E276" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C277" s="3">
         <v>100</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D278" s="5"/>
       <c r="E278" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="279" spans="2:6">
       <c r="B279" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C280" s="3">
         <v>100</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="282" spans="2:6">
       <c r="B282" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D282" s="5"/>
       <c r="E282" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C283" s="3">
         <v>100</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="285" spans="2:6">
       <c r="B285" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C286" s="3">
         <v>100</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="288" spans="2:6">
       <c r="B288" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D288" s="5"/>
       <c r="E288" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C289" s="3">
         <v>100</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D290" s="5"/>
       <c r="E290" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C292" s="3">
         <v>100</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D293" s="5"/>
       <c r="E293" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="294" spans="2:6">
       <c r="B294" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="295" spans="2:6">
       <c r="B295" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C295" s="3">
         <v>100</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="296" spans="2:6">
       <c r="B296" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D296" s="5"/>
       <c r="E296" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="297" spans="2:6">
       <c r="B297" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C297" s="3">
         <v>100</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="298" spans="4:5">
       <c r="D298" s="5"/>
       <c r="E298" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="299" spans="4:4">
@@ -5926,22 +5923,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5949,25 +5946,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5984,13 +5981,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5998,127 +5995,127 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15440"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="238">
   <si>
     <t>##var</t>
   </si>
@@ -134,33 +134,96 @@
     <t>X.</t>
   </si>
   <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>强化类主动道具</t>
+  </si>
+  <si>
+    <t>recipe</t>
+  </si>
+  <si>
     <t>frag_L4</t>
   </si>
   <si>
+    <t>调整类主动道具</t>
+  </si>
+  <si>
+    <t>被动道具</t>
+  </si>
+  <si>
     <t>frag_2x2</t>
   </si>
   <si>
     <t>30,100</t>
   </si>
   <si>
+    <t>事件</t>
+  </si>
+  <si>
+    <t>奖励</t>
+  </si>
+  <si>
     <t>frag_L5</t>
   </si>
   <si>
+    <t>商店</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
     <t>frag_L6</t>
   </si>
   <si>
     <t>frag_L7</t>
   </si>
   <si>
+    <t>❤️❤️❤️</t>
+  </si>
+  <si>
+    <t>普通事件</t>
+  </si>
+  <si>
     <t>frag_L8</t>
   </si>
   <si>
+    <t>强化类主动道具n选1</t>
+  </si>
+  <si>
+    <t>调整类主动道具n选1</t>
+  </si>
+  <si>
     <t>frag_S1</t>
   </si>
   <si>
+    <t>事件（有好有坏）</t>
+  </si>
+  <si>
+    <t>节点事件</t>
+  </si>
+  <si>
+    <t>奖励（好事件）</t>
+  </si>
+  <si>
     <t>frag_S2</t>
   </si>
   <si>
+    <t>厄运（坏事件）</t>
+  </si>
+  <si>
+    <t>利息事件</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>恢复血量</t>
+  </si>
+  <si>
     <t>frag_S3</t>
   </si>
   <si>
@@ -168,6 +231,9 @@
   </si>
   <si>
     <t>XX.</t>
+  </si>
+  <si>
+    <t>抽奖机</t>
   </si>
   <si>
     <t>frag_S4</t>
@@ -831,12 +897,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1155,7 +1233,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -1179,16 +1257,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -1197,89 +1275,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1294,6 +1372,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1642,7 +1726,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S316"/>
+  <dimension ref="A1:W316"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="3" customWidth="1"/>
@@ -1655,7 +1739,7 @@
     <col min="8" max="12" width="9" style="3"/>
     <col min="13" max="13" width="12.9230769230769" style="3"/>
     <col min="14" max="20" width="9" style="3"/>
-    <col min="21" max="21" width="12.2307692307692" style="3" customWidth="1"/>
+    <col min="21" max="21" width="23.6923076923077" style="3" customWidth="1"/>
     <col min="22" max="22" width="9" style="3"/>
     <col min="23" max="23" width="43.3846153846154" style="3" customWidth="1"/>
     <col min="24" max="16384" width="9" style="3"/>
@@ -2003,7 +2087,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:5">
+    <row r="19" spans="2:21">
       <c r="B19" s="3" t="s">
         <v>37</v>
       </c>
@@ -2016,15 +2100,24 @@
       <c r="E19" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" spans="5:5">
+      <c r="U19" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="5:23">
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="21" spans="2:5">
+      <c r="U20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21">
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3">
         <v>700</v>
@@ -2035,67 +2128,88 @@
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="5:5">
+      <c r="U21" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="5:21">
       <c r="E22" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="23" spans="2:5">
+      <c r="U22" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21">
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C23" s="3">
         <v>700</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="24" spans="4:5">
+      <c r="U23" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="4:21">
       <c r="D24" s="5"/>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="2:5">
+      <c r="U24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21">
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C25" s="3">
         <v>700</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="4:5">
+      <c r="U25" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="4:21">
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="27" spans="4:5">
+      <c r="U26" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="4:21">
       <c r="D27" s="5"/>
       <c r="E27" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="U27" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C28" s="3">
         <v>700</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>35</v>
@@ -2115,68 +2229,93 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3">
         <v>700</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="4:5">
+    <row r="32" spans="4:23">
       <c r="D32" s="5"/>
       <c r="E32" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" spans="4:5">
+      <c r="W32" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="4:21">
       <c r="D33" s="5"/>
       <c r="E33" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="2:5">
+      <c r="T33" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21">
       <c r="B34" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C34" s="3">
         <v>700</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="4:5">
+      <c r="T34" s="6"/>
+      <c r="U34" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="4:21">
       <c r="D35" s="5"/>
       <c r="E35" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="36" spans="4:5">
+      <c r="T35" s="6"/>
+      <c r="U35" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36" spans="4:21">
       <c r="D36" s="5"/>
       <c r="E36" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="37" spans="2:5">
+      <c r="T36" s="6"/>
+      <c r="U36" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21">
       <c r="B37" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="C37" s="3">
         <v>700</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>38</v>
+      </c>
+      <c r="T37" s="6"/>
+      <c r="U37" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="4:5">
@@ -2185,104 +2324,133 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="4:5">
+    <row r="39" spans="4:21">
       <c r="D39" s="5"/>
       <c r="E39" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="2:5">
+      <c r="T39" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="U39" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="2:21">
       <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C40" s="3">
         <v>700</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="4:5">
+      <c r="T40" s="7"/>
+      <c r="U40" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="4:21">
       <c r="D41" s="5"/>
       <c r="E41" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="42" spans="4:5">
+      <c r="T41" s="7"/>
+      <c r="U41" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="4:23">
       <c r="D42" s="5"/>
       <c r="E42" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="43" spans="2:5">
+      <c r="T42" s="7"/>
+      <c r="U42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21">
       <c r="B43" s="3" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C43" s="3">
         <v>700</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="4:5">
+        <v>70</v>
+      </c>
+      <c r="T43" s="7"/>
+      <c r="U43" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="4:21">
       <c r="D44" s="5"/>
       <c r="E44" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
+      </c>
+      <c r="T44" s="7"/>
+      <c r="U44" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C45" s="3">
         <v>700</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="4:5">
       <c r="D46" s="5"/>
       <c r="E46" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C48" s="3">
         <v>100</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>26</v>
@@ -2294,13 +2462,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3">
         <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>23</v>
@@ -2312,7 +2480,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="3" t="s">
@@ -2325,13 +2493,13 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C51" s="3">
         <v>100</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>26</v>
@@ -2343,7 +2511,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
@@ -2356,13 +2524,13 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C53" s="3">
         <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>35</v>
@@ -2374,7 +2542,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
@@ -2387,13 +2555,13 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="3" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C55" s="3">
         <v>100</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>38</v>
@@ -2405,7 +2573,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="3" t="s">
@@ -2418,13 +2586,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="3" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C57" s="3">
         <v>100</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>26</v>
@@ -2436,7 +2604,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
@@ -2449,13 +2617,13 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C59" s="3">
         <v>100</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>26</v>
@@ -2467,7 +2635,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="3" t="s">
@@ -2480,13 +2648,13 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C61" s="3">
         <v>100</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>26</v>
@@ -2498,7 +2666,7 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="3" t="s">
@@ -2511,7 +2679,7 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
@@ -2524,13 +2692,13 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64" s="3">
         <v>100</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>35</v>
@@ -2542,7 +2710,7 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
@@ -2555,7 +2723,7 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="3" t="s">
@@ -2568,13 +2736,13 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C67" s="3">
         <v>100</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>38</v>
@@ -2586,7 +2754,7 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="3" t="s">
@@ -2599,7 +2767,7 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="3" t="s">
@@ -2612,13 +2780,13 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C70" s="3">
         <v>100</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>26</v>
@@ -2630,7 +2798,7 @@
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
@@ -2643,7 +2811,7 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="3" t="s">
@@ -2656,13 +2824,13 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C73" s="3">
         <v>100</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>38</v>
@@ -2674,7 +2842,7 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="3" t="s">
@@ -2687,7 +2855,7 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="3" t="s">
@@ -2700,13 +2868,13 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C76" s="3">
         <v>100</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>35</v>
@@ -2718,7 +2886,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="3" t="s">
@@ -2731,7 +2899,7 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="3" t="s">
@@ -2744,16 +2912,16 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C79" s="3">
         <v>100</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F79" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2762,11 +2930,11 @@
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F80" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2775,16 +2943,16 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C81" s="3">
         <v>100</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F81" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2794,7 +2962,7 @@
     <row r="82" spans="4:7">
       <c r="D82" s="5"/>
       <c r="E82" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G82" s="3" t="str">
         <f>IF(B82="","",B82&amp;"_cherry")</f>
@@ -2803,3038 +2971,3038 @@
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C84" s="3">
         <v>100</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C87" s="3">
         <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C89" s="3">
         <v>100</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C91" s="3">
         <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C93" s="3">
         <v>100</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C95" s="3">
         <v>100</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C97" s="3">
         <v>100</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C100" s="3">
         <v>100</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C103" s="3">
         <v>100</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C106" s="3">
         <v>100</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C109" s="3">
         <v>100</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C112" s="3">
         <v>100</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C115" s="3">
         <v>100</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C117" s="3">
         <v>100</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="118" spans="4:5">
       <c r="D118" s="5"/>
       <c r="E118" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="3" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C119" s="3">
         <v>1</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C120" s="3">
         <v>100</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C123" s="3">
         <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C125" s="3">
         <v>100</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C127" s="3">
         <v>100</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C129" s="3">
         <v>100</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C131" s="3">
         <v>100</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D132" s="5"/>
       <c r="E132" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C133" s="3">
         <v>100</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="135" spans="2:6">
       <c r="B135" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C136" s="3">
         <v>100</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="2:6">
       <c r="B138" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C139" s="3">
         <v>100</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="2:6">
       <c r="B141" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C142" s="3">
         <v>100</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="144" spans="2:6">
       <c r="B144" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C145" s="3">
         <v>100</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C148" s="3">
         <v>100</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" spans="2:6">
       <c r="B150" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C151" s="3">
         <v>100</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D152" s="5"/>
       <c r="E152" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C153" s="3">
         <v>100</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
     </row>
     <row r="154" spans="4:5">
       <c r="D154" s="5"/>
       <c r="E154" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="3" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C156" s="3">
         <v>100</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C159" s="3">
         <v>100</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C161" s="3">
         <v>100</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C163" s="3">
         <v>100</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C165" s="3">
         <v>100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C167" s="3">
         <v>100</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D168" s="5"/>
       <c r="E168" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C169" s="3">
         <v>100</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171" spans="2:6">
       <c r="B171" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C172" s="3">
         <v>100</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="2:6">
       <c r="B174" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C175" s="3">
         <v>100</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="177" spans="2:6">
       <c r="B177" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C178" s="3">
         <v>100</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D180" s="5"/>
       <c r="E180" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C181" s="3">
         <v>100</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183" spans="2:6">
       <c r="B183" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C184" s="3">
         <v>100</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D185" s="5"/>
       <c r="E185" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="186" spans="2:6">
       <c r="B186" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C187" s="3">
         <v>100</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D188" s="5"/>
       <c r="E188" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C189" s="3">
         <v>100</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="190" spans="4:5">
       <c r="D190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="3" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C191" s="3">
         <v>1</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C192" s="3">
         <v>100</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C195" s="3">
         <v>100</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C197" s="3">
         <v>100</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C199" s="3">
         <v>100</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C201" s="3">
         <v>100</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C203" s="3">
         <v>100</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D204" s="5"/>
       <c r="E204" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C205" s="3">
         <v>100</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="B207" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C208" s="3">
         <v>100</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C211" s="3">
         <v>100</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D212" s="5"/>
       <c r="E212" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C214" s="3">
         <v>100</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D216" s="5"/>
       <c r="E216" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C217" s="3">
         <v>100</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C220" s="3">
         <v>100</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D221" s="5"/>
       <c r="E221" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="222" spans="2:6">
       <c r="B222" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D222" s="5"/>
       <c r="E222" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C223" s="3">
         <v>100</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D224" s="5"/>
       <c r="E224" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C225" s="3">
         <v>100</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="226" spans="4:5">
       <c r="D226" s="5"/>
       <c r="E226" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="227" spans="2:6">
       <c r="B227" s="3" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C227" s="3">
         <v>1</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C228" s="3">
         <v>100</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C231" s="3">
         <v>100</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C233" s="3">
         <v>100</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D234" s="5"/>
       <c r="E234" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C235" s="3">
         <v>100</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D236" s="5"/>
       <c r="E236" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C237" s="3">
         <v>100</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D238" s="5"/>
       <c r="E238" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C239" s="3">
         <v>100</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D240" s="5"/>
       <c r="E240" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C241" s="3">
         <v>100</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D242" s="5"/>
       <c r="E242" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D243" s="5"/>
       <c r="E243" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C244" s="3">
         <v>100</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C247" s="3">
         <v>100</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D248" s="5"/>
       <c r="E248" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C250" s="3">
         <v>100</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D252" s="5"/>
       <c r="E252" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C253" s="3">
         <v>100</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D254" s="5"/>
       <c r="E254" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C256" s="3">
         <v>100</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D257" s="5"/>
       <c r="E257" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="258" spans="2:6">
       <c r="B258" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C259" s="3">
         <v>100</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D260" s="5"/>
       <c r="E260" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C261" s="3">
         <v>100</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
     </row>
     <row r="262" spans="4:5">
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C263" s="3">
         <v>1</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C264" s="3">
         <v>100</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C267" s="3">
         <v>100</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C269" s="3">
         <v>100</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C271" s="3">
         <v>100</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C273" s="3">
         <v>100</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C275" s="3">
         <v>100</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D276" s="5"/>
       <c r="E276" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C277" s="3">
         <v>100</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D278" s="5"/>
       <c r="E278" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="279" spans="2:6">
       <c r="B279" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C280" s="3">
         <v>100</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="2:6">
       <c r="B282" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D282" s="5"/>
       <c r="E282" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C283" s="3">
         <v>100</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="285" spans="2:6">
       <c r="B285" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C286" s="3">
         <v>100</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="288" spans="2:6">
       <c r="B288" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D288" s="5"/>
       <c r="E288" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C289" s="3">
         <v>100</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D290" s="5"/>
       <c r="E290" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C292" s="3">
         <v>100</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>35</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D293" s="5"/>
       <c r="E293" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="294" spans="2:6">
       <c r="B294" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
         <v>38</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295" spans="2:6">
       <c r="B295" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C295" s="3">
         <v>100</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="296" spans="2:6">
       <c r="B296" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D296" s="5"/>
       <c r="E296" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="297" spans="2:6">
       <c r="B297" s="3" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C297" s="3">
         <v>100</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
     </row>
     <row r="298" spans="4:5">
       <c r="D298" s="5"/>
       <c r="E298" s="3" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
     </row>
     <row r="299" spans="4:4">
@@ -5892,6 +6060,10 @@
       <c r="D316" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="T33:T37"/>
+    <mergeCell ref="T39:T44"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5923,22 +6095,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5946,25 +6118,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5981,13 +6153,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5995,127 +6167,127 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="239">
   <si>
     <t>##var</t>
   </si>
@@ -68,52 +68,55 @@
     <t>list,string</t>
   </si>
   <si>
-    <t>gut_3x3</t>
+    <t>gut_4x3</t>
   </si>
   <si>
     <t>0,0</t>
   </si>
   <si>
+    <t>XXXX</t>
+  </si>
+  <si>
+    <t>0周</t>
+  </si>
+  <si>
+    <t>frag_1x1</t>
+  </si>
+  <si>
+    <t>10,100</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>1周</t>
+  </si>
+  <si>
+    <t>frag_1x2</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>2周</t>
+  </si>
+  <si>
+    <t>frag_2x1</t>
+  </si>
+  <si>
+    <t>3周</t>
+  </si>
+  <si>
+    <t>4周</t>
+  </si>
+  <si>
+    <t>frag_3x1</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
     <t>XXX</t>
-  </si>
-  <si>
-    <t>0周</t>
-  </si>
-  <si>
-    <t>frag_1x1</t>
-  </si>
-  <si>
-    <t>10,100</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>1周</t>
-  </si>
-  <si>
-    <t>frag_1x2</t>
-  </si>
-  <si>
-    <t>XX</t>
-  </si>
-  <si>
-    <t>2周</t>
-  </si>
-  <si>
-    <t>frag_2x1</t>
-  </si>
-  <si>
-    <t>3周</t>
-  </si>
-  <si>
-    <t>4周</t>
-  </si>
-  <si>
-    <t>frag_3x1</t>
-  </si>
-  <si>
-    <t>10,60</t>
   </si>
   <si>
     <t>frag_1x3</t>
@@ -2022,12 +2025,12 @@
         <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3">
         <v>700</v>
@@ -2051,7 +2054,7 @@
     </row>
     <row r="15" spans="2:5">
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3">
         <v>700</v>
@@ -2065,12 +2068,12 @@
     </row>
     <row r="16" spans="5:5">
       <c r="E16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3">
         <v>700</v>
@@ -2079,7 +2082,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="5:5">
@@ -2089,7 +2092,7 @@
     </row>
     <row r="19" spans="2:21">
       <c r="B19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3">
         <v>700</v>
@@ -2098,10 +2101,10 @@
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="5:23">
@@ -2109,15 +2112,15 @@
         <v>26</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="2:21">
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3">
         <v>700</v>
@@ -2129,32 +2132,32 @@
         <v>26</v>
       </c>
       <c r="U21" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="5:21">
       <c r="E22" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:21">
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3">
         <v>700</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="U23" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="4:21">
@@ -2163,62 +2166,62 @@
         <v>26</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="2:21">
       <c r="B25" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" s="3">
         <v>700</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="4:21">
       <c r="D26" s="5"/>
       <c r="E26" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="4:21">
       <c r="D27" s="5"/>
       <c r="E27" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="3">
         <v>700</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="4:5">
       <c r="D29" s="5"/>
       <c r="E29" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="4:5">
@@ -2229,25 +2232,25 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" s="3">
         <v>700</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="4:23">
       <c r="D32" s="5"/>
       <c r="E32" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="4:21">
@@ -2256,66 +2259,66 @@
         <v>26</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="2:21">
       <c r="B34" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C34" s="3">
         <v>700</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="6"/>
       <c r="U34" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="4:21">
       <c r="D35" s="5"/>
       <c r="E35" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T35" s="6"/>
       <c r="U35" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="4:21">
       <c r="D36" s="5"/>
       <c r="E36" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="2:21">
       <c r="B37" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C37" s="3">
         <v>700</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T37" s="6"/>
       <c r="U37" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="4:5">
@@ -2327,31 +2330,31 @@
     <row r="39" spans="4:21">
       <c r="D39" s="5"/>
       <c r="E39" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T39" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="2:21">
       <c r="B40" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C40" s="3">
         <v>700</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T40" s="7"/>
       <c r="U40" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="4:21">
@@ -2361,96 +2364,96 @@
       </c>
       <c r="T41" s="7"/>
       <c r="U41" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="4:23">
       <c r="D42" s="5"/>
       <c r="E42" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T42" s="7"/>
       <c r="U42" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" spans="2:21">
       <c r="B43" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C43" s="3">
         <v>700</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T43" s="7"/>
       <c r="U43" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="4:21">
       <c r="D44" s="5"/>
       <c r="E44" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T44" s="7"/>
       <c r="U44" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C45" s="3">
         <v>700</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="4:5">
       <c r="D46" s="5"/>
       <c r="E46" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" s="3">
         <v>100</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>26</v>
@@ -2462,13 +2465,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C49" s="3">
         <v>100</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>23</v>
@@ -2480,7 +2483,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="3" t="s">
@@ -2493,13 +2496,13 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C51" s="3">
         <v>100</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>26</v>
@@ -2511,11 +2514,11 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2524,16 +2527,16 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C53" s="3">
         <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2542,7 +2545,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
@@ -2555,16 +2558,16 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C55" s="3">
         <v>100</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2573,7 +2576,7 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="3" t="s">
@@ -2586,13 +2589,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C57" s="3">
         <v>100</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>26</v>
@@ -2604,11 +2607,11 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F58" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2617,13 +2620,13 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C59" s="3">
         <v>100</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>26</v>
@@ -2635,7 +2638,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="3" t="s">
@@ -2648,13 +2651,13 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C61" s="3">
         <v>100</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>26</v>
@@ -2666,11 +2669,11 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F62" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2679,11 +2682,11 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F63" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2692,16 +2695,16 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C64" s="3">
         <v>100</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F64" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2710,11 +2713,11 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F65" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2723,7 +2726,7 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="3" t="s">
@@ -2736,16 +2739,16 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C67" s="3">
         <v>100</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F67" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2754,11 +2757,11 @@
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D68" s="5"/>
       <c r="E68" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F68" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2767,7 +2770,7 @@
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="3" t="s">
@@ -2780,13 +2783,13 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C70" s="3">
         <v>100</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>26</v>
@@ -2798,11 +2801,11 @@
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D71" s="5"/>
       <c r="E71" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F71" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2811,11 +2814,11 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F72" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2824,16 +2827,16 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C73" s="3">
         <v>100</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F73" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2842,7 +2845,7 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="3" t="s">
@@ -2855,11 +2858,11 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F75" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2868,16 +2871,16 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C76" s="3">
         <v>100</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F76" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2886,7 +2889,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D77" s="5"/>
       <c r="E77" s="3" t="s">
@@ -2899,11 +2902,11 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F78" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2912,16 +2915,16 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C79" s="3">
         <v>100</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F79" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2930,11 +2933,11 @@
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F80" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2943,16 +2946,16 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C81" s="3">
         <v>100</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F81" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2962,7 +2965,7 @@
     <row r="82" spans="4:7">
       <c r="D82" s="5"/>
       <c r="E82" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G82" s="3" t="str">
         <f>IF(B82="","",B82&amp;"_cherry")</f>
@@ -2971,3038 +2974,3038 @@
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" s="3">
+        <v>100</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F84" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C84" s="3">
-        <v>100</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D86" s="5"/>
       <c r="E86" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C87" s="3">
         <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C89" s="3">
         <v>100</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C91" s="3">
         <v>100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D92" s="5"/>
       <c r="E92" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C93" s="3">
         <v>100</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E93" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C95" s="3">
         <v>100</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D96" s="5"/>
       <c r="E96" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C97" s="3">
         <v>100</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D98" s="5"/>
       <c r="E98" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C100" s="3">
         <v>100</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D101" s="5"/>
       <c r="E101" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C103" s="3">
         <v>100</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C106" s="3">
         <v>100</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E106" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D107" s="5"/>
       <c r="E107" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D108" s="5"/>
       <c r="E108" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C109" s="3">
         <v>100</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D110" s="5"/>
       <c r="E110" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C112" s="3">
         <v>100</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="2:6">
       <c r="B114" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C115" s="3">
         <v>100</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D116" s="5"/>
       <c r="E116" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C117" s="3">
         <v>100</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="118" spans="4:5">
       <c r="D118" s="5"/>
       <c r="E118" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C119" s="3">
         <v>1</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C120" s="3">
+        <v>100</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C120" s="3">
-        <v>100</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D122" s="5"/>
       <c r="E122" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C123" s="3">
         <v>100</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D124" s="5"/>
       <c r="E124" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C125" s="3">
         <v>100</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D126" s="5"/>
       <c r="E126" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C127" s="3">
         <v>100</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C129" s="3">
         <v>100</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C131" s="3">
         <v>100</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D132" s="5"/>
       <c r="E132" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C133" s="3">
         <v>100</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D134" s="5"/>
       <c r="E134" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135" spans="2:6">
       <c r="B135" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C136" s="3">
         <v>100</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D137" s="5"/>
       <c r="E137" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="2:6">
       <c r="B138" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C139" s="3">
         <v>100</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141" spans="2:6">
       <c r="B141" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C142" s="3">
         <v>100</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" spans="2:6">
       <c r="B144" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C145" s="3">
         <v>100</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D146" s="5"/>
       <c r="E146" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="147" spans="2:6">
       <c r="B147" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C148" s="3">
         <v>100</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D149" s="5"/>
       <c r="E149" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="150" spans="2:6">
       <c r="B150" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C151" s="3">
         <v>100</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D152" s="5"/>
       <c r="E152" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C153" s="3">
         <v>100</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="154" spans="4:5">
       <c r="D154" s="5"/>
       <c r="E154" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C155" s="3">
         <v>1</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C156" s="3">
+        <v>100</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F156" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C156" s="3">
-        <v>100</v>
-      </c>
-      <c r="D156" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D158" s="5"/>
       <c r="E158" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C159" s="3">
         <v>100</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D160" s="5"/>
       <c r="E160" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C161" s="3">
         <v>100</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D162" s="5"/>
       <c r="E162" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C163" s="3">
         <v>100</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D164" s="5"/>
       <c r="E164" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C165" s="3">
         <v>100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C167" s="3">
         <v>100</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D168" s="5"/>
       <c r="E168" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C169" s="3">
         <v>100</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D170" s="5"/>
       <c r="E170" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="171" spans="2:6">
       <c r="B171" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C172" s="3">
         <v>100</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D173" s="5"/>
       <c r="E173" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="2:6">
       <c r="B174" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C175" s="3">
         <v>100</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D176" s="5"/>
       <c r="E176" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177" spans="2:6">
       <c r="B177" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C178" s="3">
         <v>100</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D179" s="5"/>
       <c r="E179" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D180" s="5"/>
       <c r="E180" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C181" s="3">
         <v>100</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="183" spans="2:6">
       <c r="B183" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C184" s="3">
         <v>100</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D185" s="5"/>
       <c r="E185" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="186" spans="2:6">
       <c r="B186" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C187" s="3">
         <v>100</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D188" s="5"/>
       <c r="E188" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C189" s="3">
         <v>100</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="190" spans="4:5">
       <c r="D190" s="5"/>
       <c r="E190" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C191" s="3">
         <v>1</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C192" s="3">
+        <v>100</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F192" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C192" s="3">
-        <v>100</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D194" s="5"/>
       <c r="E194" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C195" s="3">
         <v>100</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D196" s="5"/>
       <c r="E196" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C197" s="3">
         <v>100</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D198" s="5"/>
       <c r="E198" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C199" s="3">
         <v>100</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D200" s="5"/>
       <c r="E200" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C201" s="3">
         <v>100</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D202" s="5"/>
       <c r="E202" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C203" s="3">
         <v>100</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D204" s="5"/>
       <c r="E204" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C205" s="3">
         <v>100</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D206" s="5"/>
       <c r="E206" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="207" spans="2:6">
       <c r="B207" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C208" s="3">
         <v>100</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D209" s="5"/>
       <c r="E209" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="210" spans="2:6">
       <c r="B210" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C211" s="3">
         <v>100</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D212" s="5"/>
       <c r="E212" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="213" spans="2:6">
       <c r="B213" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C214" s="3">
         <v>100</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D215" s="5"/>
       <c r="E215" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="216" spans="2:6">
       <c r="B216" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D216" s="5"/>
       <c r="E216" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C217" s="3">
         <v>100</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="219" spans="2:6">
       <c r="B219" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C220" s="3">
         <v>100</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D221" s="5"/>
       <c r="E221" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="222" spans="2:6">
       <c r="B222" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D222" s="5"/>
       <c r="E222" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C223" s="3">
         <v>100</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D224" s="5"/>
       <c r="E224" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C225" s="3">
         <v>100</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="226" spans="4:5">
       <c r="D226" s="5"/>
       <c r="E226" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="227" spans="2:6">
       <c r="B227" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C227" s="3">
         <v>1</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C228" s="3">
+        <v>100</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E228" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F228" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="C228" s="3">
-        <v>100</v>
-      </c>
-      <c r="D228" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D230" s="5"/>
       <c r="E230" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C231" s="3">
         <v>100</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D232" s="5"/>
       <c r="E232" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C233" s="3">
         <v>100</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D234" s="5"/>
       <c r="E234" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C235" s="3">
         <v>100</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D236" s="5"/>
       <c r="E236" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C237" s="3">
         <v>100</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D238" s="5"/>
       <c r="E238" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C239" s="3">
         <v>100</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D240" s="5"/>
       <c r="E240" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C241" s="3">
         <v>100</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D242" s="5"/>
       <c r="E242" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="243" spans="2:6">
       <c r="B243" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D243" s="5"/>
       <c r="E243" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C244" s="3">
         <v>100</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D245" s="5"/>
       <c r="E245" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="246" spans="2:6">
       <c r="B246" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C247" s="3">
         <v>100</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D248" s="5"/>
       <c r="E248" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="249" spans="2:6">
       <c r="B249" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F249" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C250" s="3">
         <v>100</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D251" s="5"/>
       <c r="E251" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="252" spans="2:6">
       <c r="B252" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D252" s="5"/>
       <c r="E252" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C253" s="3">
         <v>100</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D254" s="5"/>
       <c r="E254" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="255" spans="2:6">
       <c r="B255" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C256" s="3">
         <v>100</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D257" s="5"/>
       <c r="E257" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="258" spans="2:6">
       <c r="B258" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C259" s="3">
         <v>100</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D260" s="5"/>
       <c r="E260" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C261" s="3">
         <v>100</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="262" spans="4:5">
       <c r="D262" s="5"/>
       <c r="E262" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="263" spans="2:6">
       <c r="B263" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C263" s="3">
         <v>1</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C264" s="3">
+        <v>100</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E264" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F264" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C264" s="3">
-        <v>100</v>
-      </c>
-      <c r="D264" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E264" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D266" s="5"/>
       <c r="E266" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C267" s="3">
         <v>100</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D268" s="5"/>
       <c r="E268" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C269" s="3">
         <v>100</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D270" s="5"/>
       <c r="E270" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C271" s="3">
         <v>100</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D272" s="5"/>
       <c r="E272" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C273" s="3">
         <v>100</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C275" s="3">
         <v>100</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D276" s="5"/>
       <c r="E276" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C277" s="3">
         <v>100</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D278" s="5"/>
       <c r="E278" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="279" spans="2:6">
       <c r="B279" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C280" s="3">
         <v>100</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D281" s="5"/>
       <c r="E281" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="282" spans="2:6">
       <c r="B282" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D282" s="5"/>
       <c r="E282" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C283" s="3">
         <v>100</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="285" spans="2:6">
       <c r="B285" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C286" s="3">
         <v>100</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D287" s="5"/>
       <c r="E287" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="288" spans="2:6">
       <c r="B288" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D288" s="5"/>
       <c r="E288" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C289" s="3">
         <v>100</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D290" s="5"/>
       <c r="E290" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="291" spans="2:6">
       <c r="B291" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C292" s="3">
         <v>100</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D293" s="5"/>
       <c r="E293" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="294" spans="2:6">
       <c r="B294" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="295" spans="2:6">
       <c r="B295" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C295" s="3">
         <v>100</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="296" spans="2:6">
       <c r="B296" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D296" s="5"/>
       <c r="E296" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="297" spans="2:6">
       <c r="B297" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C297" s="3">
         <v>100</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="298" spans="4:5">
       <c r="D298" s="5"/>
       <c r="E298" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="299" spans="4:4">
@@ -6095,22 +6098,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6118,25 +6121,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6153,13 +6156,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -6167,127 +6170,127 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="239">
   <si>
     <t>##var</t>
   </si>
@@ -68,7 +68,7 @@
     <t>list,string</t>
   </si>
   <si>
-    <t>gut_4x3</t>
+    <t>gut_4x4</t>
   </si>
   <si>
     <t>0,0</t>
@@ -77,58 +77,58 @@
     <t>XXXX</t>
   </si>
   <si>
+    <t>frag_1x1</t>
+  </si>
+  <si>
+    <t>10,100</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>frag_1x2</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>frag_2x1</t>
+  </si>
+  <si>
+    <t>frag_3x1</t>
+  </si>
+  <si>
+    <t>10,60</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>frag_1x3</t>
+  </si>
+  <si>
     <t>0周</t>
   </si>
   <si>
-    <t>frag_1x1</t>
-  </si>
-  <si>
-    <t>10,100</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>frag_L1</t>
   </si>
   <si>
     <t>1周</t>
   </si>
   <si>
-    <t>frag_1x2</t>
-  </si>
-  <si>
-    <t>XX</t>
+    <t>.X</t>
   </si>
   <si>
     <t>2周</t>
   </si>
   <si>
-    <t>frag_2x1</t>
+    <t>frag_L2</t>
   </si>
   <si>
     <t>3周</t>
   </si>
   <si>
     <t>4周</t>
-  </si>
-  <si>
-    <t>frag_3x1</t>
-  </si>
-  <si>
-    <t>10,60</t>
-  </si>
-  <si>
-    <t>XXX</t>
-  </si>
-  <si>
-    <t>frag_1x3</t>
-  </si>
-  <si>
-    <t>frag_L1</t>
-  </si>
-  <si>
-    <t>.X</t>
-  </si>
-  <si>
-    <t>frag_L2</t>
   </si>
   <si>
     <t>frag_L3</t>
@@ -1729,7 +1729,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W316"/>
+  <dimension ref="A1:W317"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="3" customWidth="1"/>
@@ -1827,470 +1827,465 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="5:19">
+    <row r="6" spans="5:5">
       <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="3" t="s">
+    </row>
+    <row r="7" spans="5:5">
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="3">
-        <v>10</v>
-      </c>
-      <c r="M6" s="3">
-        <v>11</v>
-      </c>
-      <c r="N6" s="3">
-        <v>12</v>
-      </c>
-      <c r="O6" s="3">
-        <v>13</v>
-      </c>
-      <c r="P6" s="3">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>15</v>
-      </c>
-      <c r="R6" s="3">
-        <v>16</v>
-      </c>
-      <c r="S6" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19">
-      <c r="B7" s="3" t="s">
+      <c r="C8" s="3">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="3">
-        <v>7</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3" t="s">
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="3">
-        <v>20</v>
-      </c>
-      <c r="M7" s="3">
-        <v>21</v>
-      </c>
-      <c r="N7" s="3">
-        <v>22</v>
-      </c>
-      <c r="O7" s="3">
-        <v>23</v>
-      </c>
-      <c r="P7" s="3">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>25</v>
-      </c>
-      <c r="R7" s="3">
-        <v>26</v>
-      </c>
-      <c r="S7" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="B8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="3">
-        <v>700</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="3">
-        <v>30</v>
-      </c>
-      <c r="M8" s="3">
-        <v>31</v>
-      </c>
-      <c r="N8" s="3">
-        <v>32</v>
-      </c>
-      <c r="O8" s="3">
-        <v>33</v>
-      </c>
-      <c r="P8" s="3">
-        <v>34</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>35</v>
-      </c>
-      <c r="R8" s="3">
-        <v>36</v>
-      </c>
-      <c r="S8" s="3">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19">
-      <c r="B9" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C9" s="3">
         <v>700</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="3">
+        <v>700</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="3">
-        <v>40</v>
-      </c>
-      <c r="M9" s="3">
-        <v>41</v>
-      </c>
-      <c r="N9" s="3">
-        <v>42</v>
-      </c>
-      <c r="O9" s="3">
-        <v>43</v>
-      </c>
-      <c r="P9" s="3">
-        <v>44</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>45</v>
-      </c>
-      <c r="R9" s="3">
-        <v>46</v>
-      </c>
-      <c r="S9" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="5:19">
-      <c r="E10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" s="3">
-        <v>50</v>
-      </c>
-      <c r="M10" s="3">
-        <v>51</v>
-      </c>
-      <c r="N10" s="3">
-        <v>52</v>
-      </c>
-      <c r="O10" s="3">
-        <v>53</v>
-      </c>
-      <c r="P10" s="3">
-        <v>54</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>55</v>
-      </c>
-      <c r="R10" s="3">
-        <v>56</v>
-      </c>
-      <c r="S10" s="3">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="3">
-        <v>700</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>32</v>
-      </c>
+    </row>
+    <row r="11" spans="5:5">
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3">
         <v>700</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="5:5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3">
+        <v>700</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="5:5">
       <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19">
+      <c r="E15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L15" s="3">
+        <v>10</v>
+      </c>
+      <c r="M15" s="3">
+        <v>11</v>
+      </c>
+      <c r="N15" s="3">
+        <v>12</v>
+      </c>
+      <c r="O15" s="3">
+        <v>13</v>
+      </c>
+      <c r="P15" s="3">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>15</v>
+      </c>
+      <c r="R15" s="3">
+        <v>16</v>
+      </c>
+      <c r="S15" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3">
+        <v>700</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L16" s="3">
+        <v>20</v>
+      </c>
+      <c r="M16" s="3">
+        <v>21</v>
+      </c>
+      <c r="N16" s="3">
+        <v>22</v>
+      </c>
+      <c r="O16" s="3">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="2:5">
-      <c r="B15" s="3" t="s">
+      <c r="P16" s="3">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>25</v>
+      </c>
+      <c r="R16" s="3">
+        <v>26</v>
+      </c>
+      <c r="S16" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19">
+      <c r="E17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L17" s="3">
+        <v>30</v>
+      </c>
+      <c r="M17" s="3">
+        <v>31</v>
+      </c>
+      <c r="N17" s="3">
+        <v>32</v>
+      </c>
+      <c r="O17" s="3">
+        <v>33</v>
+      </c>
+      <c r="P17" s="3">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="3">
         <v>35</v>
       </c>
-      <c r="C15" s="3">
+      <c r="R17" s="3">
+        <v>36</v>
+      </c>
+      <c r="S17" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="3">
         <v>700</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="5:5">
-      <c r="E16" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="2:5">
-      <c r="B17" s="3" t="s">
+      <c r="L18" s="3">
+        <v>40</v>
+      </c>
+      <c r="M18" s="3">
+        <v>41</v>
+      </c>
+      <c r="N18" s="3">
+        <v>42</v>
+      </c>
+      <c r="O18" s="3">
+        <v>43</v>
+      </c>
+      <c r="P18" s="3">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>45</v>
+      </c>
+      <c r="R18" s="3">
+        <v>46</v>
+      </c>
+      <c r="S18" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19">
+      <c r="E19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="3">
+      <c r="L19" s="3">
+        <v>50</v>
+      </c>
+      <c r="M19" s="3">
+        <v>51</v>
+      </c>
+      <c r="N19" s="3">
+        <v>52</v>
+      </c>
+      <c r="O19" s="3">
+        <v>53</v>
+      </c>
+      <c r="P19" s="3">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="3">
+        <v>55</v>
+      </c>
+      <c r="R19" s="3">
+        <v>56</v>
+      </c>
+      <c r="S19" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21">
+      <c r="B20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="3">
         <v>700</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="5:5">
-      <c r="E18" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21">
-      <c r="B19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="3">
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="5:23">
+      <c r="E21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21">
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3">
         <v>700</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="5:21">
+      <c r="E23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="U19" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="5:23">
-      <c r="E20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21">
-      <c r="B21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="U23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="3">
         <v>700</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="5:21">
-      <c r="E22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21">
-      <c r="B23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="3">
+      <c r="D24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="4:21">
+      <c r="D25" s="5"/>
+      <c r="E25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U25" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21">
+      <c r="B26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="3">
         <v>700</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="4:21">
-      <c r="D24" s="5"/>
-      <c r="E24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21">
-      <c r="B25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="3">
-        <v>700</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="4:21">
-      <c r="D26" s="5"/>
-      <c r="E26" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="27" spans="4:21">
       <c r="D27" s="5"/>
       <c r="E27" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="U27" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="4:21">
+      <c r="D28" s="5"/>
+      <c r="E28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="3" t="s">
+    <row r="29" spans="2:5">
+      <c r="B29" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <v>700</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="4:5">
-      <c r="D29" s="5"/>
       <c r="E29" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="4:5">
       <c r="D30" s="5"/>
       <c r="E30" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5">
+      <c r="D31" s="5"/>
+      <c r="E31" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C32" s="3">
         <v>700</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="4:23">
-      <c r="D32" s="5"/>
       <c r="E32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="33" spans="4:21">
+    </row>
+    <row r="33" spans="4:23">
       <c r="D33" s="5"/>
       <c r="E33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="4:21">
+      <c r="D34" s="5"/>
+      <c r="E34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T34" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="U33" s="3" t="s">
+      <c r="U34" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="2:21">
-      <c r="B34" s="3" t="s">
+    <row r="35" spans="2:21">
+      <c r="B35" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C35" s="3">
         <v>700</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T34" s="6"/>
-      <c r="U34" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="4:21">
-      <c r="D35" s="5"/>
       <c r="E35" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="T35" s="6"/>
       <c r="U35" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="4:21">
@@ -2300,172 +2295,164 @@
       </c>
       <c r="T36" s="6"/>
       <c r="U36" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21">
-      <c r="B37" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" s="3">
-        <v>700</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="4:21">
+      <c r="D37" s="5"/>
       <c r="E37" s="3" t="s">
         <v>39</v>
       </c>
       <c r="T37" s="6"/>
       <c r="U37" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21">
+      <c r="B38" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="3">
+        <v>700</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T38" s="6"/>
+      <c r="U38" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="4:5">
-      <c r="D38" s="5"/>
-      <c r="E38" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="4:21">
+    <row r="39" spans="4:5">
       <c r="D39" s="5"/>
       <c r="E39" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T39" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="4:21">
+      <c r="D40" s="5"/>
+      <c r="E40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T40" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="U39" s="3" t="s">
+      <c r="U40" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="2:21">
-      <c r="B40" s="3" t="s">
+    <row r="41" spans="2:21">
+      <c r="B41" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C41" s="3">
         <v>700</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="T40" s="7"/>
-      <c r="U40" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="4:21">
-      <c r="D41" s="5"/>
       <c r="E41" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="T41" s="7"/>
       <c r="U41" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="4:23">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="4:21">
       <c r="D42" s="5"/>
       <c r="E42" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="T42" s="7"/>
       <c r="U42" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21">
-      <c r="B43" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="3">
-        <v>700</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="4:23">
+      <c r="D43" s="5"/>
       <c r="E43" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="T43" s="7"/>
       <c r="U43" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="4:21">
-      <c r="D44" s="5"/>
+        <v>68</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21">
+      <c r="B44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="3">
+        <v>700</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E44" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="T44" s="7"/>
       <c r="U44" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5">
-      <c r="B45" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="3">
-        <v>700</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>47</v>
-      </c>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="4:21">
+      <c r="D45" s="5"/>
       <c r="E45" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="4:5">
-      <c r="D46" s="5"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="3">
+        <v>700</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="E46" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="4:5">
+      <c r="D47" s="5"/>
+      <c r="E47" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C47" s="3">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C48" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F48" s="3" t="str">
-        <f>IF(B48="","",$F$47)</f>
-        <v>m_cherry</v>
+        <v>22</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="3">
         <v>100</v>
@@ -2474,219 +2461,224 @@
         <v>76</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f t="shared" ref="F49:F81" si="0">IF(B49="","",$F$47)</f>
+        <f>IF(B49="","",$F$48)</f>
         <v>m_cherry</v>
       </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" s="5"/>
+        <v>79</v>
+      </c>
+      <c r="C50" s="3">
+        <v>100</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E50" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F50" s="3" t="str">
+        <f t="shared" ref="F50:F82" si="0">IF(B50="","",$F$48)</f>
+        <v>m_cherry</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="5"/>
+      <c r="E51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="2:6">
+      <c r="B52" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="3">
-        <v>100</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="3" t="str">
+      <c r="C52" s="3">
+        <v>100</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F52" s="3" t="str">
+    <row r="53" spans="2:6">
+      <c r="B53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="3" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C53" s="3">
-        <v>100</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F53" s="3" t="str">
+      <c r="C54" s="3">
+        <v>100</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F54" s="3" t="str">
+    <row r="55" spans="2:6">
+      <c r="B55" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="55" spans="2:6">
-      <c r="B55" s="3" t="s">
+    <row r="56" spans="2:6">
+      <c r="B56" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="3">
-        <v>100</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="C56" s="3">
+        <v>100</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F55" s="3" t="str">
+      <c r="F56" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56" s="5"/>
-      <c r="E56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F56" s="3" t="str">
+    <row r="57" spans="2:6">
+      <c r="B57" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="3" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="3">
-        <v>100</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F57" s="3" t="str">
+      <c r="C58" s="3">
+        <v>100</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="3" t="s">
+    <row r="59" spans="2:6">
+      <c r="B59" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F58" s="3" t="str">
+      <c r="F59" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="3" t="s">
+    <row r="60" spans="2:6">
+      <c r="B60" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C59" s="3">
-        <v>100</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" s="3" t="str">
+      <c r="C60" s="3">
+        <v>100</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60" s="5"/>
-      <c r="E60" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F60" s="3" t="str">
+    <row r="61" spans="2:6">
+      <c r="B61" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D61" s="5"/>
+      <c r="E61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F61" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="3" t="s">
+    <row r="62" spans="2:6">
+      <c r="B62" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="3">
-        <v>100</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F61" s="3" t="str">
+      <c r="C62" s="3">
+        <v>100</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="3" t="str">
         <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
-      <c r="B62" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="E62" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F62" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
     <row r="63" spans="2:6">
       <c r="B63" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F63" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2695,33 +2687,33 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C64" s="3">
-        <v>100</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D64" s="5"/>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F64" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D65" s="5"/>
+        <v>87</v>
+      </c>
+      <c r="C65" s="3">
+        <v>100</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E65" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F65" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="D66" s="5"/>
       <c r="E66" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F66" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2739,33 +2731,33 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="3">
-        <v>100</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D67" s="5"/>
       <c r="E67" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F67" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D68" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="C68" s="3">
+        <v>100</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E68" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F68" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="69" spans="2:6">
@@ -2774,7 +2766,7 @@
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F69" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2783,33 +2775,33 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="3">
-        <v>100</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D70" s="5"/>
       <c r="E70" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F70" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D71" s="5"/>
+        <v>89</v>
+      </c>
+      <c r="C71" s="3">
+        <v>100</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E71" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F71" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="72" spans="2:6">
@@ -2827,33 +2819,33 @@
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C73" s="3">
-        <v>100</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D73" s="5"/>
       <c r="E73" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F73" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="C74" s="3">
+        <v>100</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E74" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F74" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="75" spans="2:6">
@@ -2862,7 +2854,7 @@
       </c>
       <c r="D75" s="5"/>
       <c r="E75" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F75" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2871,33 +2863,33 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C76" s="3">
-        <v>100</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D76" s="5"/>
       <c r="E76" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F76" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="C77" s="3">
+        <v>100</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E77" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F77" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="78" spans="2:6">
@@ -2906,7 +2898,7 @@
       </c>
       <c r="D78" s="5"/>
       <c r="E78" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F78" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2915,92 +2907,88 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C79" s="3">
-        <v>100</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D79" s="5"/>
       <c r="E79" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F79" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>m_cherry</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D80" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="C80" s="3">
+        <v>100</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E80" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F80" s="3" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>m_cherry</v>
       </c>
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C81" s="3">
-        <v>100</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D81" s="5"/>
       <c r="E81" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F81" s="3" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
+      <c r="B82" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82" s="3">
+        <v>100</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F82" s="3" t="str">
+        <f t="shared" si="0"/>
         <v>m_cherry</v>
       </c>
     </row>
-    <row r="82" spans="4:7">
-      <c r="D82" s="5"/>
-      <c r="E82" s="3" t="s">
+    <row r="83" spans="4:7">
+      <c r="D83" s="5"/>
+      <c r="E83" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G82" s="3" t="str">
-        <f>IF(B82="","",B82&amp;"_cherry")</f>
+      <c r="G83" s="3" t="str">
+        <f>IF(B83="","",B83&amp;"_cherry")</f>
         <v/>
-      </c>
-    </row>
-    <row r="83" spans="2:6">
-      <c r="B83" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C83" s="3">
-        <v>1</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C84" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>95</v>
@@ -3008,7 +2996,7 @@
     </row>
     <row r="85" spans="2:6">
       <c r="B85" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C85" s="3">
         <v>100</v>
@@ -3017,7 +3005,7 @@
         <v>76</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>95</v>
@@ -3025,188 +3013,193 @@
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D86" s="5"/>
+        <v>97</v>
+      </c>
+      <c r="C86" s="3">
+        <v>100</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E86" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C87" s="3">
-        <v>100</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D87" s="5"/>
       <c r="E87" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D88" s="5"/>
+        <v>98</v>
+      </c>
+      <c r="C88" s="3">
+        <v>100</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E88" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C89" s="3">
-        <v>100</v>
-      </c>
-      <c r="D89" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D89" s="5"/>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D90" s="5"/>
+        <v>99</v>
+      </c>
+      <c r="C90" s="3">
+        <v>100</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E90" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="2:6">
       <c r="B91" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C91" s="3">
-        <v>100</v>
-      </c>
-      <c r="D91" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D91" s="5"/>
       <c r="E91" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D92" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="C92" s="3">
+        <v>100</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E92" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C93" s="3">
-        <v>100</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D93" s="5"/>
       <c r="E93" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D94" s="5"/>
+        <v>101</v>
+      </c>
+      <c r="C94" s="3">
+        <v>100</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E94" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="2:6">
       <c r="B95" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C95" s="3">
-        <v>100</v>
-      </c>
-      <c r="D95" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D95" s="5"/>
       <c r="E95" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D96" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="C96" s="3">
+        <v>100</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E96" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C97" s="3">
-        <v>100</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D97" s="5"/>
       <c r="E97" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D98" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="C98" s="3">
+        <v>100</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E98" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="2:6">
@@ -3215,7 +3208,7 @@
       </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>80</v>
@@ -3223,31 +3216,31 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C100" s="3">
-        <v>100</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D100" s="5"/>
       <c r="E100" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D101" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="C101" s="3">
+        <v>100</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E101" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="2:6">
@@ -3256,7 +3249,7 @@
       </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>80</v>
@@ -3264,31 +3257,31 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C103" s="3">
-        <v>100</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D103" s="5"/>
       <c r="E103" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D104" s="5"/>
+        <v>105</v>
+      </c>
+      <c r="C104" s="3">
+        <v>100</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E104" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="2:6">
@@ -3297,7 +3290,7 @@
       </c>
       <c r="D105" s="5"/>
       <c r="E105" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>80</v>
@@ -3305,31 +3298,31 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C106" s="3">
-        <v>100</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D106" s="5"/>
       <c r="E106" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D107" s="5"/>
+        <v>106</v>
+      </c>
+      <c r="C107" s="3">
+        <v>100</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E107" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="2:6">
@@ -3346,31 +3339,31 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C109" s="3">
-        <v>100</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D109" s="5"/>
       <c r="E109" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D110" s="5"/>
+        <v>107</v>
+      </c>
+      <c r="C110" s="3">
+        <v>100</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E110" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="2:6">
@@ -3379,7 +3372,7 @@
       </c>
       <c r="D111" s="5"/>
       <c r="E111" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>80</v>
@@ -3387,31 +3380,31 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C112" s="3">
-        <v>100</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D112" s="5"/>
       <c r="E112" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" spans="2:6">
       <c r="B113" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D113" s="5"/>
+        <v>108</v>
+      </c>
+      <c r="C113" s="3">
+        <v>100</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E113" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="114" spans="2:6">
@@ -3420,7 +3413,7 @@
       </c>
       <c r="D114" s="5"/>
       <c r="E114" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>80</v>
@@ -3428,85 +3421,80 @@
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C115" s="3">
-        <v>100</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D115" s="5"/>
       <c r="E115" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D116" s="5"/>
+        <v>109</v>
+      </c>
+      <c r="C116" s="3">
+        <v>100</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E116" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C117" s="3">
-        <v>100</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D117" s="5"/>
       <c r="E117" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F117" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="2:6">
+      <c r="B118" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118" s="3">
+        <v>100</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="118" spans="4:5">
-      <c r="D118" s="5"/>
-      <c r="E118" s="3" t="s">
+    <row r="119" spans="4:5">
+      <c r="D119" s="5"/>
+      <c r="E119" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
-      <c r="B119" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C119" s="3">
-        <v>1</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C120" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>112</v>
@@ -3514,7 +3502,7 @@
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C121" s="3">
         <v>100</v>
@@ -3523,7 +3511,7 @@
         <v>76</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>112</v>
@@ -3531,188 +3519,193 @@
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D122" s="5"/>
+        <v>114</v>
+      </c>
+      <c r="C122" s="3">
+        <v>100</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E122" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="123" spans="2:6">
       <c r="B123" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C123" s="3">
-        <v>100</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D123" s="5"/>
       <c r="E123" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D124" s="5"/>
+        <v>115</v>
+      </c>
+      <c r="C124" s="3">
+        <v>100</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E124" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C125" s="3">
-        <v>100</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D125" s="5"/>
       <c r="E125" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="126" spans="2:6">
       <c r="B126" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D126" s="5"/>
+        <v>116</v>
+      </c>
+      <c r="C126" s="3">
+        <v>100</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E126" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="127" spans="2:6">
       <c r="B127" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C127" s="3">
-        <v>100</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D127" s="5"/>
       <c r="E127" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="128" spans="2:6">
       <c r="B128" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D128" s="5"/>
+        <v>117</v>
+      </c>
+      <c r="C128" s="3">
+        <v>100</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E128" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="129" spans="2:6">
       <c r="B129" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C129" s="3">
-        <v>100</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D129" s="5"/>
       <c r="E129" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D130" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="C130" s="3">
+        <v>100</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E130" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="131" spans="2:6">
       <c r="B131" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C131" s="3">
-        <v>100</v>
-      </c>
-      <c r="D131" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D131" s="5"/>
       <c r="E131" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="132" spans="2:6">
       <c r="B132" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D132" s="5"/>
+        <v>119</v>
+      </c>
+      <c r="C132" s="3">
+        <v>100</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E132" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="133" spans="2:6">
       <c r="B133" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C133" s="3">
-        <v>100</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D133" s="5"/>
       <c r="E133" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="134" spans="2:6">
       <c r="B134" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D134" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="C134" s="3">
+        <v>100</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E134" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="135" spans="2:6">
@@ -3721,7 +3714,7 @@
       </c>
       <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>80</v>
@@ -3729,31 +3722,31 @@
     </row>
     <row r="136" spans="2:6">
       <c r="B136" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C136" s="3">
-        <v>100</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D136" s="5"/>
       <c r="E136" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137" spans="2:6">
       <c r="B137" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D137" s="5"/>
+        <v>121</v>
+      </c>
+      <c r="C137" s="3">
+        <v>100</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E137" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -3762,7 +3755,7 @@
       </c>
       <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>80</v>
@@ -3770,31 +3763,31 @@
     </row>
     <row r="139" spans="2:6">
       <c r="B139" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C139" s="3">
-        <v>100</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D139" s="5"/>
       <c r="E139" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140" spans="2:6">
       <c r="B140" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D140" s="5"/>
+        <v>122</v>
+      </c>
+      <c r="C140" s="3">
+        <v>100</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E140" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="141" spans="2:6">
@@ -3803,7 +3796,7 @@
       </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>80</v>
@@ -3811,31 +3804,31 @@
     </row>
     <row r="142" spans="2:6">
       <c r="B142" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C142" s="3">
-        <v>100</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D142" s="5"/>
       <c r="E142" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143" spans="2:6">
       <c r="B143" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D143" s="5"/>
+        <v>123</v>
+      </c>
+      <c r="C143" s="3">
+        <v>100</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E143" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="144" spans="2:6">
@@ -3852,31 +3845,31 @@
     </row>
     <row r="145" spans="2:6">
       <c r="B145" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C145" s="3">
-        <v>100</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D145" s="5"/>
       <c r="E145" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D146" s="5"/>
+        <v>124</v>
+      </c>
+      <c r="C146" s="3">
+        <v>100</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E146" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="147" spans="2:6">
@@ -3885,7 +3878,7 @@
       </c>
       <c r="D147" s="5"/>
       <c r="E147" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>80</v>
@@ -3893,31 +3886,31 @@
     </row>
     <row r="148" spans="2:6">
       <c r="B148" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C148" s="3">
-        <v>100</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D148" s="5"/>
       <c r="E148" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="149" spans="2:6">
       <c r="B149" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D149" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="C149" s="3">
+        <v>100</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E149" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="150" spans="2:6">
@@ -3926,7 +3919,7 @@
       </c>
       <c r="D150" s="5"/>
       <c r="E150" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>80</v>
@@ -3934,85 +3927,80 @@
     </row>
     <row r="151" spans="2:6">
       <c r="B151" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C151" s="3">
-        <v>100</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D151" s="5"/>
       <c r="E151" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="152" spans="2:6">
       <c r="B152" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D152" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="C152" s="3">
+        <v>100</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E152" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="153" spans="2:6">
       <c r="B153" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C153" s="3">
-        <v>100</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D153" s="5"/>
       <c r="E153" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F153" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6">
+      <c r="B154" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C154" s="3">
+        <v>100</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F154" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="154" spans="4:5">
-      <c r="D154" s="5"/>
-      <c r="E154" s="3" t="s">
+    <row r="155" spans="4:5">
+      <c r="D155" s="5"/>
+      <c r="E155" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C155" s="3">
-        <v>1</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E155" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F155" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="156" spans="2:6">
       <c r="B156" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C156" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>129</v>
@@ -4020,7 +4008,7 @@
     </row>
     <row r="157" spans="2:6">
       <c r="B157" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C157" s="3">
         <v>100</v>
@@ -4029,7 +4017,7 @@
         <v>76</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>129</v>
@@ -4037,188 +4025,193 @@
     </row>
     <row r="158" spans="2:6">
       <c r="B158" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D158" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="C158" s="3">
+        <v>100</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E158" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C159" s="3">
-        <v>100</v>
-      </c>
-      <c r="D159" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D159" s="5"/>
       <c r="E159" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="160" spans="2:6">
       <c r="B160" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D160" s="5"/>
+        <v>132</v>
+      </c>
+      <c r="C160" s="3">
+        <v>100</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E160" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C161" s="3">
-        <v>100</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D161" s="5"/>
       <c r="E161" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D162" s="5"/>
+        <v>133</v>
+      </c>
+      <c r="C162" s="3">
+        <v>100</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E162" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C163" s="3">
-        <v>100</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D163" s="5"/>
       <c r="E163" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D164" s="5"/>
+        <v>134</v>
+      </c>
+      <c r="C164" s="3">
+        <v>100</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E164" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C165" s="3">
-        <v>100</v>
-      </c>
-      <c r="D165" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D165" s="5"/>
       <c r="E165" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D166" s="5"/>
+        <v>135</v>
+      </c>
+      <c r="C166" s="3">
+        <v>100</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E166" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C167" s="3">
-        <v>100</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D167" s="5"/>
       <c r="E167" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D168" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="C168" s="3">
+        <v>100</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E168" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="169" spans="2:6">
       <c r="B169" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C169" s="3">
-        <v>100</v>
-      </c>
-      <c r="D169" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D169" s="5"/>
       <c r="E169" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="170" spans="2:6">
       <c r="B170" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D170" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="C170" s="3">
+        <v>100</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E170" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="171" spans="2:6">
@@ -4227,7 +4220,7 @@
       </c>
       <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>80</v>
@@ -4235,31 +4228,31 @@
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C172" s="3">
-        <v>100</v>
-      </c>
-      <c r="D172" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D172" s="5"/>
       <c r="E172" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="173" spans="2:6">
       <c r="B173" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D173" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="C173" s="3">
+        <v>100</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E173" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174" spans="2:6">
@@ -4268,7 +4261,7 @@
       </c>
       <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>80</v>
@@ -4276,31 +4269,31 @@
     </row>
     <row r="175" spans="2:6">
       <c r="B175" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C175" s="3">
-        <v>100</v>
-      </c>
-      <c r="D175" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D175" s="5"/>
       <c r="E175" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D176" s="5"/>
+        <v>139</v>
+      </c>
+      <c r="C176" s="3">
+        <v>100</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E176" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="177" spans="2:6">
@@ -4309,7 +4302,7 @@
       </c>
       <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>80</v>
@@ -4317,31 +4310,31 @@
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C178" s="3">
-        <v>100</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D178" s="5"/>
       <c r="E178" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D179" s="5"/>
+        <v>140</v>
+      </c>
+      <c r="C179" s="3">
+        <v>100</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E179" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="180" spans="2:6">
@@ -4358,31 +4351,31 @@
     </row>
     <row r="181" spans="2:6">
       <c r="B181" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C181" s="3">
-        <v>100</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D181" s="5"/>
       <c r="E181" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D182" s="5"/>
+        <v>141</v>
+      </c>
+      <c r="C182" s="3">
+        <v>100</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E182" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="183" spans="2:6">
@@ -4391,7 +4384,7 @@
       </c>
       <c r="D183" s="5"/>
       <c r="E183" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>80</v>
@@ -4399,31 +4392,31 @@
     </row>
     <row r="184" spans="2:6">
       <c r="B184" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C184" s="3">
-        <v>100</v>
-      </c>
-      <c r="D184" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D184" s="5"/>
       <c r="E184" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D185" s="5"/>
+        <v>142</v>
+      </c>
+      <c r="C185" s="3">
+        <v>100</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E185" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="186" spans="2:6">
@@ -4432,7 +4425,7 @@
       </c>
       <c r="D186" s="5"/>
       <c r="E186" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>80</v>
@@ -4440,85 +4433,80 @@
     </row>
     <row r="187" spans="2:6">
       <c r="B187" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C187" s="3">
-        <v>100</v>
-      </c>
-      <c r="D187" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D187" s="5"/>
       <c r="E187" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
     </row>
     <row r="188" spans="2:6">
       <c r="B188" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D188" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="C188" s="3">
+        <v>100</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E188" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C189" s="3">
-        <v>100</v>
-      </c>
-      <c r="D189" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D189" s="5"/>
       <c r="E189" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F189" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="190" spans="2:6">
+      <c r="B190" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C190" s="3">
+        <v>100</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F190" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="190" spans="4:5">
-      <c r="D190" s="5"/>
-      <c r="E190" s="3" t="s">
+    <row r="191" spans="4:5">
+      <c r="D191" s="5"/>
+      <c r="E191" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="191" spans="2:6">
-      <c r="B191" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C191" s="3">
-        <v>1</v>
-      </c>
-      <c r="D191" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C192" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>146</v>
@@ -4526,7 +4514,7 @@
     </row>
     <row r="193" spans="2:6">
       <c r="B193" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C193" s="3">
         <v>100</v>
@@ -4535,7 +4523,7 @@
         <v>76</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>146</v>
@@ -4543,188 +4531,193 @@
     </row>
     <row r="194" spans="2:6">
       <c r="B194" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D194" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="C194" s="3">
+        <v>100</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E194" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="195" spans="2:6">
       <c r="B195" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C195" s="3">
-        <v>100</v>
-      </c>
-      <c r="D195" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D195" s="5"/>
       <c r="E195" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="196" spans="2:6">
       <c r="B196" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D196" s="5"/>
+        <v>149</v>
+      </c>
+      <c r="C196" s="3">
+        <v>100</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E196" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="197" spans="2:6">
       <c r="B197" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C197" s="3">
-        <v>100</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D197" s="5"/>
       <c r="E197" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="198" spans="2:6">
       <c r="B198" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D198" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="C198" s="3">
+        <v>100</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E198" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="199" spans="2:6">
       <c r="B199" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C199" s="3">
-        <v>100</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D199" s="5"/>
       <c r="E199" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="200" spans="2:6">
       <c r="B200" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D200" s="5"/>
+        <v>151</v>
+      </c>
+      <c r="C200" s="3">
+        <v>100</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E200" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="201" spans="2:6">
       <c r="B201" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C201" s="3">
-        <v>100</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D201" s="5"/>
       <c r="E201" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="2:6">
       <c r="B202" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D202" s="5"/>
+        <v>152</v>
+      </c>
+      <c r="C202" s="3">
+        <v>100</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E202" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="203" spans="2:6">
       <c r="B203" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C203" s="3">
-        <v>100</v>
-      </c>
-      <c r="D203" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D203" s="5"/>
       <c r="E203" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204" spans="2:6">
       <c r="B204" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D204" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="C204" s="3">
+        <v>100</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E204" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="205" spans="2:6">
       <c r="B205" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C205" s="3">
-        <v>100</v>
-      </c>
-      <c r="D205" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D205" s="5"/>
       <c r="E205" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="206" spans="2:6">
       <c r="B206" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D206" s="5"/>
+        <v>154</v>
+      </c>
+      <c r="C206" s="3">
+        <v>100</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E206" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="207" spans="2:6">
@@ -4733,7 +4726,7 @@
       </c>
       <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>80</v>
@@ -4741,31 +4734,31 @@
     </row>
     <row r="208" spans="2:6">
       <c r="B208" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C208" s="3">
-        <v>100</v>
-      </c>
-      <c r="D208" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D208" s="5"/>
       <c r="E208" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="209" spans="2:6">
       <c r="B209" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D209" s="5"/>
+        <v>155</v>
+      </c>
+      <c r="C209" s="3">
+        <v>100</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E209" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="210" spans="2:6">
@@ -4774,7 +4767,7 @@
       </c>
       <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>80</v>
@@ -4782,31 +4775,31 @@
     </row>
     <row r="211" spans="2:6">
       <c r="B211" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C211" s="3">
-        <v>100</v>
-      </c>
-      <c r="D211" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D211" s="5"/>
       <c r="E211" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="212" spans="2:6">
       <c r="B212" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D212" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="C212" s="3">
+        <v>100</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E212" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="213" spans="2:6">
@@ -4815,7 +4808,7 @@
       </c>
       <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>80</v>
@@ -4823,31 +4816,31 @@
     </row>
     <row r="214" spans="2:6">
       <c r="B214" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C214" s="3">
-        <v>100</v>
-      </c>
-      <c r="D214" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D214" s="5"/>
       <c r="E214" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F214" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="215" spans="2:6">
       <c r="B215" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D215" s="5"/>
+        <v>157</v>
+      </c>
+      <c r="C215" s="3">
+        <v>100</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E215" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="216" spans="2:6">
@@ -4864,31 +4857,31 @@
     </row>
     <row r="217" spans="2:6">
       <c r="B217" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C217" s="3">
-        <v>100</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D217" s="5"/>
       <c r="E217" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="218" spans="2:6">
       <c r="B218" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D218" s="5"/>
+        <v>158</v>
+      </c>
+      <c r="C218" s="3">
+        <v>100</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E218" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="219" spans="2:6">
@@ -4897,7 +4890,7 @@
       </c>
       <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>80</v>
@@ -4905,31 +4898,31 @@
     </row>
     <row r="220" spans="2:6">
       <c r="B220" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C220" s="3">
-        <v>100</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D220" s="5"/>
       <c r="E220" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="221" spans="2:6">
       <c r="B221" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D221" s="5"/>
+        <v>159</v>
+      </c>
+      <c r="C221" s="3">
+        <v>100</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E221" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="222" spans="2:6">
@@ -4938,7 +4931,7 @@
       </c>
       <c r="D222" s="5"/>
       <c r="E222" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>80</v>
@@ -4946,85 +4939,80 @@
     </row>
     <row r="223" spans="2:6">
       <c r="B223" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C223" s="3">
-        <v>100</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D223" s="5"/>
       <c r="E223" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>146</v>
+        <v>80</v>
       </c>
     </row>
     <row r="224" spans="2:6">
       <c r="B224" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D224" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="C224" s="3">
+        <v>100</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E224" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
     </row>
     <row r="225" spans="2:6">
       <c r="B225" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C225" s="3">
-        <v>100</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D225" s="5"/>
       <c r="E225" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F225" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6">
+      <c r="B226" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C226" s="3">
+        <v>100</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F226" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="226" spans="4:5">
-      <c r="D226" s="5"/>
-      <c r="E226" s="3" t="s">
+    <row r="227" spans="4:5">
+      <c r="D227" s="5"/>
+      <c r="E227" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="227" spans="2:6">
-      <c r="B227" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C227" s="3">
-        <v>1</v>
-      </c>
-      <c r="D227" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E227" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="228" spans="2:6">
       <c r="B228" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C228" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D228" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>163</v>
@@ -5032,7 +5020,7 @@
     </row>
     <row r="229" spans="2:6">
       <c r="B229" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C229" s="3">
         <v>100</v>
@@ -5041,7 +5029,7 @@
         <v>76</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>163</v>
@@ -5049,188 +5037,193 @@
     </row>
     <row r="230" spans="2:6">
       <c r="B230" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D230" s="5"/>
+        <v>165</v>
+      </c>
+      <c r="C230" s="3">
+        <v>100</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E230" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="231" spans="2:6">
       <c r="B231" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C231" s="3">
-        <v>100</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D231" s="5"/>
       <c r="E231" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="232" spans="2:6">
       <c r="B232" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D232" s="5"/>
+        <v>166</v>
+      </c>
+      <c r="C232" s="3">
+        <v>100</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E232" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="233" spans="2:6">
       <c r="B233" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C233" s="3">
-        <v>100</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D233" s="5"/>
       <c r="E233" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="234" spans="2:6">
       <c r="B234" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D234" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="C234" s="3">
+        <v>100</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E234" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="235" spans="2:6">
       <c r="B235" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C235" s="3">
-        <v>100</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D235" s="5"/>
       <c r="E235" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="236" spans="2:6">
       <c r="B236" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D236" s="5"/>
+        <v>168</v>
+      </c>
+      <c r="C236" s="3">
+        <v>100</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E236" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="237" spans="2:6">
       <c r="B237" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C237" s="3">
-        <v>100</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D237" s="5"/>
       <c r="E237" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="238" spans="2:6">
       <c r="B238" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D238" s="5"/>
+        <v>169</v>
+      </c>
+      <c r="C238" s="3">
+        <v>100</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E238" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="239" spans="2:6">
       <c r="B239" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C239" s="3">
-        <v>100</v>
-      </c>
-      <c r="D239" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D239" s="5"/>
       <c r="E239" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F239" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="240" spans="2:6">
       <c r="B240" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D240" s="5"/>
+        <v>170</v>
+      </c>
+      <c r="C240" s="3">
+        <v>100</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E240" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="241" spans="2:6">
       <c r="B241" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C241" s="3">
-        <v>100</v>
-      </c>
-      <c r="D241" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D241" s="5"/>
       <c r="E241" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F241" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="242" spans="2:6">
       <c r="B242" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D242" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="C242" s="3">
+        <v>100</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E242" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="243" spans="2:6">
@@ -5239,7 +5232,7 @@
       </c>
       <c r="D243" s="5"/>
       <c r="E243" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>80</v>
@@ -5247,31 +5240,31 @@
     </row>
     <row r="244" spans="2:6">
       <c r="B244" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C244" s="3">
-        <v>100</v>
-      </c>
-      <c r="D244" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D244" s="5"/>
       <c r="E244" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F244" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="245" spans="2:6">
       <c r="B245" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D245" s="5"/>
+        <v>172</v>
+      </c>
+      <c r="C245" s="3">
+        <v>100</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E245" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="246" spans="2:6">
@@ -5280,7 +5273,7 @@
       </c>
       <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>80</v>
@@ -5288,31 +5281,31 @@
     </row>
     <row r="247" spans="2:6">
       <c r="B247" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C247" s="3">
-        <v>100</v>
-      </c>
-      <c r="D247" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D247" s="5"/>
       <c r="E247" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F247" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="248" spans="2:6">
       <c r="B248" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D248" s="5"/>
+        <v>173</v>
+      </c>
+      <c r="C248" s="3">
+        <v>100</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E248" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="249" spans="2:6">
@@ -5321,7 +5314,7 @@
       </c>
       <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>80</v>
@@ -5329,31 +5322,31 @@
     </row>
     <row r="250" spans="2:6">
       <c r="B250" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C250" s="3">
-        <v>100</v>
-      </c>
-      <c r="D250" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D250" s="5"/>
       <c r="E250" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="251" spans="2:6">
       <c r="B251" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D251" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="C251" s="3">
+        <v>100</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E251" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="252" spans="2:6">
@@ -5370,31 +5363,31 @@
     </row>
     <row r="253" spans="2:6">
       <c r="B253" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C253" s="3">
-        <v>100</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D253" s="5"/>
       <c r="E253" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F253" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="254" spans="2:6">
       <c r="B254" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D254" s="5"/>
+        <v>175</v>
+      </c>
+      <c r="C254" s="3">
+        <v>100</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E254" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="255" spans="2:6">
@@ -5403,7 +5396,7 @@
       </c>
       <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>80</v>
@@ -5411,31 +5404,31 @@
     </row>
     <row r="256" spans="2:6">
       <c r="B256" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C256" s="3">
-        <v>100</v>
-      </c>
-      <c r="D256" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D256" s="5"/>
       <c r="E256" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="257" spans="2:6">
       <c r="B257" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D257" s="5"/>
+        <v>176</v>
+      </c>
+      <c r="C257" s="3">
+        <v>100</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E257" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="258" spans="2:6">
@@ -5444,7 +5437,7 @@
       </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>80</v>
@@ -5452,85 +5445,80 @@
     </row>
     <row r="259" spans="2:6">
       <c r="B259" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C259" s="3">
-        <v>100</v>
-      </c>
-      <c r="D259" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D259" s="5"/>
       <c r="E259" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>163</v>
+        <v>80</v>
       </c>
     </row>
     <row r="260" spans="2:6">
       <c r="B260" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D260" s="5"/>
+        <v>177</v>
+      </c>
+      <c r="C260" s="3">
+        <v>100</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E260" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>80</v>
+        <v>163</v>
       </c>
     </row>
     <row r="261" spans="2:6">
       <c r="B261" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C261" s="3">
-        <v>100</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D261" s="5"/>
       <c r="E261" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F261" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6">
+      <c r="B262" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C262" s="3">
+        <v>100</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E262" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F262" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="262" spans="4:5">
-      <c r="D262" s="5"/>
-      <c r="E262" s="3" t="s">
+    <row r="263" spans="4:5">
+      <c r="D263" s="5"/>
+      <c r="E263" s="3" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="263" spans="2:6">
-      <c r="B263" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C263" s="3">
-        <v>1</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E263" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F263" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="264" spans="2:6">
       <c r="B264" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C264" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D264" s="5" t="s">
         <v>76</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>180</v>
@@ -5538,7 +5526,7 @@
     </row>
     <row r="265" spans="2:6">
       <c r="B265" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C265" s="3">
         <v>100</v>
@@ -5547,7 +5535,7 @@
         <v>76</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>180</v>
@@ -5555,188 +5543,193 @@
     </row>
     <row r="266" spans="2:6">
       <c r="B266" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D266" s="5"/>
+        <v>182</v>
+      </c>
+      <c r="C266" s="3">
+        <v>100</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E266" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="267" spans="2:6">
       <c r="B267" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C267" s="3">
-        <v>100</v>
-      </c>
-      <c r="D267" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D267" s="5"/>
       <c r="E267" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="268" spans="2:6">
       <c r="B268" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D268" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="C268" s="3">
+        <v>100</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E268" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="269" spans="2:6">
       <c r="B269" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C269" s="3">
-        <v>100</v>
-      </c>
-      <c r="D269" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D269" s="5"/>
       <c r="E269" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="270" spans="2:6">
       <c r="B270" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D270" s="5"/>
+        <v>184</v>
+      </c>
+      <c r="C270" s="3">
+        <v>100</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E270" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="271" spans="2:6">
       <c r="B271" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C271" s="3">
-        <v>100</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D271" s="5"/>
       <c r="E271" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="272" spans="2:6">
       <c r="B272" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D272" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="C272" s="3">
+        <v>100</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E272" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="273" spans="2:6">
       <c r="B273" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C273" s="3">
-        <v>100</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D273" s="5"/>
       <c r="E273" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="274" spans="2:6">
       <c r="B274" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D274" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="C274" s="3">
+        <v>100</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E274" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="275" spans="2:6">
       <c r="B275" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C275" s="3">
-        <v>100</v>
-      </c>
-      <c r="D275" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D275" s="5"/>
       <c r="E275" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="276" spans="2:6">
       <c r="B276" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D276" s="5"/>
+        <v>187</v>
+      </c>
+      <c r="C276" s="3">
+        <v>100</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E276" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="277" spans="2:6">
       <c r="B277" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C277" s="3">
-        <v>100</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D277" s="5"/>
       <c r="E277" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="278" spans="2:6">
       <c r="B278" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D278" s="5"/>
+        <v>188</v>
+      </c>
+      <c r="C278" s="3">
+        <v>100</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E278" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="279" spans="2:6">
@@ -5745,7 +5738,7 @@
       </c>
       <c r="D279" s="5"/>
       <c r="E279" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>80</v>
@@ -5753,31 +5746,31 @@
     </row>
     <row r="280" spans="2:6">
       <c r="B280" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C280" s="3">
-        <v>100</v>
-      </c>
-      <c r="D280" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D280" s="5"/>
       <c r="E280" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="281" spans="2:6">
       <c r="B281" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D281" s="5"/>
+        <v>189</v>
+      </c>
+      <c r="C281" s="3">
+        <v>100</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E281" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="282" spans="2:6">
@@ -5786,7 +5779,7 @@
       </c>
       <c r="D282" s="5"/>
       <c r="E282" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>80</v>
@@ -5794,31 +5787,31 @@
     </row>
     <row r="283" spans="2:6">
       <c r="B283" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C283" s="3">
-        <v>100</v>
-      </c>
-      <c r="D283" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D283" s="5"/>
       <c r="E283" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="284" spans="2:6">
       <c r="B284" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D284" s="5"/>
+        <v>190</v>
+      </c>
+      <c r="C284" s="3">
+        <v>100</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E284" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="285" spans="2:6">
@@ -5827,7 +5820,7 @@
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>80</v>
@@ -5835,31 +5828,31 @@
     </row>
     <row r="286" spans="2:6">
       <c r="B286" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C286" s="3">
-        <v>100</v>
-      </c>
-      <c r="D286" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D286" s="5"/>
       <c r="E286" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="287" spans="2:6">
       <c r="B287" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D287" s="5"/>
+        <v>191</v>
+      </c>
+      <c r="C287" s="3">
+        <v>100</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E287" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="288" spans="2:6">
@@ -5876,31 +5869,31 @@
     </row>
     <row r="289" spans="2:6">
       <c r="B289" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C289" s="3">
-        <v>100</v>
-      </c>
-      <c r="D289" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D289" s="5"/>
       <c r="E289" s="3" t="s">
         <v>39</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="290" spans="2:6">
       <c r="B290" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D290" s="5"/>
+        <v>192</v>
+      </c>
+      <c r="C290" s="3">
+        <v>100</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E290" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="291" spans="2:6">
@@ -5909,7 +5902,7 @@
       </c>
       <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F291" s="3" t="s">
         <v>80</v>
@@ -5917,31 +5910,31 @@
     </row>
     <row r="292" spans="2:6">
       <c r="B292" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C292" s="3">
-        <v>100</v>
-      </c>
-      <c r="D292" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D292" s="5"/>
       <c r="E292" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="293" spans="2:6">
       <c r="B293" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" s="5"/>
+        <v>193</v>
+      </c>
+      <c r="C293" s="3">
+        <v>100</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E293" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="294" spans="2:6">
@@ -5950,7 +5943,7 @@
       </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>80</v>
@@ -5958,58 +5951,67 @@
     </row>
     <row r="295" spans="2:6">
       <c r="B295" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C295" s="3">
-        <v>100</v>
-      </c>
-      <c r="D295" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D295" s="5"/>
       <c r="E295" s="3" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="296" spans="2:6">
       <c r="B296" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D296" s="5"/>
+        <v>194</v>
+      </c>
+      <c r="C296" s="3">
+        <v>100</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="E296" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="297" spans="2:6">
       <c r="B297" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C297" s="3">
-        <v>100</v>
-      </c>
-      <c r="D297" s="5" t="s">
-        <v>76</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D297" s="5"/>
       <c r="E297" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F297" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="298" spans="2:6">
+      <c r="B298" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C298" s="3">
+        <v>100</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E298" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F298" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="298" spans="4:5">
-      <c r="D298" s="5"/>
-      <c r="E298" s="3" t="s">
+    <row r="299" spans="4:5">
+      <c r="D299" s="5"/>
+      <c r="E299" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="299" spans="4:4">
-      <c r="D299" s="5"/>
     </row>
     <row r="300" spans="4:4">
       <c r="D300" s="5"/>
@@ -6062,10 +6064,13 @@
     <row r="316" spans="4:4">
       <c r="D316" s="5"/>
     </row>
+    <row r="317" spans="4:4">
+      <c r="D317" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="T33:T37"/>
-    <mergeCell ref="T39:T44"/>
+    <mergeCell ref="T34:T38"/>
+    <mergeCell ref="T40:T45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="129">
   <si>
     <t>##var</t>
   </si>
@@ -263,6 +263,9 @@
     <t/>
   </si>
   <si>
+    <t>60,100</t>
+  </si>
+  <si>
     <t>m_walnut</t>
   </si>
   <si>
@@ -329,39 +332,30 @@
     <t>樱桃木</t>
   </si>
   <si>
-    <t>分数+30</t>
+    <t>分数+60</t>
   </si>
   <si>
     <t>AddFlat</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>胡桃木</t>
   </si>
   <si>
-    <t>分数永久+10</t>
+    <t>分数永久+15</t>
   </si>
   <si>
     <t>PermanentAddFlat</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>大理石</t>
   </si>
   <si>
-    <t>倍率+3</t>
+    <t>倍率+2</t>
   </si>
   <si>
     <t>AddMultFlat</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>黑曜石</t>
   </si>
   <si>
@@ -378,13 +372,10 @@
   </si>
   <si>
     <t>每占 1 格翡翠
-倍率+0.3</t>
+倍率+0.8</t>
   </si>
   <si>
     <t>AddMultFlatPerCell</t>
-  </si>
-  <si>
-    <t>0.3</t>
   </si>
   <si>
     <t>金</t>
@@ -398,6 +389,9 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>银</t>
@@ -2113,10 +2107,11 @@
         <v>frag_4_1_m_cherry</v>
       </c>
       <c r="C48" s="3">
-        <v>1400</v>
+        <f>IF(B48="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>24</v>
@@ -2128,7 +2123,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="4:6">
+    <row r="49" spans="3:6">
+      <c r="C49" s="3" t="str">
+        <f t="shared" ref="C49:C112" si="0">IF(B49="","",50)</f>
+        <v/>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="3" t="s">
         <v>24</v>
@@ -2143,10 +2142,11 @@
         <v>frag_4_2_m_cherry</v>
       </c>
       <c r="C50" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>24</v>
@@ -2158,7 +2158,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="4:6">
+    <row r="51" spans="3:6">
+      <c r="C51" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D51" s="5"/>
       <c r="E51" s="3" t="s">
         <v>27</v>
@@ -2167,7 +2171,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="4:6">
+    <row r="52" spans="3:6">
+      <c r="C52" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D52" s="5"/>
       <c r="E52" s="3" t="s">
         <v>27</v>
@@ -2182,10 +2190,11 @@
         <v>frag_4_3_m_cherry</v>
       </c>
       <c r="C53" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>24</v>
@@ -2197,7 +2206,11 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="4:6">
+    <row r="54" spans="3:6">
+      <c r="C54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D54" s="5"/>
       <c r="E54" s="3" t="s">
         <v>29</v>
@@ -2206,7 +2219,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" spans="4:6">
+    <row r="55" spans="3:6">
+      <c r="C55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D55" s="5"/>
       <c r="E55" s="3" t="s">
         <v>29</v>
@@ -2221,10 +2238,11 @@
         <v>frag_4_4_m_cherry</v>
       </c>
       <c r="C56" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>29</v>
@@ -2236,7 +2254,11 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="4:6">
+    <row r="57" spans="3:6">
+      <c r="C57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D57" s="5"/>
       <c r="E57" s="3" t="s">
         <v>24</v>
@@ -2245,7 +2267,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58" spans="4:6">
+    <row r="58" spans="3:6">
+      <c r="C58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D58" s="5"/>
       <c r="E58" s="3" t="s">
         <v>27</v>
@@ -2260,10 +2286,11 @@
         <v>frag_4_5_m_cherry</v>
       </c>
       <c r="C59" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>27</v>
@@ -2275,7 +2302,11 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="4:6">
+    <row r="60" spans="3:6">
+      <c r="C60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D60" s="5"/>
       <c r="E60" s="3" t="s">
         <v>24</v>
@@ -2284,7 +2315,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61" spans="4:6">
+    <row r="61" spans="3:6">
+      <c r="C61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D61" s="5"/>
       <c r="E61" s="3" t="s">
         <v>29</v>
@@ -2299,10 +2334,11 @@
         <v>frag_4_6_m_cherry</v>
       </c>
       <c r="C62" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>22</v>
@@ -2314,7 +2350,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="4:6">
+    <row r="63" spans="3:6">
+      <c r="C63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D63" s="5"/>
       <c r="E63" s="3" t="s">
         <v>22</v>
@@ -2323,7 +2363,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64" spans="4:6">
+    <row r="64" spans="3:6">
+      <c r="C64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D64" s="5"/>
       <c r="E64" s="3" t="s">
         <v>22</v>
@@ -2332,7 +2376,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="4:6">
+    <row r="65" spans="3:6">
+      <c r="C65" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D65" s="5"/>
       <c r="E65" s="3" t="s">
         <v>22</v>
@@ -2347,10 +2395,11 @@
         <v>frag_5_1_m_cherry</v>
       </c>
       <c r="C66" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>19</v>
@@ -2362,7 +2411,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="5:6">
+    <row r="67" spans="3:6">
+      <c r="C67" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E67" s="3" t="s">
         <v>49</v>
       </c>
@@ -2376,10 +2429,11 @@
         <v>frag_5_2_m_cherry</v>
       </c>
       <c r="C68" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>19</v>
@@ -2391,7 +2445,11 @@
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="5:6">
+    <row r="69" spans="3:6">
+      <c r="C69" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E69" s="3" t="s">
         <v>53</v>
       </c>
@@ -2405,10 +2463,11 @@
         <v>frag_5_3_m_cherry</v>
       </c>
       <c r="C70" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>55</v>
@@ -2420,7 +2479,11 @@
         <v>54</v>
       </c>
     </row>
-    <row r="71" spans="5:6">
+    <row r="71" spans="3:6">
+      <c r="C71" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E71" s="3" t="s">
         <v>56</v>
       </c>
@@ -2434,10 +2497,11 @@
         <v>frag_5_4_m_cherry</v>
       </c>
       <c r="C72" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>55</v>
@@ -2449,7 +2513,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" spans="5:6">
+    <row r="73" spans="3:6">
+      <c r="C73" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E73" s="3" t="s">
         <v>59</v>
       </c>
@@ -2463,10 +2531,11 @@
         <v>frag_6_1_m_cherry</v>
       </c>
       <c r="C74" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>55</v>
@@ -2478,7 +2547,11 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="5:6">
+    <row r="75" spans="3:6">
+      <c r="C75" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E75" s="3" t="s">
         <v>55</v>
       </c>
@@ -2492,10 +2565,11 @@
         <v>frag_6_2_m_cherry</v>
       </c>
       <c r="C76" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>55</v>
@@ -2507,7 +2581,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="5:6">
+    <row r="77" spans="3:6">
+      <c r="C77" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E77" s="3" t="s">
         <v>59</v>
       </c>
@@ -2515,7 +2593,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="5:6">
+    <row r="78" spans="3:6">
+      <c r="C78" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E78" s="3" t="s">
         <v>67</v>
       </c>
@@ -2529,10 +2611,11 @@
         <v>frag_6_3_m_cherry</v>
       </c>
       <c r="C79" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>55</v>
@@ -2544,7 +2627,11 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="5:6">
+    <row r="80" spans="3:6">
+      <c r="C80" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E80" s="3" t="s">
         <v>56</v>
       </c>
@@ -2552,7 +2639,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="81" spans="5:6">
+    <row r="81" spans="3:6">
+      <c r="C81" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E81" s="3" t="s">
         <v>72</v>
       </c>
@@ -2562,14 +2653,15 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="3" t="str">
-        <f t="shared" ref="B82:B87" si="0">H82&amp;"_"&amp;F82</f>
+        <f t="shared" ref="B82:B87" si="1">H82&amp;"_"&amp;F82</f>
         <v>frag_8_1_m_cherry</v>
       </c>
       <c r="C82" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>19</v>
@@ -2581,7 +2673,11 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="5:7">
+    <row r="83" spans="3:7">
+      <c r="C83" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E83" s="3" t="s">
         <v>19</v>
       </c>
@@ -2592,14 +2688,15 @@
     </row>
     <row r="84" spans="2:8">
       <c r="B84" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>frag_9_1_m_cherry</v>
+      </c>
+      <c r="C84" s="3">
         <f t="shared" si="0"/>
-        <v>frag_9_1_m_cherry</v>
-      </c>
-      <c r="C84" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>55</v>
@@ -2611,12 +2708,20 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" spans="5:5">
+    <row r="85" spans="3:5">
+      <c r="C85" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E85" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="86" spans="5:6">
+    <row r="86" spans="3:6">
+      <c r="C86" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E86" s="3" t="s">
         <v>55</v>
       </c>
@@ -2627,26 +2732,31 @@
     </row>
     <row r="87" spans="2:8">
       <c r="B87" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>frag_4_1_m_walnut</v>
+      </c>
+      <c r="C87" s="3">
         <f t="shared" si="0"/>
-        <v>frag_4_1_m_walnut</v>
-      </c>
-      <c r="C87" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="4:6">
+    <row r="88" spans="3:6">
+      <c r="C88" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D88" s="5"/>
       <c r="E88" s="3" t="s">
         <v>24</v>
@@ -2661,22 +2771,27 @@
         <v>frag_4_2_m_walnut</v>
       </c>
       <c r="C89" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="90" spans="4:6">
+    <row r="90" spans="3:6">
+      <c r="C90" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D90" s="5"/>
       <c r="E90" s="3" t="s">
         <v>27</v>
@@ -2685,7 +2800,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="91" spans="4:6">
+    <row r="91" spans="3:6">
+      <c r="C91" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D91" s="5"/>
       <c r="E91" s="3" t="s">
         <v>27</v>
@@ -2700,22 +2819,27 @@
         <v>frag_4_3_m_walnut</v>
       </c>
       <c r="C92" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="4:6">
+    <row r="93" spans="3:6">
+      <c r="C93" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D93" s="5"/>
       <c r="E93" s="3" t="s">
         <v>29</v>
@@ -2724,7 +2848,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94" spans="4:6">
+    <row r="94" spans="3:6">
+      <c r="C94" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D94" s="5"/>
       <c r="E94" s="3" t="s">
         <v>29</v>
@@ -2739,22 +2867,27 @@
         <v>frag_4_4_m_walnut</v>
       </c>
       <c r="C95" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="4:6">
+    <row r="96" spans="3:6">
+      <c r="C96" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D96" s="5"/>
       <c r="E96" s="3" t="s">
         <v>24</v>
@@ -2763,7 +2896,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="4:6">
+    <row r="97" spans="3:6">
+      <c r="C97" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D97" s="5"/>
       <c r="E97" s="3" t="s">
         <v>27</v>
@@ -2778,22 +2915,27 @@
         <v>frag_4_5_m_walnut</v>
       </c>
       <c r="C98" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="4:6">
+    <row r="99" spans="3:6">
+      <c r="C99" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D99" s="5"/>
       <c r="E99" s="3" t="s">
         <v>24</v>
@@ -2802,7 +2944,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="100" spans="4:6">
+    <row r="100" spans="3:6">
+      <c r="C100" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D100" s="5"/>
       <c r="E100" s="3" t="s">
         <v>29</v>
@@ -2817,22 +2963,27 @@
         <v>frag_4_6_m_walnut</v>
       </c>
       <c r="C101" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="102" spans="4:6">
+    <row r="102" spans="3:6">
+      <c r="C102" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D102" s="5"/>
       <c r="E102" s="3" t="s">
         <v>22</v>
@@ -2841,7 +2992,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="103" spans="4:6">
+    <row r="103" spans="3:6">
+      <c r="C103" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D103" s="5"/>
       <c r="E103" s="3" t="s">
         <v>22</v>
@@ -2850,7 +3005,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="4:6">
+    <row r="104" spans="3:6">
+      <c r="C104" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="D104" s="5"/>
       <c r="E104" s="3" t="s">
         <v>22</v>
@@ -2861,26 +3020,31 @@
     </row>
     <row r="105" spans="2:8">
       <c r="B105" s="3" t="str">
-        <f t="shared" ref="B105:B109" si="1">H105&amp;"_"&amp;F105</f>
+        <f t="shared" ref="B105:B109" si="2">H105&amp;"_"&amp;F105</f>
         <v>frag_5_1_m_walnut</v>
       </c>
       <c r="C105" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="5:6">
+    <row r="106" spans="3:6">
+      <c r="C106" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E106" s="3" t="s">
         <v>49</v>
       </c>
@@ -2890,26 +3054,31 @@
     </row>
     <row r="107" spans="2:8">
       <c r="B107" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>frag_5_2_m_walnut</v>
       </c>
       <c r="C107" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="108" spans="5:6">
+    <row r="108" spans="3:6">
+      <c r="C108" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E108" s="3" t="s">
         <v>53</v>
       </c>
@@ -2919,26 +3088,31 @@
     </row>
     <row r="109" spans="2:8">
       <c r="B109" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>frag_5_3_m_walnut</v>
       </c>
       <c r="C109" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E109" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="5:6">
+    <row r="110" spans="3:6">
+      <c r="C110" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E110" s="3" t="s">
         <v>56</v>
       </c>
@@ -2948,26 +3122,31 @@
     </row>
     <row r="111" spans="2:8">
       <c r="B111" s="3" t="str">
-        <f t="shared" ref="B111:B115" si="2">H111&amp;"_"&amp;F111</f>
+        <f t="shared" ref="B111:B115" si="3">H111&amp;"_"&amp;F111</f>
         <v>frag_5_4_m_walnut</v>
       </c>
       <c r="C111" s="3">
-        <v>1400</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E111" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="5:6">
+    <row r="112" spans="3:6">
+      <c r="C112" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="E112" s="3" t="s">
         <v>59</v>
       </c>
@@ -2977,26 +3156,31 @@
     </row>
     <row r="113" spans="2:8">
       <c r="B113" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>frag_6_1_m_walnut</v>
       </c>
       <c r="C113" s="3">
-        <v>1400</v>
+        <f t="shared" ref="C113:C176" si="4">IF(B113="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="5:6">
+    <row r="114" spans="3:6">
+      <c r="C114" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E114" s="3" t="s">
         <v>55</v>
       </c>
@@ -3006,26 +3190,31 @@
     </row>
     <row r="115" spans="2:8">
       <c r="B115" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>frag_6_2_m_walnut</v>
       </c>
       <c r="C115" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="116" spans="5:6">
+    <row r="116" spans="3:6">
+      <c r="C116" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E116" s="3" t="s">
         <v>59</v>
       </c>
@@ -3033,7 +3222,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="117" spans="5:6">
+    <row r="117" spans="3:6">
+      <c r="C117" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E117" s="3" t="s">
         <v>67</v>
       </c>
@@ -3043,26 +3236,31 @@
     </row>
     <row r="118" spans="2:8">
       <c r="B118" s="3" t="str">
-        <f t="shared" ref="B118:B123" si="3">H118&amp;"_"&amp;F118</f>
+        <f t="shared" ref="B118:B123" si="5">H118&amp;"_"&amp;F118</f>
         <v>frag_6_3_m_walnut</v>
       </c>
       <c r="C118" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E118" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="119" spans="5:6">
+    <row r="119" spans="3:6">
+      <c r="C119" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E119" s="3" t="s">
         <v>56</v>
       </c>
@@ -3070,7 +3268,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="120" spans="5:6">
+    <row r="120" spans="3:6">
+      <c r="C120" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E120" s="3" t="s">
         <v>72</v>
       </c>
@@ -3080,30 +3282,34 @@
     </row>
     <row r="121" spans="2:8">
       <c r="B121" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>frag_8_1_m_walnut</v>
       </c>
       <c r="C121" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="122" spans="5:7">
+    <row r="122" spans="3:7">
+      <c r="C122" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E122" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F122" s="3"/>
       <c r="G122" s="3" t="str">
         <f>IF(B122="","",B122&amp;"_walnut")</f>
         <v/>
@@ -3111,31 +3317,40 @@
     </row>
     <row r="123" spans="2:8">
       <c r="B123" s="3" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>frag_9_1_m_walnut</v>
       </c>
       <c r="C123" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="124" spans="5:5">
+    <row r="124" spans="3:5">
+      <c r="C124" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E124" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="125" spans="5:6">
+    <row r="125" spans="3:6">
+      <c r="C125" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E125" s="3" t="s">
         <v>55</v>
       </c>
@@ -3146,26 +3361,31 @@
     </row>
     <row r="126" spans="2:8">
       <c r="B126" s="3" t="str">
-        <f t="shared" ref="B126:B131" si="4">H126&amp;"_"&amp;F126</f>
+        <f t="shared" ref="B126:B131" si="6">H126&amp;"_"&amp;F126</f>
         <v>frag_4_1_m_marble</v>
       </c>
       <c r="C126" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="127" spans="4:6">
+    <row r="127" spans="3:6">
+      <c r="C127" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D127" s="5"/>
       <c r="E127" s="3" t="s">
         <v>24</v>
@@ -3176,26 +3396,31 @@
     </row>
     <row r="128" spans="2:8">
       <c r="B128" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>frag_4_2_m_marble</v>
+      </c>
+      <c r="C128" s="3">
         <f t="shared" si="4"/>
-        <v>frag_4_2_m_marble</v>
-      </c>
-      <c r="C128" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H128" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="4:6">
+    <row r="129" spans="3:6">
+      <c r="C129" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D129" s="5"/>
       <c r="E129" s="3" t="s">
         <v>27</v>
@@ -3204,7 +3429,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="130" spans="4:6">
+    <row r="130" spans="3:6">
+      <c r="C130" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D130" s="5"/>
       <c r="E130" s="3" t="s">
         <v>27</v>
@@ -3215,26 +3444,31 @@
     </row>
     <row r="131" spans="2:8">
       <c r="B131" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>frag_4_3_m_marble</v>
+      </c>
+      <c r="C131" s="3">
         <f t="shared" si="4"/>
-        <v>frag_4_3_m_marble</v>
-      </c>
-      <c r="C131" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H131" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="4:6">
+    <row r="132" spans="3:6">
+      <c r="C132" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D132" s="5"/>
       <c r="E132" s="3" t="s">
         <v>29</v>
@@ -3243,7 +3477,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="133" spans="4:6">
+    <row r="133" spans="3:6">
+      <c r="C133" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D133" s="5"/>
       <c r="E133" s="3" t="s">
         <v>29</v>
@@ -3258,22 +3496,27 @@
         <v>frag_4_4_m_marble</v>
       </c>
       <c r="C134" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H134" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="135" spans="4:6">
+    <row r="135" spans="3:6">
+      <c r="C135" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D135" s="5"/>
       <c r="E135" s="3" t="s">
         <v>24</v>
@@ -3282,7 +3525,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="136" spans="4:6">
+    <row r="136" spans="3:6">
+      <c r="C136" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D136" s="5"/>
       <c r="E136" s="3" t="s">
         <v>27</v>
@@ -3297,22 +3544,27 @@
         <v>frag_4_5_m_marble</v>
       </c>
       <c r="C137" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H137" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="138" spans="4:6">
+    <row r="138" spans="3:6">
+      <c r="C138" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D138" s="5"/>
       <c r="E138" s="3" t="s">
         <v>24</v>
@@ -3321,7 +3573,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="139" spans="4:6">
+    <row r="139" spans="3:6">
+      <c r="C139" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D139" s="5"/>
       <c r="E139" s="3" t="s">
         <v>29</v>
@@ -3336,22 +3592,27 @@
         <v>frag_4_6_m_marble</v>
       </c>
       <c r="C140" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="4:6">
+    <row r="141" spans="3:6">
+      <c r="C141" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D141" s="5"/>
       <c r="E141" s="3" t="s">
         <v>22</v>
@@ -3360,7 +3621,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="142" spans="4:6">
+    <row r="142" spans="3:6">
+      <c r="C142" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D142" s="5"/>
       <c r="E142" s="3" t="s">
         <v>22</v>
@@ -3369,7 +3634,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="143" spans="4:6">
+    <row r="143" spans="3:6">
+      <c r="C143" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D143" s="5"/>
       <c r="E143" s="3" t="s">
         <v>22</v>
@@ -3380,26 +3649,31 @@
     </row>
     <row r="144" spans="2:8">
       <c r="B144" s="3" t="str">
-        <f t="shared" ref="B144:B148" si="5">H144&amp;"_"&amp;F144</f>
+        <f t="shared" ref="B144:B148" si="7">H144&amp;"_"&amp;F144</f>
         <v>frag_5_1_m_marble</v>
       </c>
       <c r="C144" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="5:6">
+    <row r="145" spans="3:6">
+      <c r="C145" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E145" s="3" t="s">
         <v>49</v>
       </c>
@@ -3409,26 +3683,31 @@
     </row>
     <row r="146" spans="2:8">
       <c r="B146" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>frag_5_2_m_marble</v>
       </c>
       <c r="C146" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="147" spans="5:6">
+    <row r="147" spans="3:6">
+      <c r="C147" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E147" s="3" t="s">
         <v>53</v>
       </c>
@@ -3438,26 +3717,31 @@
     </row>
     <row r="148" spans="2:8">
       <c r="B148" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>frag_5_3_m_marble</v>
       </c>
       <c r="C148" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="149" spans="5:6">
+    <row r="149" spans="3:6">
+      <c r="C149" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E149" s="3" t="s">
         <v>56</v>
       </c>
@@ -3467,26 +3751,31 @@
     </row>
     <row r="150" spans="2:8">
       <c r="B150" s="3" t="str">
-        <f t="shared" ref="B150:B154" si="6">H150&amp;"_"&amp;F150</f>
+        <f t="shared" ref="B150:B154" si="8">H150&amp;"_"&amp;F150</f>
         <v>frag_5_4_m_marble</v>
       </c>
       <c r="C150" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="151" spans="5:6">
+    <row r="151" spans="3:6">
+      <c r="C151" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E151" s="3" t="s">
         <v>59</v>
       </c>
@@ -3496,26 +3785,31 @@
     </row>
     <row r="152" spans="2:8">
       <c r="B152" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>frag_6_1_m_marble</v>
       </c>
       <c r="C152" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="5:6">
+    <row r="153" spans="3:6">
+      <c r="C153" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E153" s="3" t="s">
         <v>55</v>
       </c>
@@ -3525,26 +3819,31 @@
     </row>
     <row r="154" spans="2:8">
       <c r="B154" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>frag_6_2_m_marble</v>
       </c>
       <c r="C154" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D154" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H154" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="155" spans="5:6">
+    <row r="155" spans="3:6">
+      <c r="C155" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E155" s="3" t="s">
         <v>59</v>
       </c>
@@ -3552,7 +3851,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="156" spans="5:6">
+    <row r="156" spans="3:6">
+      <c r="C156" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E156" s="3" t="s">
         <v>67</v>
       </c>
@@ -3562,26 +3865,31 @@
     </row>
     <row r="157" spans="2:8">
       <c r="B157" s="3" t="str">
-        <f t="shared" ref="B157:B162" si="7">H157&amp;"_"&amp;F157</f>
+        <f t="shared" ref="B157:B162" si="9">H157&amp;"_"&amp;F157</f>
         <v>frag_6_3_m_marble</v>
       </c>
       <c r="C157" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H157" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="158" spans="5:6">
+    <row r="158" spans="3:6">
+      <c r="C158" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E158" s="3" t="s">
         <v>56</v>
       </c>
@@ -3589,7 +3897,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="159" spans="5:6">
+    <row r="159" spans="3:6">
+      <c r="C159" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E159" s="3" t="s">
         <v>72</v>
       </c>
@@ -3599,30 +3911,34 @@
     </row>
     <row r="160" spans="2:8">
       <c r="B160" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>frag_8_1_m_marble</v>
       </c>
       <c r="C160" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H160" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="161" spans="5:7">
+    <row r="161" spans="3:7">
+      <c r="C161" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E161" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F161" s="3"/>
       <c r="G161" s="3" t="str">
         <f>IF(B161="","",B161&amp;"_marble")</f>
         <v/>
@@ -3630,31 +3946,40 @@
     </row>
     <row r="162" spans="2:8">
       <c r="B162" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>frag_9_1_m_marble</v>
       </c>
       <c r="C162" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H162" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="163" spans="5:5">
+    <row r="163" spans="3:5">
+      <c r="C163" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E163" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="164" spans="5:6">
+    <row r="164" spans="3:6">
+      <c r="C164" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="E164" s="3" t="s">
         <v>55</v>
       </c>
@@ -3665,26 +3990,31 @@
     </row>
     <row r="165" spans="2:8">
       <c r="B165" s="3" t="str">
-        <f t="shared" ref="B165:B170" si="8">H165&amp;"_"&amp;F165</f>
+        <f t="shared" ref="B165:B170" si="10">H165&amp;"_"&amp;F165</f>
         <v>frag_4_1_m_obsidian</v>
       </c>
       <c r="C165" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H165" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="4:6">
+    <row r="166" spans="3:6">
+      <c r="C166" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D166" s="5"/>
       <c r="E166" s="3" t="s">
         <v>24</v>
@@ -3695,26 +4025,31 @@
     </row>
     <row r="167" spans="2:8">
       <c r="B167" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>frag_4_2_m_obsidian</v>
       </c>
       <c r="C167" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H167" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="168" spans="4:6">
+    <row r="168" spans="3:6">
+      <c r="C168" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D168" s="5"/>
       <c r="E168" s="3" t="s">
         <v>27</v>
@@ -3723,7 +4058,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="169" spans="4:6">
+    <row r="169" spans="3:6">
+      <c r="C169" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D169" s="5"/>
       <c r="E169" s="3" t="s">
         <v>27</v>
@@ -3734,26 +4073,31 @@
     </row>
     <row r="170" spans="2:8">
       <c r="B170" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>frag_4_3_m_obsidian</v>
       </c>
       <c r="C170" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H170" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="4:6">
+    <row r="171" spans="3:6">
+      <c r="C171" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D171" s="5"/>
       <c r="E171" s="3" t="s">
         <v>29</v>
@@ -3762,7 +4106,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="172" spans="4:6">
+    <row r="172" spans="3:6">
+      <c r="C172" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D172" s="5"/>
       <c r="E172" s="3" t="s">
         <v>29</v>
@@ -3777,22 +4125,27 @@
         <v>frag_4_4_m_obsidian</v>
       </c>
       <c r="C173" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H173" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="4:6">
+    <row r="174" spans="3:6">
+      <c r="C174" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D174" s="5"/>
       <c r="E174" s="3" t="s">
         <v>24</v>
@@ -3801,7 +4154,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="175" spans="4:6">
+    <row r="175" spans="3:6">
+      <c r="C175" s="3" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
       <c r="D175" s="5"/>
       <c r="E175" s="3" t="s">
         <v>27</v>
@@ -3816,22 +4173,27 @@
         <v>frag_4_5_m_obsidian</v>
       </c>
       <c r="C176" s="3">
-        <v>1400</v>
+        <f t="shared" si="4"/>
+        <v>50</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H176" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="177" spans="4:6">
+    <row r="177" spans="3:6">
+      <c r="C177" s="3" t="str">
+        <f t="shared" ref="C177:C240" si="11">IF(B177="","",50)</f>
+        <v/>
+      </c>
       <c r="D177" s="5"/>
       <c r="E177" s="3" t="s">
         <v>24</v>
@@ -3840,7 +4202,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="178" spans="4:6">
+    <row r="178" spans="3:6">
+      <c r="C178" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D178" s="5"/>
       <c r="E178" s="3" t="s">
         <v>29</v>
@@ -3855,22 +4221,27 @@
         <v>frag_4_6_m_obsidian</v>
       </c>
       <c r="C179" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H179" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="180" spans="4:6">
+    <row r="180" spans="3:6">
+      <c r="C180" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D180" s="5"/>
       <c r="E180" s="3" t="s">
         <v>22</v>
@@ -3879,7 +4250,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="181" spans="4:6">
+    <row r="181" spans="3:6">
+      <c r="C181" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D181" s="5"/>
       <c r="E181" s="3" t="s">
         <v>22</v>
@@ -3888,7 +4263,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="182" spans="4:6">
+    <row r="182" spans="3:6">
+      <c r="C182" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D182" s="5"/>
       <c r="E182" s="3" t="s">
         <v>22</v>
@@ -3899,26 +4278,31 @@
     </row>
     <row r="183" spans="2:8">
       <c r="B183" s="3" t="str">
-        <f t="shared" ref="B183:B187" si="9">H183&amp;"_"&amp;F183</f>
+        <f t="shared" ref="B183:B187" si="12">H183&amp;"_"&amp;F183</f>
         <v>frag_5_1_m_obsidian</v>
       </c>
       <c r="C183" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H183" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="184" spans="5:6">
+    <row r="184" spans="3:6">
+      <c r="C184" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E184" s="3" t="s">
         <v>49</v>
       </c>
@@ -3928,26 +4312,31 @@
     </row>
     <row r="185" spans="2:8">
       <c r="B185" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>frag_5_2_m_obsidian</v>
       </c>
       <c r="C185" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H185" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="5:6">
+    <row r="186" spans="3:6">
+      <c r="C186" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E186" s="3" t="s">
         <v>53</v>
       </c>
@@ -3957,26 +4346,31 @@
     </row>
     <row r="187" spans="2:8">
       <c r="B187" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>frag_5_3_m_obsidian</v>
       </c>
       <c r="C187" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H187" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="188" spans="5:6">
+    <row r="188" spans="3:6">
+      <c r="C188" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E188" s="3" t="s">
         <v>56</v>
       </c>
@@ -3986,26 +4380,31 @@
     </row>
     <row r="189" spans="2:8">
       <c r="B189" s="3" t="str">
-        <f t="shared" ref="B189:B193" si="10">H189&amp;"_"&amp;F189</f>
+        <f t="shared" ref="B189:B193" si="13">H189&amp;"_"&amp;F189</f>
         <v>frag_5_4_m_obsidian</v>
       </c>
       <c r="C189" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="190" spans="5:6">
+    <row r="190" spans="3:6">
+      <c r="C190" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E190" s="3" t="s">
         <v>59</v>
       </c>
@@ -4015,26 +4414,31 @@
     </row>
     <row r="191" spans="2:8">
       <c r="B191" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>frag_6_1_m_obsidian</v>
       </c>
       <c r="C191" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="5:6">
+    <row r="192" spans="3:6">
+      <c r="C192" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E192" s="3" t="s">
         <v>55</v>
       </c>
@@ -4044,26 +4448,31 @@
     </row>
     <row r="193" spans="2:8">
       <c r="B193" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>frag_6_2_m_obsidian</v>
       </c>
       <c r="C193" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="194" spans="5:6">
+    <row r="194" spans="3:6">
+      <c r="C194" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E194" s="3" t="s">
         <v>59</v>
       </c>
@@ -4071,7 +4480,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="195" spans="5:6">
+    <row r="195" spans="3:6">
+      <c r="C195" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E195" s="3" t="s">
         <v>67</v>
       </c>
@@ -4081,26 +4494,31 @@
     </row>
     <row r="196" spans="2:8">
       <c r="B196" s="3" t="str">
-        <f t="shared" ref="B196:B201" si="11">H196&amp;"_"&amp;F196</f>
+        <f t="shared" ref="B196:B201" si="14">H196&amp;"_"&amp;F196</f>
         <v>frag_6_3_m_obsidian</v>
       </c>
       <c r="C196" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H196" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="197" spans="5:6">
+    <row r="197" spans="3:6">
+      <c r="C197" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E197" s="3" t="s">
         <v>56</v>
       </c>
@@ -4108,7 +4526,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="198" spans="5:6">
+    <row r="198" spans="3:6">
+      <c r="C198" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E198" s="3" t="s">
         <v>72</v>
       </c>
@@ -4118,30 +4540,34 @@
     </row>
     <row r="199" spans="2:8">
       <c r="B199" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>frag_8_1_m_obsidian</v>
+      </c>
+      <c r="C199" s="3">
         <f t="shared" si="11"/>
-        <v>frag_8_1_m_obsidian</v>
-      </c>
-      <c r="C199" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="200" spans="5:7">
+    <row r="200" spans="3:7">
+      <c r="C200" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E200" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F200" s="3"/>
       <c r="G200" s="3" t="str">
         <f>IF(B200="","",B200&amp;"_obsidian")</f>
         <v/>
@@ -4149,31 +4575,40 @@
     </row>
     <row r="201" spans="2:8">
       <c r="B201" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>frag_9_1_m_obsidian</v>
+      </c>
+      <c r="C201" s="3">
         <f t="shared" si="11"/>
-        <v>frag_9_1_m_obsidian</v>
-      </c>
-      <c r="C201" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H201" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="202" spans="5:5">
+    <row r="202" spans="3:5">
+      <c r="C202" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E202" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="203" spans="5:6">
+    <row r="203" spans="3:6">
+      <c r="C203" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E203" s="3" t="s">
         <v>55</v>
       </c>
@@ -4184,26 +4619,31 @@
     </row>
     <row r="204" spans="2:8">
       <c r="B204" s="3" t="str">
-        <f t="shared" ref="B204:B209" si="12">H204&amp;"_"&amp;F204</f>
+        <f t="shared" ref="B204:B209" si="15">H204&amp;"_"&amp;F204</f>
         <v>frag_4_1_m_emerald</v>
       </c>
       <c r="C204" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="4:6">
+    <row r="205" spans="3:6">
+      <c r="C205" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D205" s="5"/>
       <c r="E205" s="3" t="s">
         <v>24</v>
@@ -4214,26 +4654,31 @@
     </row>
     <row r="206" spans="2:8">
       <c r="B206" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>frag_4_2_m_emerald</v>
       </c>
       <c r="C206" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="207" spans="4:6">
+    <row r="207" spans="3:6">
+      <c r="C207" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D207" s="5"/>
       <c r="E207" s="3" t="s">
         <v>27</v>
@@ -4242,7 +4687,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="208" spans="4:6">
+    <row r="208" spans="3:6">
+      <c r="C208" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D208" s="5"/>
       <c r="E208" s="3" t="s">
         <v>27</v>
@@ -4253,26 +4702,31 @@
     </row>
     <row r="209" spans="2:8">
       <c r="B209" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>frag_4_3_m_emerald</v>
       </c>
       <c r="C209" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="4:6">
+    <row r="210" spans="3:6">
+      <c r="C210" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D210" s="5"/>
       <c r="E210" s="3" t="s">
         <v>29</v>
@@ -4281,7 +4735,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="211" spans="4:6">
+    <row r="211" spans="3:6">
+      <c r="C211" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D211" s="5"/>
       <c r="E211" s="3" t="s">
         <v>29</v>
@@ -4296,22 +4754,27 @@
         <v>frag_4_4_m_emerald</v>
       </c>
       <c r="C212" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="4:6">
+    <row r="213" spans="3:6">
+      <c r="C213" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D213" s="5"/>
       <c r="E213" s="3" t="s">
         <v>24</v>
@@ -4320,7 +4783,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="214" spans="4:6">
+    <row r="214" spans="3:6">
+      <c r="C214" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D214" s="5"/>
       <c r="E214" s="3" t="s">
         <v>27</v>
@@ -4335,22 +4802,27 @@
         <v>frag_4_5_m_emerald</v>
       </c>
       <c r="C215" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="216" spans="4:6">
+    <row r="216" spans="3:6">
+      <c r="C216" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D216" s="5"/>
       <c r="E216" s="3" t="s">
         <v>24</v>
@@ -4359,7 +4831,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="217" spans="4:6">
+    <row r="217" spans="3:6">
+      <c r="C217" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D217" s="5"/>
       <c r="E217" s="3" t="s">
         <v>29</v>
@@ -4374,22 +4850,27 @@
         <v>frag_4_6_m_emerald</v>
       </c>
       <c r="C218" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F218" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="219" spans="4:6">
+    <row r="219" spans="3:6">
+      <c r="C219" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D219" s="5"/>
       <c r="E219" s="3" t="s">
         <v>22</v>
@@ -4398,7 +4879,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="220" spans="4:6">
+    <row r="220" spans="3:6">
+      <c r="C220" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D220" s="5"/>
       <c r="E220" s="3" t="s">
         <v>22</v>
@@ -4407,7 +4892,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="221" spans="4:6">
+    <row r="221" spans="3:6">
+      <c r="C221" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="D221" s="5"/>
       <c r="E221" s="3" t="s">
         <v>22</v>
@@ -4418,26 +4907,31 @@
     </row>
     <row r="222" spans="2:8">
       <c r="B222" s="3" t="str">
-        <f t="shared" ref="B222:B226" si="13">H222&amp;"_"&amp;F222</f>
+        <f t="shared" ref="B222:B226" si="16">H222&amp;"_"&amp;F222</f>
         <v>frag_5_1_m_emerald</v>
       </c>
       <c r="C222" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F222" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="223" spans="5:6">
+    <row r="223" spans="3:6">
+      <c r="C223" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E223" s="3" t="s">
         <v>49</v>
       </c>
@@ -4447,26 +4941,31 @@
     </row>
     <row r="224" spans="2:8">
       <c r="B224" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>frag_5_2_m_emerald</v>
       </c>
       <c r="C224" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H224" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="225" spans="5:6">
+    <row r="225" spans="3:6">
+      <c r="C225" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E225" s="3" t="s">
         <v>53</v>
       </c>
@@ -4476,26 +4975,31 @@
     </row>
     <row r="226" spans="2:8">
       <c r="B226" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>frag_5_3_m_emerald</v>
       </c>
       <c r="C226" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H226" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="227" spans="5:6">
+    <row r="227" spans="3:6">
+      <c r="C227" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E227" s="3" t="s">
         <v>56</v>
       </c>
@@ -4505,26 +5009,31 @@
     </row>
     <row r="228" spans="2:8">
       <c r="B228" s="3" t="str">
-        <f t="shared" ref="B228:B232" si="14">H228&amp;"_"&amp;F228</f>
+        <f t="shared" ref="B228:B232" si="17">H228&amp;"_"&amp;F228</f>
         <v>frag_5_4_m_emerald</v>
       </c>
       <c r="C228" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H228" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="229" spans="5:6">
+    <row r="229" spans="3:6">
+      <c r="C229" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E229" s="3" t="s">
         <v>59</v>
       </c>
@@ -4534,26 +5043,31 @@
     </row>
     <row r="230" spans="2:8">
       <c r="B230" s="3" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>frag_6_1_m_emerald</v>
       </c>
       <c r="C230" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="231" spans="5:6">
+    <row r="231" spans="3:6">
+      <c r="C231" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E231" s="3" t="s">
         <v>55</v>
       </c>
@@ -4563,26 +5077,31 @@
     </row>
     <row r="232" spans="2:8">
       <c r="B232" s="3" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>frag_6_2_m_emerald</v>
       </c>
       <c r="C232" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="233" spans="5:6">
+    <row r="233" spans="3:6">
+      <c r="C233" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E233" s="3" t="s">
         <v>59</v>
       </c>
@@ -4590,7 +5109,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="234" spans="5:6">
+    <row r="234" spans="3:6">
+      <c r="C234" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E234" s="3" t="s">
         <v>67</v>
       </c>
@@ -4600,26 +5123,31 @@
     </row>
     <row r="235" spans="2:8">
       <c r="B235" s="3" t="str">
-        <f t="shared" ref="B235:B240" si="15">H235&amp;"_"&amp;F235</f>
+        <f t="shared" ref="B235:B240" si="18">H235&amp;"_"&amp;F235</f>
         <v>frag_6_3_m_emerald</v>
       </c>
       <c r="C235" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="236" spans="5:6">
+    <row r="236" spans="3:6">
+      <c r="C236" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E236" s="3" t="s">
         <v>56</v>
       </c>
@@ -4627,7 +5155,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="237" spans="5:6">
+    <row r="237" spans="3:6">
+      <c r="C237" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E237" s="3" t="s">
         <v>72</v>
       </c>
@@ -4637,30 +5169,34 @@
     </row>
     <row r="238" spans="2:8">
       <c r="B238" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>frag_8_1_m_emerald</v>
       </c>
       <c r="C238" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="239" spans="5:7">
+    <row r="239" spans="3:7">
+      <c r="C239" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
       <c r="E239" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F239" s="3"/>
       <c r="G239" s="3" t="str">
         <f>IF(B239="","",B239&amp;"_emerald")</f>
         <v/>
@@ -4668,31 +5204,40 @@
     </row>
     <row r="240" spans="2:8">
       <c r="B240" s="3" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>frag_9_1_m_emerald</v>
       </c>
       <c r="C240" s="3">
-        <v>1400</v>
+        <f t="shared" si="11"/>
+        <v>50</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="241" spans="5:5">
+    <row r="241" spans="3:5">
+      <c r="C241" s="3" t="str">
+        <f t="shared" ref="C241:C304" si="19">IF(B241="","",50)</f>
+        <v/>
+      </c>
       <c r="E241" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="242" spans="5:6">
+    <row r="242" spans="3:6">
+      <c r="C242" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E242" s="3" t="s">
         <v>55</v>
       </c>
@@ -4703,26 +5248,31 @@
     </row>
     <row r="243" spans="2:8">
       <c r="B243" s="3" t="str">
-        <f t="shared" ref="B243:B248" si="16">H243&amp;"_"&amp;F243</f>
+        <f t="shared" ref="B243:B248" si="20">H243&amp;"_"&amp;F243</f>
         <v>frag_4_1_m_gold</v>
       </c>
       <c r="C243" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F243" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="244" spans="4:6">
+    <row r="244" spans="3:6">
+      <c r="C244" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D244" s="5"/>
       <c r="E244" s="3" t="s">
         <v>24</v>
@@ -4733,26 +5283,31 @@
     </row>
     <row r="245" spans="2:8">
       <c r="B245" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>frag_4_2_m_gold</v>
       </c>
       <c r="C245" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="246" spans="4:6">
+    <row r="246" spans="3:6">
+      <c r="C246" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D246" s="5"/>
       <c r="E246" s="3" t="s">
         <v>27</v>
@@ -4761,7 +5316,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="247" spans="4:6">
+    <row r="247" spans="3:6">
+      <c r="C247" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D247" s="5"/>
       <c r="E247" s="3" t="s">
         <v>27</v>
@@ -4772,26 +5331,31 @@
     </row>
     <row r="248" spans="2:8">
       <c r="B248" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>frag_4_3_m_gold</v>
       </c>
       <c r="C248" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="249" spans="4:6">
+    <row r="249" spans="3:6">
+      <c r="C249" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D249" s="5"/>
       <c r="E249" s="3" t="s">
         <v>29</v>
@@ -4800,7 +5364,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="250" spans="4:6">
+    <row r="250" spans="3:6">
+      <c r="C250" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D250" s="5"/>
       <c r="E250" s="3" t="s">
         <v>29</v>
@@ -4815,22 +5383,27 @@
         <v>frag_4_4_m_gold</v>
       </c>
       <c r="C251" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="252" spans="4:6">
+    <row r="252" spans="3:6">
+      <c r="C252" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D252" s="5"/>
       <c r="E252" s="3" t="s">
         <v>24</v>
@@ -4839,7 +5412,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="253" spans="4:6">
+    <row r="253" spans="3:6">
+      <c r="C253" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D253" s="5"/>
       <c r="E253" s="3" t="s">
         <v>27</v>
@@ -4854,22 +5431,27 @@
         <v>frag_4_5_m_gold</v>
       </c>
       <c r="C254" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="255" spans="4:6">
+    <row r="255" spans="3:6">
+      <c r="C255" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D255" s="5"/>
       <c r="E255" s="3" t="s">
         <v>24</v>
@@ -4878,7 +5460,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="256" spans="4:6">
+    <row r="256" spans="3:6">
+      <c r="C256" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D256" s="5"/>
       <c r="E256" s="3" t="s">
         <v>29</v>
@@ -4893,22 +5479,27 @@
         <v>frag_4_6_m_gold</v>
       </c>
       <c r="C257" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="258" spans="4:6">
+    <row r="258" spans="3:6">
+      <c r="C258" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D258" s="5"/>
       <c r="E258" s="3" t="s">
         <v>22</v>
@@ -4917,7 +5508,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="259" spans="4:6">
+    <row r="259" spans="3:6">
+      <c r="C259" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D259" s="5"/>
       <c r="E259" s="3" t="s">
         <v>22</v>
@@ -4926,7 +5521,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="4:6">
+    <row r="260" spans="3:6">
+      <c r="C260" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D260" s="5"/>
       <c r="E260" s="3" t="s">
         <v>22</v>
@@ -4937,26 +5536,31 @@
     </row>
     <row r="261" spans="2:8">
       <c r="B261" s="3" t="str">
-        <f t="shared" ref="B261:B265" si="17">H261&amp;"_"&amp;F261</f>
+        <f t="shared" ref="B261:B265" si="21">H261&amp;"_"&amp;F261</f>
         <v>frag_5_1_m_gold</v>
       </c>
       <c r="C261" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="262" spans="5:6">
+    <row r="262" spans="3:6">
+      <c r="C262" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E262" s="3" t="s">
         <v>49</v>
       </c>
@@ -4966,26 +5570,31 @@
     </row>
     <row r="263" spans="2:8">
       <c r="B263" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>frag_5_2_m_gold</v>
       </c>
       <c r="C263" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="264" spans="5:6">
+    <row r="264" spans="3:6">
+      <c r="C264" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E264" s="3" t="s">
         <v>53</v>
       </c>
@@ -4995,26 +5604,31 @@
     </row>
     <row r="265" spans="2:8">
       <c r="B265" s="3" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>frag_5_3_m_gold</v>
       </c>
       <c r="C265" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="266" spans="5:6">
+    <row r="266" spans="3:6">
+      <c r="C266" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E266" s="3" t="s">
         <v>56</v>
       </c>
@@ -5024,26 +5638,31 @@
     </row>
     <row r="267" spans="2:8">
       <c r="B267" s="3" t="str">
-        <f t="shared" ref="B267:B271" si="18">H267&amp;"_"&amp;F267</f>
+        <f t="shared" ref="B267:B271" si="22">H267&amp;"_"&amp;F267</f>
         <v>frag_5_4_m_gold</v>
       </c>
       <c r="C267" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="268" spans="5:6">
+    <row r="268" spans="3:6">
+      <c r="C268" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E268" s="3" t="s">
         <v>59</v>
       </c>
@@ -5053,26 +5672,31 @@
     </row>
     <row r="269" spans="2:8">
       <c r="B269" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>frag_6_1_m_gold</v>
       </c>
       <c r="C269" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="270" spans="5:6">
+    <row r="270" spans="3:6">
+      <c r="C270" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E270" s="3" t="s">
         <v>55</v>
       </c>
@@ -5082,26 +5706,31 @@
     </row>
     <row r="271" spans="2:8">
       <c r="B271" s="3" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>frag_6_2_m_gold</v>
       </c>
       <c r="C271" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>62</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="272" spans="5:6">
+    <row r="272" spans="3:6">
+      <c r="C272" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E272" s="3" t="s">
         <v>59</v>
       </c>
@@ -5109,7 +5738,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="273" spans="5:6">
+    <row r="273" spans="3:6">
+      <c r="C273" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E273" s="3" t="s">
         <v>67</v>
       </c>
@@ -5119,26 +5752,31 @@
     </row>
     <row r="274" spans="2:8">
       <c r="B274" s="3" t="str">
-        <f t="shared" ref="B274:B279" si="19">H274&amp;"_"&amp;F274</f>
+        <f t="shared" ref="B274:B279" si="23">H274&amp;"_"&amp;F274</f>
         <v>frag_6_3_m_gold</v>
       </c>
       <c r="C274" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="275" spans="5:6">
+    <row r="275" spans="3:6">
+      <c r="C275" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E275" s="3" t="s">
         <v>56</v>
       </c>
@@ -5146,7 +5784,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="276" spans="5:6">
+    <row r="276" spans="3:6">
+      <c r="C276" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E276" s="3" t="s">
         <v>72</v>
       </c>
@@ -5156,30 +5798,34 @@
     </row>
     <row r="277" spans="2:8">
       <c r="B277" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>frag_8_1_m_gold</v>
+      </c>
+      <c r="C277" s="3">
         <f t="shared" si="19"/>
-        <v>frag_8_1_m_gold</v>
-      </c>
-      <c r="C277" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="278" spans="5:7">
+    <row r="278" spans="3:7">
+      <c r="C278" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E278" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F278" s="3"/>
       <c r="G278" s="3" t="str">
         <f>IF(B278="","",B278&amp;"_gold")</f>
         <v/>
@@ -5187,31 +5833,40 @@
     </row>
     <row r="279" spans="2:8">
       <c r="B279" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v>frag_9_1_m_gold</v>
+      </c>
+      <c r="C279" s="3">
         <f t="shared" si="19"/>
-        <v>frag_9_1_m_gold</v>
-      </c>
-      <c r="C279" s="3">
-        <v>1400</v>
+        <v>50</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="280" spans="5:5">
+    <row r="280" spans="3:5">
+      <c r="C280" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E280" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="281" spans="5:6">
+    <row r="281" spans="3:6">
+      <c r="C281" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E281" s="3" t="s">
         <v>55</v>
       </c>
@@ -5222,26 +5877,31 @@
     </row>
     <row r="282" spans="2:8">
       <c r="B282" s="3" t="str">
-        <f t="shared" ref="B282:B287" si="20">H282&amp;"_"&amp;F282</f>
+        <f t="shared" ref="B282:B287" si="24">H282&amp;"_"&amp;F282</f>
         <v>frag_4_1_m_silver</v>
       </c>
       <c r="C282" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="283" spans="4:6">
+    <row r="283" spans="3:6">
+      <c r="C283" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D283" s="5"/>
       <c r="E283" s="3" t="s">
         <v>24</v>
@@ -5252,26 +5912,31 @@
     </row>
     <row r="284" spans="2:8">
       <c r="B284" s="3" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>frag_4_2_m_silver</v>
       </c>
       <c r="C284" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="285" spans="4:6">
+    <row r="285" spans="3:6">
+      <c r="C285" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D285" s="5"/>
       <c r="E285" s="3" t="s">
         <v>27</v>
@@ -5280,7 +5945,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="286" spans="4:6">
+    <row r="286" spans="3:6">
+      <c r="C286" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D286" s="5"/>
       <c r="E286" s="3" t="s">
         <v>27</v>
@@ -5291,26 +5960,31 @@
     </row>
     <row r="287" spans="2:8">
       <c r="B287" s="3" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>frag_4_3_m_silver</v>
       </c>
       <c r="C287" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="288" spans="4:6">
+    <row r="288" spans="3:6">
+      <c r="C288" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D288" s="5"/>
       <c r="E288" s="3" t="s">
         <v>29</v>
@@ -5319,7 +5993,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="289" spans="4:6">
+    <row r="289" spans="3:6">
+      <c r="C289" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D289" s="5"/>
       <c r="E289" s="3" t="s">
         <v>29</v>
@@ -5334,22 +6012,27 @@
         <v>frag_4_4_m_silver</v>
       </c>
       <c r="C290" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>29</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="291" spans="4:6">
+    <row r="291" spans="3:6">
+      <c r="C291" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D291" s="5"/>
       <c r="E291" s="3" t="s">
         <v>24</v>
@@ -5358,7 +6041,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="292" spans="4:6">
+    <row r="292" spans="3:6">
+      <c r="C292" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D292" s="5"/>
       <c r="E292" s="3" t="s">
         <v>27</v>
@@ -5373,22 +6060,27 @@
         <v>frag_4_5_m_silver</v>
       </c>
       <c r="C293" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="294" spans="4:6">
+    <row r="294" spans="3:6">
+      <c r="C294" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D294" s="5"/>
       <c r="E294" s="3" t="s">
         <v>24</v>
@@ -5397,7 +6089,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="295" spans="4:6">
+    <row r="295" spans="3:6">
+      <c r="C295" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D295" s="5"/>
       <c r="E295" s="3" t="s">
         <v>29</v>
@@ -5412,22 +6108,27 @@
         <v>frag_4_6_m_silver</v>
       </c>
       <c r="C296" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="297" spans="4:6">
+    <row r="297" spans="3:6">
+      <c r="C297" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D297" s="5"/>
       <c r="E297" s="3" t="s">
         <v>22</v>
@@ -5436,7 +6137,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="298" spans="4:6">
+    <row r="298" spans="3:6">
+      <c r="C298" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D298" s="5"/>
       <c r="E298" s="3" t="s">
         <v>22</v>
@@ -5445,7 +6150,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="299" spans="4:6">
+    <row r="299" spans="3:6">
+      <c r="C299" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="D299" s="5"/>
       <c r="E299" s="3" t="s">
         <v>22</v>
@@ -5456,26 +6165,31 @@
     </row>
     <row r="300" spans="2:8">
       <c r="B300" s="3" t="str">
-        <f t="shared" ref="B300:B304" si="21">H300&amp;"_"&amp;F300</f>
+        <f t="shared" ref="B300:B304" si="25">H300&amp;"_"&amp;F300</f>
         <v>frag_5_1_m_silver</v>
       </c>
       <c r="C300" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="301" spans="5:6">
+    <row r="301" spans="3:6">
+      <c r="C301" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E301" s="3" t="s">
         <v>49</v>
       </c>
@@ -5485,26 +6199,31 @@
     </row>
     <row r="302" spans="2:8">
       <c r="B302" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>frag_5_2_m_silver</v>
       </c>
       <c r="C302" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H302" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="303" spans="5:6">
+    <row r="303" spans="3:6">
+      <c r="C303" s="3" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
       <c r="E303" s="3" t="s">
         <v>53</v>
       </c>
@@ -5514,26 +6233,31 @@
     </row>
     <row r="304" spans="2:8">
       <c r="B304" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v>frag_5_3_m_silver</v>
       </c>
       <c r="C304" s="3">
-        <v>1400</v>
+        <f t="shared" si="19"/>
+        <v>50</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H304" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="305" spans="5:6">
+    <row r="305" spans="3:6">
+      <c r="C305" s="3" t="str">
+        <f>IF(B305="","",50)</f>
+        <v/>
+      </c>
       <c r="E305" s="3" t="s">
         <v>56</v>
       </c>
@@ -5543,26 +6267,31 @@
     </row>
     <row r="306" spans="2:8">
       <c r="B306" s="3" t="str">
-        <f t="shared" ref="B306:B310" si="22">H306&amp;"_"&amp;F306</f>
+        <f t="shared" ref="B306:B310" si="26">H306&amp;"_"&amp;F306</f>
         <v>frag_5_4_m_silver</v>
       </c>
       <c r="C306" s="3">
-        <v>1400</v>
+        <f>IF(B306="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="307" spans="5:6">
+    <row r="307" spans="3:6">
+      <c r="C307" s="3" t="str">
+        <f>IF(B307="","",50)</f>
+        <v/>
+      </c>
       <c r="E307" s="3" t="s">
         <v>59</v>
       </c>
@@ -5572,26 +6301,31 @@
     </row>
     <row r="308" spans="2:8">
       <c r="B308" s="3" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>frag_6_1_m_silver</v>
       </c>
       <c r="C308" s="3">
-        <v>1400</v>
+        <f>IF(B308="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H308" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="309" spans="5:6">
+    <row r="309" spans="3:6">
+      <c r="C309" s="3" t="str">
+        <f>IF(B309="","",50)</f>
+        <v/>
+      </c>
       <c r="E309" s="3" t="s">
         <v>55</v>
       </c>
@@ -5601,26 +6335,31 @@
     </row>
     <row r="310" spans="2:8">
       <c r="B310" s="3" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v>frag_6_2_m_silver</v>
       </c>
       <c r="C310" s="3">
-        <v>1400</v>
-      </c>
-      <c r="D310" s="5" t="s">
-        <v>62</v>
+        <f>IF(B310="","",50)</f>
+        <v>50</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H310" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="311" spans="5:6">
+    <row r="311" spans="3:6">
+      <c r="C311" s="3" t="str">
+        <f>IF(B311="","",50)</f>
+        <v/>
+      </c>
       <c r="E311" s="3" t="s">
         <v>59</v>
       </c>
@@ -5628,7 +6367,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="312" spans="5:6">
+    <row r="312" spans="3:6">
+      <c r="C312" s="3" t="str">
+        <f>IF(B312="","",50)</f>
+        <v/>
+      </c>
       <c r="E312" s="3" t="s">
         <v>67</v>
       </c>
@@ -5638,26 +6381,31 @@
     </row>
     <row r="313" spans="2:8">
       <c r="B313" s="3" t="str">
-        <f t="shared" ref="B313:B318" si="23">H313&amp;"_"&amp;F313</f>
+        <f t="shared" ref="B313:B318" si="27">H313&amp;"_"&amp;F313</f>
         <v>frag_6_3_m_silver</v>
       </c>
       <c r="C313" s="3">
-        <v>1400</v>
+        <f>IF(B313="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="314" spans="5:6">
+    <row r="314" spans="3:6">
+      <c r="C314" s="3" t="str">
+        <f>IF(B314="","",50)</f>
+        <v/>
+      </c>
       <c r="E314" s="3" t="s">
         <v>56</v>
       </c>
@@ -5665,7 +6413,11 @@
         <v>81</v>
       </c>
     </row>
-    <row r="315" spans="5:6">
+    <row r="315" spans="3:6">
+      <c r="C315" s="3" t="str">
+        <f>IF(B315="","",50)</f>
+        <v/>
+      </c>
       <c r="E315" s="3" t="s">
         <v>72</v>
       </c>
@@ -5675,26 +6427,31 @@
     </row>
     <row r="316" spans="2:8">
       <c r="B316" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>frag_8_1_m_silver</v>
       </c>
       <c r="C316" s="3">
-        <v>1400</v>
+        <f>IF(B316="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H316" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="317" spans="5:7">
+    <row r="317" spans="3:7">
+      <c r="C317" s="3" t="str">
+        <f>IF(B317="","",50)</f>
+        <v/>
+      </c>
       <c r="E317" s="3" t="s">
         <v>19</v>
       </c>
@@ -5705,20 +6462,21 @@
     </row>
     <row r="318" spans="2:8">
       <c r="B318" s="3" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v>frag_9_1_m_silver</v>
       </c>
       <c r="C318" s="3">
-        <v>1400</v>
+        <f>IF(B318="","",50)</f>
+        <v>50</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H318" s="3" t="s">
         <v>78</v>
@@ -5774,22 +6532,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5797,25 +6555,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5832,13 +6590,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -5849,21 +6607,21 @@
         <v>80</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
         <v>106</v>
+      </c>
+      <c r="G4" s="1">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>107</v>
@@ -5874,99 +6632,99 @@
       <c r="E5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>110</v>
+      <c r="G5" s="1">
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>114</v>
+      <c r="G6" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>122</v>
+      <c r="G8" s="1">
+        <v>0.8</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="G9" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="1"/>
+    <workbookView windowHeight="15280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -382,7 +382,7 @@
   </si>
   <si>
     <t>占据 2 格金餐桌时
-+ 10 金币</t>
++ 15 金币</t>
   </si>
   <si>
     <t>GrantGoldIfCellCount</t>
@@ -398,7 +398,7 @@
   </si>
   <si>
     <t>占据 2 格银餐桌时
-1/3 概率获得主动道具</t>
+1/2 概率获得主动道具</t>
   </si>
   <si>
     <t>GrantItemRollIfCellCount</t>
@@ -6255,7 +6255,7 @@
     </row>
     <row r="305" spans="3:6">
       <c r="C305" s="3" t="str">
-        <f>IF(B305="","",50)</f>
+        <f t="shared" ref="C305:C318" si="26">IF(B305="","",50)</f>
         <v/>
       </c>
       <c r="E305" s="3" t="s">
@@ -6267,11 +6267,11 @@
     </row>
     <row r="306" spans="2:8">
       <c r="B306" s="3" t="str">
-        <f t="shared" ref="B306:B310" si="26">H306&amp;"_"&amp;F306</f>
+        <f t="shared" ref="B306:B310" si="27">H306&amp;"_"&amp;F306</f>
         <v>frag_5_4_m_silver</v>
       </c>
       <c r="C306" s="3">
-        <f>IF(B306="","",50)</f>
+        <f t="shared" si="26"/>
         <v>50</v>
       </c>
       <c r="D306" s="4" t="s">
@@ -6289,7 +6289,7 @@
     </row>
     <row r="307" spans="3:6">
       <c r="C307" s="3" t="str">
-        <f>IF(B307="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E307" s="3" t="s">
@@ -6301,11 +6301,11 @@
     </row>
     <row r="308" spans="2:8">
       <c r="B308" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>frag_6_1_m_silver</v>
+      </c>
+      <c r="C308" s="3">
         <f t="shared" si="26"/>
-        <v>frag_6_1_m_silver</v>
-      </c>
-      <c r="C308" s="3">
-        <f>IF(B308="","",50)</f>
         <v>50</v>
       </c>
       <c r="D308" s="4" t="s">
@@ -6323,7 +6323,7 @@
     </row>
     <row r="309" spans="3:6">
       <c r="C309" s="3" t="str">
-        <f>IF(B309="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E309" s="3" t="s">
@@ -6335,11 +6335,11 @@
     </row>
     <row r="310" spans="2:8">
       <c r="B310" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>frag_6_2_m_silver</v>
+      </c>
+      <c r="C310" s="3">
         <f t="shared" si="26"/>
-        <v>frag_6_2_m_silver</v>
-      </c>
-      <c r="C310" s="3">
-        <f>IF(B310="","",50)</f>
         <v>50</v>
       </c>
       <c r="D310" s="4" t="s">
@@ -6357,7 +6357,7 @@
     </row>
     <row r="311" spans="3:6">
       <c r="C311" s="3" t="str">
-        <f>IF(B311="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E311" s="3" t="s">
@@ -6369,7 +6369,7 @@
     </row>
     <row r="312" spans="3:6">
       <c r="C312" s="3" t="str">
-        <f>IF(B312="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E312" s="3" t="s">
@@ -6381,11 +6381,11 @@
     </row>
     <row r="313" spans="2:8">
       <c r="B313" s="3" t="str">
-        <f t="shared" ref="B313:B318" si="27">H313&amp;"_"&amp;F313</f>
+        <f t="shared" ref="B313:B318" si="28">H313&amp;"_"&amp;F313</f>
         <v>frag_6_3_m_silver</v>
       </c>
       <c r="C313" s="3">
-        <f>IF(B313="","",50)</f>
+        <f t="shared" si="26"/>
         <v>50</v>
       </c>
       <c r="D313" s="4" t="s">
@@ -6403,7 +6403,7 @@
     </row>
     <row r="314" spans="3:6">
       <c r="C314" s="3" t="str">
-        <f>IF(B314="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E314" s="3" t="s">
@@ -6415,7 +6415,7 @@
     </row>
     <row r="315" spans="3:6">
       <c r="C315" s="3" t="str">
-        <f>IF(B315="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E315" s="3" t="s">
@@ -6427,11 +6427,11 @@
     </row>
     <row r="316" spans="2:8">
       <c r="B316" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>frag_8_1_m_silver</v>
       </c>
       <c r="C316" s="3">
-        <f>IF(B316="","",50)</f>
+        <f t="shared" si="26"/>
         <v>50</v>
       </c>
       <c r="D316" s="4" t="s">
@@ -6449,7 +6449,7 @@
     </row>
     <row r="317" spans="3:7">
       <c r="C317" s="3" t="str">
-        <f>IF(B317="","",50)</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="E317" s="3" t="s">
@@ -6462,11 +6462,11 @@
     </row>
     <row r="318" spans="2:8">
       <c r="B318" s="3" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>frag_9_1_m_silver</v>
       </c>
       <c r="C318" s="3">
-        <f>IF(B318="","",50)</f>
+        <f t="shared" si="26"/>
         <v>50</v>
       </c>
       <c r="D318" s="4" t="s">

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_fragment" sheetId="1" r:id="R9c1b132835384bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material" sheetId="2" r:id="R352c7f6dc9c34c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="table_fragment" sheetId="1" r:id="Rdf25d099755f46e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material" sheetId="2" r:id="Ra61d7e5b23a5478f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -329,17 +329,10 @@
     <x:t xml:space="preserve">金</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">占据 2 格金餐桌时
-+ 15 金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">GrantGoldIfCellCount</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">银</x:t>
@@ -6610,17 +6603,18 @@
       <x:c r="C9" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D9" s="2" t="s">
+      <x:c r="D9" s="2" t="str">
+        <x:v>占据 2 格金餐桌时
++15 金币</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
+      <x:c r="F9" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="F9" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>109</x:v>
+      <x:c r="G9" s="1" t="n">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34">
@@ -6628,20 +6622,20 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
         <x:v>占据 2 格银餐桌时
 1/2 概率获得消耗品</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="1"/>
+    <workbookView windowHeight="15160"/>
   </bookViews>
   <sheets>
     <sheet name="table_fragment" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="129">
   <si>
     <t>##var</t>
   </si>
@@ -113,7 +113,7 @@
     <t>frag_4_1</t>
   </si>
   <si>
-    <t>24,100</t>
+    <t>30,100</t>
   </si>
   <si>
     <t>frag_4_2</t>
@@ -125,9 +125,6 @@
     <t>frag_4_3</t>
   </si>
   <si>
-    <t>0 周</t>
-  </si>
-  <si>
     <t>1 周</t>
   </si>
   <si>
@@ -140,9 +137,6 @@
     <t>3 周</t>
   </si>
   <si>
-    <t>4 周</t>
-  </si>
-  <si>
     <t>frag_4_5</t>
   </si>
   <si>
@@ -176,100 +170,100 @@
     <t>frag_5_1</t>
   </si>
   <si>
+    <t>50,100</t>
+  </si>
+  <si>
+    <t>利息</t>
+  </si>
+  <si>
+    <t>X...</t>
+  </si>
+  <si>
+    <t>4～9</t>
+  </si>
+  <si>
+    <t>boss</t>
+  </si>
+  <si>
+    <t>frag_5_2</t>
+  </si>
+  <si>
+    <t>...X</t>
+  </si>
+  <si>
+    <t>frag_5_3</t>
+  </si>
+  <si>
+    <t>XX.</t>
+  </si>
+  <si>
+    <t>frag_5_4</t>
+  </si>
+  <si>
+    <t>❤️❤️❤️</t>
+  </si>
+  <si>
+    <t>.XX</t>
+  </si>
+  <si>
+    <t>普通事件</t>
+  </si>
+  <si>
+    <t>frag_6_1</t>
+  </si>
+  <si>
+    <t>强化类消耗品n选1</t>
+  </si>
+  <si>
+    <t>调整类消耗品n选1</t>
+  </si>
+  <si>
+    <t>frag_6_2</t>
+  </si>
+  <si>
+    <t>事件（有好有坏）</t>
+  </si>
+  <si>
+    <t>..X</t>
+  </si>
+  <si>
+    <t>frag_6_3</t>
+  </si>
+  <si>
+    <t>节点行动</t>
+  </si>
+  <si>
+    <t>奖励（好事件）</t>
+  </si>
+  <si>
+    <t>厄运（坏事件）</t>
+  </si>
+  <si>
+    <t>X..</t>
+  </si>
+  <si>
+    <t>利息事件</t>
+  </si>
+  <si>
+    <t>frag_8_1</t>
+  </si>
+  <si>
+    <t>60,100</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>恢复红心</t>
+  </si>
+  <si>
+    <t>frag_9_1</t>
+  </si>
+  <si>
+    <t>抽奖机</t>
+  </si>
+  <si>
     <t>40,100</t>
-  </si>
-  <si>
-    <t>利息</t>
-  </si>
-  <si>
-    <t>X...</t>
-  </si>
-  <si>
-    <t>4～9</t>
-  </si>
-  <si>
-    <t>boss</t>
-  </si>
-  <si>
-    <t>frag_5_2</t>
-  </si>
-  <si>
-    <t>...X</t>
-  </si>
-  <si>
-    <t>frag_5_3</t>
-  </si>
-  <si>
-    <t>XX.</t>
-  </si>
-  <si>
-    <t>frag_5_4</t>
-  </si>
-  <si>
-    <t>❤️❤️❤️</t>
-  </si>
-  <si>
-    <t>.XX</t>
-  </si>
-  <si>
-    <t>普通事件</t>
-  </si>
-  <si>
-    <t>frag_6_1</t>
-  </si>
-  <si>
-    <t>50,100</t>
-  </si>
-  <si>
-    <t>强化类消耗品n选1</t>
-  </si>
-  <si>
-    <t>调整类消耗品n选1</t>
-  </si>
-  <si>
-    <t>frag_6_2</t>
-  </si>
-  <si>
-    <t>事件（有好有坏）</t>
-  </si>
-  <si>
-    <t>..X</t>
-  </si>
-  <si>
-    <t>frag_6_3</t>
-  </si>
-  <si>
-    <t>节点行动</t>
-  </si>
-  <si>
-    <t>奖励（好事件）</t>
-  </si>
-  <si>
-    <t>厄运（坏事件）</t>
-  </si>
-  <si>
-    <t>X..</t>
-  </si>
-  <si>
-    <t>利息事件</t>
-  </si>
-  <si>
-    <t>frag_8_1</t>
-  </si>
-  <si>
-    <t>60,100</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>恢复红心</t>
-  </si>
-  <si>
-    <t>frag_9_1</t>
-  </si>
-  <si>
-    <t>抽奖机</t>
   </si>
   <si>
     <t>m_cherry</t>
@@ -1771,37 +1765,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="4:19">
+    <row r="21" spans="4:5">
       <c r="D21" s="5"/>
       <c r="E21" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" s="3">
-        <v>10</v>
-      </c>
-      <c r="M21" s="3">
-        <v>11</v>
-      </c>
-      <c r="N21" s="3">
-        <v>12</v>
-      </c>
-      <c r="O21" s="3">
-        <v>13</v>
-      </c>
-      <c r="P21" s="3">
-        <v>14</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>15</v>
-      </c>
-      <c r="R21" s="3">
-        <v>16</v>
-      </c>
-      <c r="S21" s="3">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="4:19">
@@ -1810,7 +1777,7 @@
         <v>30</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L22" s="3">
         <v>20</v>
@@ -1839,7 +1806,7 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3">
         <v>1400</v>
@@ -1851,7 +1818,7 @@
         <v>30</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L23" s="3">
         <v>30</v>
@@ -1884,7 +1851,7 @@
         <v>24</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L24" s="3">
         <v>40</v>
@@ -1911,42 +1878,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="4:19">
+    <row r="25" spans="4:5">
       <c r="D25" s="5"/>
       <c r="E25" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" s="3">
-        <v>50</v>
-      </c>
-      <c r="M25" s="3">
-        <v>51</v>
-      </c>
-      <c r="N25" s="3">
-        <v>52</v>
-      </c>
-      <c r="O25" s="3">
-        <v>53</v>
-      </c>
-      <c r="P25" s="3">
-        <v>54</v>
-      </c>
-      <c r="Q25" s="3">
-        <v>55</v>
-      </c>
-      <c r="R25" s="3">
-        <v>56</v>
-      </c>
-      <c r="S25" s="3">
-        <v>57</v>
-      </c>
     </row>
     <row r="26" spans="2:21">
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C26" s="3">
         <v>1400</v>
@@ -1958,7 +1898,7 @@
         <v>28</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="4:23">
@@ -1967,10 +1907,10 @@
         <v>24</v>
       </c>
       <c r="U27" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="4:21">
@@ -1979,12 +1919,12 @@
         <v>30</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="2:21">
       <c r="B29" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C29" s="3">
         <v>1400</v>
@@ -1996,7 +1936,7 @@
         <v>22</v>
       </c>
       <c r="U29" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="4:21">
@@ -2008,7 +1948,7 @@
         <v>24</v>
       </c>
       <c r="U30" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="4:21">
@@ -2020,7 +1960,7 @@
         <v>24</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="4:21">
@@ -2032,46 +1972,46 @@
         <v>22</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="2:21">
       <c r="B33" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" s="3">
         <v>1400</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="5:21">
       <c r="E34" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="35" spans="2:14">
       <c r="B35" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3">
         <v>1400</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>19</v>
@@ -2083,18 +2023,18 @@
     </row>
     <row r="36" spans="5:5">
       <c r="E36" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C37" s="3">
         <v>1400</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>26</v>
@@ -2102,53 +2042,53 @@
     </row>
     <row r="38" spans="5:5">
       <c r="E38" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="2:23">
       <c r="B39" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C39" s="3">
         <v>1400</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="5:21">
       <c r="E40" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T40" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="U40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="2:21">
       <c r="B41" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C41" s="3">
         <v>1400</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="6"/>
       <c r="U41" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="5:21">
@@ -2157,98 +2097,98 @@
       </c>
       <c r="T42" s="6"/>
       <c r="U42" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="2:21">
       <c r="B43" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C43" s="3">
         <v>1400</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="6"/>
       <c r="U43" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="5:21">
       <c r="E44" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="T44" s="6"/>
       <c r="U44" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="5:5">
       <c r="E45" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="2:21">
       <c r="B46" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C46" s="3">
         <v>1400</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>26</v>
       </c>
       <c r="T46" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="5:21">
       <c r="E47" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T47" s="7"/>
       <c r="U47" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="5:21">
       <c r="E48" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="T48" s="7"/>
       <c r="U48" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="2:23">
       <c r="B49" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C49" s="3">
         <v>1400</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>19</v>
       </c>
       <c r="T49" s="7"/>
       <c r="U49" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="W49" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="5:21">
@@ -2257,25 +2197,25 @@
       </c>
       <c r="T50" s="7"/>
       <c r="U50" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="2:21">
       <c r="B51" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C51" s="3">
         <v>1400</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="7"/>
       <c r="U51" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="5:5">
@@ -2298,13 +2238,13 @@
         <v>50</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>23</v>
@@ -2320,13 +2260,13 @@
         <v>50</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>25</v>
@@ -2342,13 +2282,13 @@
         <v>50</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>27</v>
@@ -2373,13 +2313,13 @@
         <v>50</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>29</v>
@@ -2404,13 +2344,13 @@
         <v>50</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
@@ -2436,13 +2376,13 @@
         <v>50</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>33</v>
@@ -2478,13 +2418,13 @@
         <v>50</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>35</v>
@@ -2520,16 +2460,16 @@
         <v>50</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="3:5">
@@ -2562,16 +2502,16 @@
         <v>50</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="3:5">
@@ -2604,16 +2544,16 @@
         <v>50</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75" spans="3:5">
@@ -2656,16 +2596,16 @@
         <v>50</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="3:5">
@@ -2674,7 +2614,7 @@
         <v/>
       </c>
       <c r="E79" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="2:8">
@@ -2687,16 +2627,16 @@
         <v>50</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="3:5">
@@ -2705,7 +2645,7 @@
         <v/>
       </c>
       <c r="E81" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="2:8">
@@ -2718,16 +2658,16 @@
         <v>50</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="3:5">
@@ -2736,7 +2676,7 @@
         <v/>
       </c>
       <c r="E83" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -2749,16 +2689,16 @@
         <v>50</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="3:5">
@@ -2767,7 +2707,7 @@
         <v/>
       </c>
       <c r="E85" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="2:8">
@@ -2780,16 +2720,16 @@
         <v>50</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="87" spans="3:5">
@@ -2811,16 +2751,16 @@
         <v>50</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="3:7">
@@ -2829,7 +2769,7 @@
         <v/>
       </c>
       <c r="E89" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G89" s="3" t="str">
         <f>IF(B89="","",B89&amp;"_cherry")</f>
@@ -2842,7 +2782,7 @@
         <v/>
       </c>
       <c r="E90" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -2855,16 +2795,16 @@
         <v>50</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="3:5">
@@ -2873,7 +2813,7 @@
         <v/>
       </c>
       <c r="E92" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93" spans="3:5">
@@ -2882,7 +2822,7 @@
         <v/>
       </c>
       <c r="E93" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="2:8">
@@ -2895,16 +2835,16 @@
         <v>50</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="3:5">
@@ -2926,16 +2866,16 @@
         <v>50</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="3:5">
@@ -2963,13 +2903,13 @@
         <v>50</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>23</v>
@@ -2985,13 +2925,13 @@
         <v>50</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>25</v>
@@ -3007,13 +2947,13 @@
         <v>50</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>27</v>
@@ -3038,13 +2978,13 @@
         <v>50</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>29</v>
@@ -3069,13 +3009,13 @@
         <v>50</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>31</v>
@@ -3101,13 +3041,13 @@
         <v>50</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>33</v>
@@ -3143,13 +3083,13 @@
         <v>50</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E110" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>35</v>
@@ -3185,16 +3125,16 @@
         <v>50</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="114" spans="3:5">
@@ -3227,16 +3167,16 @@
         <v>50</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117" spans="3:5">
@@ -3269,16 +3209,16 @@
         <v>50</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E119" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="120" spans="3:5">
@@ -3321,16 +3261,16 @@
         <v>50</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="3:5">
@@ -3339,7 +3279,7 @@
         <v/>
       </c>
       <c r="E124" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="125" spans="2:8">
@@ -3352,16 +3292,16 @@
         <v>50</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="3:5">
@@ -3370,7 +3310,7 @@
         <v/>
       </c>
       <c r="E126" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="127" spans="2:8">
@@ -3383,16 +3323,16 @@
         <v>50</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="3:5">
@@ -3401,7 +3341,7 @@
         <v/>
       </c>
       <c r="E128" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129" spans="2:8">
@@ -3414,16 +3354,16 @@
         <v>50</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="130" spans="3:5">
@@ -3432,7 +3372,7 @@
         <v/>
       </c>
       <c r="E130" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="131" spans="2:8">
@@ -3445,16 +3385,16 @@
         <v>50</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="3:5">
@@ -3476,16 +3416,16 @@
         <v>50</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="134" spans="3:7">
@@ -3494,7 +3434,7 @@
         <v/>
       </c>
       <c r="E134" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G134" s="3" t="str">
         <f>IF(B134="","",B134&amp;"_cherry")</f>
@@ -3507,7 +3447,7 @@
         <v/>
       </c>
       <c r="E135" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="2:8">
@@ -3520,16 +3460,16 @@
         <v>50</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -3538,7 +3478,7 @@
         <v/>
       </c>
       <c r="E137" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -3547,7 +3487,7 @@
         <v/>
       </c>
       <c r="E138" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="139" spans="2:8">
@@ -3560,16 +3500,16 @@
         <v>50</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -3591,16 +3531,16 @@
         <v>50</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -3628,13 +3568,13 @@
         <v>50</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H144" s="3" t="s">
         <v>23</v>
@@ -3650,13 +3590,13 @@
         <v>50</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H145" s="3" t="s">
         <v>25</v>
@@ -3672,13 +3612,13 @@
         <v>50</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>27</v>
@@ -3703,13 +3643,13 @@
         <v>50</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H148" s="3" t="s">
         <v>29</v>
@@ -3734,13 +3674,13 @@
         <v>50</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H150" s="3" t="s">
         <v>31</v>
@@ -3766,13 +3706,13 @@
         <v>50</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H152" s="3" t="s">
         <v>33</v>
@@ -3808,13 +3748,13 @@
         <v>50</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H155" s="3" t="s">
         <v>35</v>
@@ -3850,16 +3790,16 @@
         <v>50</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="3:5">
@@ -3892,16 +3832,16 @@
         <v>50</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="3:5">
@@ -3934,16 +3874,16 @@
         <v>50</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165" spans="3:5">
@@ -3986,16 +3926,16 @@
         <v>50</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169" spans="3:5">
@@ -4004,7 +3944,7 @@
         <v/>
       </c>
       <c r="E169" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" spans="2:8">
@@ -4017,16 +3957,16 @@
         <v>50</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="171" spans="3:5">
@@ -4035,7 +3975,7 @@
         <v/>
       </c>
       <c r="E171" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="172" spans="2:8">
@@ -4048,16 +3988,16 @@
         <v>50</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173" spans="3:5">
@@ -4066,7 +4006,7 @@
         <v/>
       </c>
       <c r="E173" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="174" spans="2:8">
@@ -4079,16 +4019,16 @@
         <v>50</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="175" spans="3:5">
@@ -4097,7 +4037,7 @@
         <v/>
       </c>
       <c r="E175" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176" spans="2:8">
@@ -4110,16 +4050,16 @@
         <v>50</v>
       </c>
       <c r="D176" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F176" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E176" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F176" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="H176" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="3:5">
@@ -4141,16 +4081,16 @@
         <v>50</v>
       </c>
       <c r="D178" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F178" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E178" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="H178" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="179" spans="3:7">
@@ -4159,7 +4099,7 @@
         <v/>
       </c>
       <c r="E179" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G179" s="3" t="str">
         <f>IF(B179="","",B179&amp;"_cherry")</f>
@@ -4172,7 +4112,7 @@
         <v/>
       </c>
       <c r="E180" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="181" spans="2:8">
@@ -4185,16 +4125,16 @@
         <v>50</v>
       </c>
       <c r="D181" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F181" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E181" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="H181" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" spans="3:5">
@@ -4203,7 +4143,7 @@
         <v/>
       </c>
       <c r="E182" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="183" spans="3:5">
@@ -4212,7 +4152,7 @@
         <v/>
       </c>
       <c r="E183" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="184" spans="2:8">
@@ -4225,16 +4165,16 @@
         <v>50</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="185" spans="3:5">
@@ -4256,16 +4196,16 @@
         <v>50</v>
       </c>
       <c r="D186" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F186" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="H186" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="187" spans="3:5">
@@ -4293,13 +4233,13 @@
         <v>50</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H189" s="3" t="s">
         <v>23</v>
@@ -4315,13 +4255,13 @@
         <v>50</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H190" s="3" t="s">
         <v>25</v>
@@ -4337,13 +4277,13 @@
         <v>50</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H191" s="3" t="s">
         <v>27</v>
@@ -4368,13 +4308,13 @@
         <v>50</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H193" s="3" t="s">
         <v>29</v>
@@ -4399,13 +4339,13 @@
         <v>50</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>31</v>
@@ -4431,13 +4371,13 @@
         <v>50</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>33</v>
@@ -4473,13 +4413,13 @@
         <v>50</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>35</v>
@@ -4515,16 +4455,16 @@
         <v>50</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H203" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="204" spans="3:5">
@@ -4557,16 +4497,16 @@
         <v>50</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H206" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="207" spans="3:5">
@@ -4599,16 +4539,16 @@
         <v>50</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="210" spans="3:5">
@@ -4651,16 +4591,16 @@
         <v>50</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H213" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="214" spans="3:5">
@@ -4669,7 +4609,7 @@
         <v/>
       </c>
       <c r="E214" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="215" spans="2:8">
@@ -4682,16 +4622,16 @@
         <v>50</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H215" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="216" spans="3:5">
@@ -4700,7 +4640,7 @@
         <v/>
       </c>
       <c r="E216" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="217" spans="2:8">
@@ -4713,16 +4653,16 @@
         <v>50</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F217" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="218" spans="3:5">
@@ -4731,7 +4671,7 @@
         <v/>
       </c>
       <c r="E218" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="219" spans="2:8">
@@ -4744,16 +4684,16 @@
         <v>50</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="220" spans="3:5">
@@ -4762,7 +4702,7 @@
         <v/>
       </c>
       <c r="E220" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="221" spans="2:8">
@@ -4775,16 +4715,16 @@
         <v>50</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="222" spans="3:5">
@@ -4806,16 +4746,16 @@
         <v>50</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="224" spans="3:7">
@@ -4824,7 +4764,7 @@
         <v/>
       </c>
       <c r="E224" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G224" s="3" t="str">
         <f>IF(B224="","",B224&amp;"_cherry")</f>
@@ -4837,7 +4777,7 @@
         <v/>
       </c>
       <c r="E225" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="2:8">
@@ -4850,16 +4790,16 @@
         <v>50</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="227" spans="3:5">
@@ -4868,7 +4808,7 @@
         <v/>
       </c>
       <c r="E227" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="228" spans="3:5">
@@ -4877,7 +4817,7 @@
         <v/>
       </c>
       <c r="E228" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="2:8">
@@ -4890,16 +4830,16 @@
         <v>50</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="230" spans="3:5">
@@ -4921,16 +4861,16 @@
         <v>50</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="232" spans="3:5">
@@ -4958,13 +4898,13 @@
         <v>50</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>23</v>
@@ -4980,13 +4920,13 @@
         <v>50</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>25</v>
@@ -5002,13 +4942,13 @@
         <v>50</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F236" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>27</v>
@@ -5033,13 +4973,13 @@
         <v>50</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>29</v>
@@ -5064,13 +5004,13 @@
         <v>50</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>31</v>
@@ -5096,13 +5036,13 @@
         <v>50</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F242" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>33</v>
@@ -5138,13 +5078,13 @@
         <v>50</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F245" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>35</v>
@@ -5180,16 +5120,16 @@
         <v>50</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="249" spans="3:5">
@@ -5222,16 +5162,16 @@
         <v>50</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F251" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252" spans="3:5">
@@ -5264,16 +5204,16 @@
         <v>50</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F254" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="255" spans="3:5">
@@ -5316,16 +5256,16 @@
         <v>50</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="259" spans="3:5">
@@ -5334,7 +5274,7 @@
         <v/>
       </c>
       <c r="E259" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="260" spans="2:8">
@@ -5347,16 +5287,16 @@
         <v>50</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="261" spans="3:5">
@@ -5365,7 +5305,7 @@
         <v/>
       </c>
       <c r="E261" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="262" spans="2:8">
@@ -5378,16 +5318,16 @@
         <v>50</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263" spans="3:5">
@@ -5396,7 +5336,7 @@
         <v/>
       </c>
       <c r="E263" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="264" spans="2:8">
@@ -5409,16 +5349,16 @@
         <v>50</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H264" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="265" spans="3:5">
@@ -5427,7 +5367,7 @@
         <v/>
       </c>
       <c r="E265" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="266" spans="2:8">
@@ -5440,16 +5380,16 @@
         <v>50</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H266" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="267" spans="3:5">
@@ -5471,16 +5411,16 @@
         <v>50</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H268" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="269" spans="3:7">
@@ -5489,7 +5429,7 @@
         <v/>
       </c>
       <c r="E269" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G269" s="3" t="str">
         <f>IF(B269="","",B269&amp;"_cherry")</f>
@@ -5502,7 +5442,7 @@
         <v/>
       </c>
       <c r="E270" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="271" spans="2:8">
@@ -5515,16 +5455,16 @@
         <v>50</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H271" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="272" spans="3:5">
@@ -5533,7 +5473,7 @@
         <v/>
       </c>
       <c r="E272" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="273" spans="3:5">
@@ -5542,7 +5482,7 @@
         <v/>
       </c>
       <c r="E273" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="274" spans="2:8">
@@ -5555,16 +5495,16 @@
         <v>50</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H274" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="275" spans="3:5">
@@ -5586,16 +5526,16 @@
         <v>50</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="277" spans="3:5">
@@ -5623,13 +5563,13 @@
         <v>50</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>23</v>
@@ -5645,13 +5585,13 @@
         <v>50</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>25</v>
@@ -5667,13 +5607,13 @@
         <v>50</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>27</v>
@@ -5698,13 +5638,13 @@
         <v>50</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>29</v>
@@ -5729,13 +5669,13 @@
         <v>50</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>31</v>
@@ -5761,13 +5701,13 @@
         <v>50</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>33</v>
@@ -5803,13 +5743,13 @@
         <v>50</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>35</v>
@@ -5845,16 +5785,16 @@
         <v>50</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H293" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="294" spans="3:5">
@@ -5887,16 +5827,16 @@
         <v>50</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H296" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="297" spans="3:5">
@@ -5929,16 +5869,16 @@
         <v>50</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H299" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="300" spans="3:5">
@@ -5981,16 +5921,16 @@
         <v>50</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H303" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="304" spans="3:5">
@@ -5999,7 +5939,7 @@
         <v/>
       </c>
       <c r="E304" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="305" spans="2:8">
@@ -6012,16 +5952,16 @@
         <v>50</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H305" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="306" spans="3:5">
@@ -6030,7 +5970,7 @@
         <v/>
       </c>
       <c r="E306" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="307" spans="2:8">
@@ -6043,16 +5983,16 @@
         <v>50</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H307" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="308" spans="3:5">
@@ -6061,7 +6001,7 @@
         <v/>
       </c>
       <c r="E308" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="309" spans="2:8">
@@ -6074,16 +6014,16 @@
         <v>50</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H309" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="310" spans="3:5">
@@ -6092,7 +6032,7 @@
         <v/>
       </c>
       <c r="E310" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="311" spans="2:8">
@@ -6105,16 +6045,16 @@
         <v>50</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H311" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="312" spans="3:5">
@@ -6136,16 +6076,16 @@
         <v>50</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H313" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="314" spans="3:7">
@@ -6154,7 +6094,7 @@
         <v/>
       </c>
       <c r="E314" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G314" s="3" t="str">
         <f>IF(B314="","",B314&amp;"_cherry")</f>
@@ -6167,7 +6107,7 @@
         <v/>
       </c>
       <c r="E315" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="316" spans="2:8">
@@ -6180,16 +6120,16 @@
         <v>50</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H316" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="317" spans="3:5">
@@ -6198,7 +6138,7 @@
         <v/>
       </c>
       <c r="E317" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="318" spans="3:5">
@@ -6207,7 +6147,7 @@
         <v/>
       </c>
       <c r="E318" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="319" spans="2:8">
@@ -6220,16 +6160,16 @@
         <v>50</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H319" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="320" spans="3:5">
@@ -6251,16 +6191,16 @@
         <v>50</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F321" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H321" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="322" spans="3:5">
@@ -6288,13 +6228,13 @@
         <v>50</v>
       </c>
       <c r="D324" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H324" s="3" t="s">
         <v>23</v>
@@ -6310,13 +6250,13 @@
         <v>50</v>
       </c>
       <c r="D325" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H325" s="3" t="s">
         <v>25</v>
@@ -6332,13 +6272,13 @@
         <v>50</v>
       </c>
       <c r="D326" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H326" s="3" t="s">
         <v>27</v>
@@ -6363,13 +6303,13 @@
         <v>50</v>
       </c>
       <c r="D328" s="4" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H328" s="3" t="s">
         <v>29</v>
@@ -6394,13 +6334,13 @@
         <v>50</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H330" s="3" t="s">
         <v>31</v>
@@ -6426,13 +6366,13 @@
         <v>50</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H332" s="3" t="s">
         <v>33</v>
@@ -6468,13 +6408,13 @@
         <v>50</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>24</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H335" s="3" t="s">
         <v>35</v>
@@ -6510,16 +6450,16 @@
         <v>50</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>30</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H338" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="339" spans="3:5">
@@ -6552,16 +6492,16 @@
         <v>50</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H341" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="342" spans="3:5">
@@ -6594,16 +6534,16 @@
         <v>50</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H344" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="345" spans="3:5">
@@ -6646,16 +6586,16 @@
         <v>50</v>
       </c>
       <c r="D348" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H348" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="349" spans="3:5">
@@ -6664,7 +6604,7 @@
         <v/>
       </c>
       <c r="E349" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="350" spans="2:8">
@@ -6677,16 +6617,16 @@
         <v>50</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H350" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="351" spans="3:5">
@@ -6695,7 +6635,7 @@
         <v/>
       </c>
       <c r="E351" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="352" spans="2:8">
@@ -6708,16 +6648,16 @@
         <v>50</v>
       </c>
       <c r="D352" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H352" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="353" spans="3:5">
@@ -6726,7 +6666,7 @@
         <v/>
       </c>
       <c r="E353" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="354" spans="2:8">
@@ -6739,16 +6679,16 @@
         <v>50</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="355" spans="3:5">
@@ -6757,7 +6697,7 @@
         <v/>
       </c>
       <c r="E355" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="356" spans="2:8">
@@ -6770,16 +6710,16 @@
         <v>50</v>
       </c>
       <c r="D356" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H356" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="357" spans="3:5">
@@ -6801,16 +6741,16 @@
         <v>50</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H358" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="359" spans="3:7">
@@ -6819,7 +6759,7 @@
         <v/>
       </c>
       <c r="E359" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G359" s="3" t="str">
         <f>IF(B359="","",B359&amp;"_cherry")</f>
@@ -6832,7 +6772,7 @@
         <v/>
       </c>
       <c r="E360" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="361" spans="2:8">
@@ -6845,16 +6785,16 @@
         <v>50</v>
       </c>
       <c r="D361" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H361" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="362" spans="3:5">
@@ -6863,7 +6803,7 @@
         <v/>
       </c>
       <c r="E362" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="363" spans="3:5">
@@ -6872,7 +6812,7 @@
         <v/>
       </c>
       <c r="E363" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="364" spans="2:8">
@@ -6885,16 +6825,16 @@
         <v>50</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>19</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H364" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="365" spans="3:5">
@@ -6916,16 +6856,16 @@
         <v>50</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H366" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="367" spans="3:5">
@@ -6979,22 +6919,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7002,25 +6942,25 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7037,13 +6977,13 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>13</v>
@@ -7051,16 +6991,16 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="G4" s="1">
         <v>80</v>
@@ -7068,16 +7008,16 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="G5" s="1">
         <v>20</v>
@@ -7085,16 +7025,16 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
@@ -7102,33 +7042,33 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:7">
       <c r="B8" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>123</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -7136,19 +7076,19 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="G9" s="1">
         <v>6</v>
@@ -7156,19 +7096,19 @@
     </row>
     <row r="10" ht="17" spans="2:7">
       <c r="B10" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>商店</t>
+  </si>
+  <si>
+    <t>frag_4_7</t>
   </si>
   <si>
     <t>frag_5_1</t>
@@ -1353,7 +1356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -1517,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>28</v>
@@ -1536,7 +1539,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>28</v>
@@ -1563,7 +1566,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>28</v>
@@ -1614,7 +1617,7 @@
         <v>34</v>
       </c>
       <c r="C21" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>28</v>
@@ -1692,7 +1695,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>28</v>
@@ -1728,7 +1731,7 @@
         <v>42</v>
       </c>
       <c r="C27" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>28</v>
@@ -1773,254 +1776,278 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
+    <row r="31" spans="2:5">
       <c r="B31" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5">
+      <c r="E32" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5">
+      <c r="E33" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20">
+      <c r="B34" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="C34" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T31" s="1" t="s">
+      <c r="T34" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="5:20">
+      <c r="E35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13">
+      <c r="B36" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="32" spans="5:20">
-      <c r="E32" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M36" s="1">
         <f>12*12</f>
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="5:5">
-      <c r="E34" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="1" t="s">
+    <row r="37" spans="5:5">
+      <c r="E37" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E35" s="1" t="s">
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="5:5">
-      <c r="E36" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22">
-      <c r="B37" s="1" t="s">
+    <row r="39" spans="5:5">
+      <c r="E39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V37" s="1" t="s">
+    </row>
+    <row r="40" spans="2:22">
+      <c r="B40" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="38" spans="5:20">
-      <c r="E38" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20">
-      <c r="B39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="5:20">
+      <c r="C40" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T40" s="1" t="s">
+      <c r="V40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" spans="5:20">
+      <c r="E41" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20">
+      <c r="B42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T42" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="2:20">
-      <c r="B41" s="1" t="s">
+    <row r="43" spans="5:20">
+      <c r="E43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T43" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="5:20">
-      <c r="E42" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="5:5">
-      <c r="E43" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="44" spans="2:20">
       <c r="B44" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C44" s="1">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S44" s="4" t="s">
-        <v>68</v>
-      </c>
       <c r="T44" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="5:20">
       <c r="E45" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T45" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="5:5">
+      <c r="E46" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20">
+      <c r="B47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T47" s="1" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="5:20">
-      <c r="E46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="2:22">
-      <c r="B47" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="V47" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="48" spans="5:20">
       <c r="E48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="5:20">
+      <c r="E49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="T49" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50" spans="2:22">
+      <c r="B50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T48" s="1" t="s">
+      <c r="T50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="5:20">
+      <c r="E51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T51" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="2:20">
-      <c r="B49" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="1">
-        <v>1400</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="1" t="s">
+    <row r="52" spans="2:20">
+      <c r="B52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T49" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="50" spans="5:5">
-      <c r="E50" s="1" t="s">
+      <c r="T52" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="5:5">
-      <c r="E51" s="1" t="s">
+    <row r="54" spans="5:5">
+      <c r="E54" s="1" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="T38:T42"/>
-    <mergeCell ref="T44:T49"/>
+    <mergeCell ref="T41:T45"/>
+    <mergeCell ref="T47:T52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/GourmetProject/GameConfig/Datas/fragment_material.xlsx
+++ b/GourmetProject/GameConfig/Datas/fragment_material.xlsx
@@ -1459,7 +1459,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -1473,7 +1473,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="1">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>19</v>
@@ -1487,7 +1487,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="1">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -1501,7 +1501,7 @@
         <v>25</v>
       </c>
       <c r="C11" s="1">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
@@ -1520,7 +1520,7 @@
         <v>27</v>
       </c>
       <c r="C13" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>28</v>
@@ -1539,7 +1539,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>28</v>
@@ -1566,7 +1566,7 @@
         <v>31</v>
       </c>
       <c r="C18" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>28</v>
@@ -1617,7 +1617,7 @@
         <v>34</v>
       </c>
       <c r="C21" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>28</v>
@@ -1695,7 +1695,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>28</v>
@@ -1731,7 +1731,7 @@
         <v>42</v>
       </c>
       <c r="C27" s="1">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>28</v>
@@ -1781,7 +1781,7 @@
         <v>47</v>
       </c>
       <c r="C31" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>28</v>
@@ -1805,7 +1805,7 @@
         <v>48</v>
       </c>
       <c r="C34" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>49</v>
@@ -1833,7 +1833,7 @@
         <v>54</v>
       </c>
       <c r="C36" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>49</v>
@@ -1856,7 +1856,7 @@
         <v>56</v>
       </c>
       <c r="C38" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>49</v>
@@ -1875,7 +1875,7 @@
         <v>58</v>
       </c>
       <c r="C40" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>49</v>
@@ -1903,7 +1903,7 @@
         <v>62</v>
       </c>
       <c r="C42" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>49</v>
@@ -1928,7 +1928,7 @@
         <v>65</v>
       </c>
       <c r="C44" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>49</v>
@@ -1958,7 +1958,7 @@
         <v>68</v>
       </c>
       <c r="C47" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>49</v>
@@ -1994,7 +1994,7 @@
         <v>74</v>
       </c>
       <c r="C50" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>75</v>
@@ -2022,7 +2022,7 @@
         <v>78</v>
       </c>
       <c r="C52" s="1">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>75</v>
